--- a/LAPORAN_POSTTEST_DAN_PERBANDINGAN_CANVA.xlsx
+++ b/LAPORAN_POSTTEST_DAN_PERBANDINGAN_CANVA.xlsx
@@ -19,6 +19,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10 Dashboard Grafik" sheetId="10" state="visible" r:id="rId10"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="11 Data Mentah" sheetId="11" state="visible" r:id="rId11"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="12 Data Berpasangan" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="13 Analisis Waktu" sheetId="13" state="visible" r:id="rId13"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -207,7 +208,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="56">
+  <cellXfs count="61">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -357,6 +358,21 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1428,6 +1444,104 @@
 </chartSpace>
 </file>
 
+<file path=xl/charts/chart19.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <style val="10"/>
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Waktu rata-rata per butir post-test (detik)</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <barChart>
+        <barDir val="col"/>
+        <grouping val="clustered"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'13 Analisis Waktu'!D5</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'13 Analisis Waktu'!$A$6:$A$25</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'13 Analisis Waktu'!$D$6:$D$25</f>
+            </numRef>
+          </val>
+        </ser>
+        <dLbls>
+          <showVal val="1"/>
+        </dLbls>
+        <gapWidth val="150"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>Detik</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <style val="10"/>
@@ -1534,6 +1648,128 @@
                 </a:pPr>
                 <a:r>
                   <a:t>Jawaban benar (dari 20)</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="r"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart20.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <style val="12"/>
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Waktu jawaban benar versus jawaban salah, per butir</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <barChart>
+        <barDir val="col"/>
+        <grouping val="clustered"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'13 Analisis Waktu'!I5</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'13 Analisis Waktu'!$A$6:$A$25</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'13 Analisis Waktu'!$I$6:$I$25</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <strRef>
+              <f>'13 Analisis Waktu'!J5</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'13 Analisis Waktu'!$A$6:$A$25</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'13 Analisis Waktu'!$J$6:$J$25</f>
+            </numRef>
+          </val>
+        </ser>
+        <gapWidth val="150"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>Detik</a:t>
                 </a:r>
               </a:p>
             </rich>
@@ -2794,6 +3030,55 @@
 </wsDr>
 </file>
 
+<file path=xl/drawings/drawing7.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>26</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="9360000" cy="3240000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="1" name="Chart 1"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>45</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="9360000" cy="3240000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="2" name="Chart 2"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -3708,7 +3993,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:F256"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
@@ -4943,7 +5228,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:V19"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
     <col width="24" customWidth="1" min="2" max="2"/>
@@ -6761,7 +7046,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:L22"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
     <col width="26" customWidth="1" min="2" max="2"/>
@@ -7361,6 +7646,2927 @@
     <mergeCell ref="A21:L21"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:V118"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="76" customWidth="1" min="5" max="5"/>
+    <col width="6" customWidth="1" min="6" max="6"/>
+    <col width="6" customWidth="1" min="7" max="7"/>
+    <col width="6" customWidth="1" min="8" max="8"/>
+    <col width="6" customWidth="1" min="9" max="9"/>
+    <col width="6" customWidth="1" min="10" max="10"/>
+    <col width="6" customWidth="1" min="11" max="11"/>
+    <col width="6" customWidth="1" min="12" max="12"/>
+    <col width="6" customWidth="1" min="13" max="13"/>
+    <col width="6" customWidth="1" min="14" max="14"/>
+    <col width="6" customWidth="1" min="15" max="15"/>
+    <col width="6" customWidth="1" min="16" max="16"/>
+    <col width="6" customWidth="1" min="17" max="17"/>
+    <col width="6" customWidth="1" min="18" max="18"/>
+    <col width="6" customWidth="1" min="19" max="19"/>
+    <col width="6" customWidth="1" min="20" max="20"/>
+    <col width="6" customWidth="1" min="21" max="21"/>
+    <col width="9" customWidth="1" min="22" max="22"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>ANALISIS WAKTU POST-TEST — PER BUTIR DAN PER PESERTA</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="36" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Diambil utuh dari sheet Time Data ekspor resmi Wayground. Kolom Vincent ditampilkan terpisah pada bagian C sebagai bukti dasar pengeluaran sesi QA, tetapi tidak ikut dalam perhitungan rata-rata mana pun.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="22" customHeight="1">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>A. WAKTU RATA-RATA PER BUTIR (15 sesi, Vincent dikeluarkan)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="34" customHeight="1">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>Butir</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>Pokok yang diuji</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>Rata-rata
+Wayground</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>Rata-rata
+hitung ulang</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>Tercepat</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>Terlama</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>Penjawab</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>p</t>
+        </is>
+      </c>
+      <c r="I5" s="4" t="inlineStr">
+        <is>
+          <t>Waktu
+jawaban benar</t>
+        </is>
+      </c>
+      <c r="J5" s="4" t="inlineStr">
+        <is>
+          <t>Waktu
+jawaban salah</t>
+        </is>
+      </c>
+      <c r="K5" s="4" t="inlineStr">
+        <is>
+          <t>Selisih</t>
+        </is>
+      </c>
+      <c r="L5" s="4" t="inlineStr">
+        <is>
+          <t>Catatan</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="22" customHeight="1">
+      <c r="A6" s="33" t="n">
+        <v>1</v>
+      </c>
+      <c r="B6" s="8" t="inlineStr">
+        <is>
+          <t>Kolaborasi real-time</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="n">
+        <v>23</v>
+      </c>
+      <c r="D6" s="26" t="n">
+        <v>24.2</v>
+      </c>
+      <c r="E6" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="F6" s="6" t="n">
+        <v>47</v>
+      </c>
+      <c r="G6" s="6" t="n">
+        <v>13</v>
+      </c>
+      <c r="H6" s="6" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="I6" s="6" t="n">
+        <v>22.9</v>
+      </c>
+      <c r="J6" s="6" t="n">
+        <v>28.7</v>
+      </c>
+      <c r="K6" s="6" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="L6" s="8" t="inlineStr"/>
+    </row>
+    <row r="7" ht="22" customHeight="1">
+      <c r="A7" s="33" t="n">
+        <v>2</v>
+      </c>
+      <c r="B7" s="8" t="inlineStr">
+        <is>
+          <t>Asal usul Canva (Fusion Books)</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="D7" s="26" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="F7" s="6" t="n">
+        <v>51</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>13</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="I7" s="6" t="n">
+        <v>17.3</v>
+      </c>
+      <c r="J7" s="6" t="n">
+        <v>26.8</v>
+      </c>
+      <c r="K7" s="6" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="L7" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Yang salah berpikir jauh lebih lama — butir membingungkan.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="22" customHeight="1">
+      <c r="A8" s="33" t="n">
+        <v>3</v>
+      </c>
+      <c r="B8" s="8" t="inlineStr">
+        <is>
+          <t>Brand Kit</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="D8" s="26" t="n">
+        <v>27.3</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>11</v>
+      </c>
+      <c r="F8" s="6" t="n">
+        <v>66</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>12</v>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="I8" s="6" t="n">
+        <v>36.2</v>
+      </c>
+      <c r="J8" s="6" t="n">
+        <v>22.9</v>
+      </c>
+      <c r="K8" s="6" t="n">
+        <v>-13.4</v>
+      </c>
+      <c r="L8" s="8" t="inlineStr"/>
+    </row>
+    <row r="9" ht="22" customHeight="1">
+      <c r="A9" s="33" t="n">
+        <v>4</v>
+      </c>
+      <c r="B9" s="8" t="inlineStr">
+        <is>
+          <t>Hierarki visual — yang bertentangan</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="n">
+        <v>31</v>
+      </c>
+      <c r="D9" s="26" t="n">
+        <v>33.5</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="F9" s="6" t="n">
+        <v>67</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>11</v>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="I9" s="6" t="n">
+        <v>36.8</v>
+      </c>
+      <c r="J9" s="6" t="n">
+        <v>19</v>
+      </c>
+      <c r="K9" s="6" t="n">
+        <v>-17.8</v>
+      </c>
+      <c r="L9" s="8" t="inlineStr"/>
+    </row>
+    <row r="10" ht="22" customHeight="1">
+      <c r="A10" s="33" t="n">
+        <v>5</v>
+      </c>
+      <c r="B10" s="8" t="inlineStr">
+        <is>
+          <t>Harga paket Pro</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="n">
+        <v>14</v>
+      </c>
+      <c r="D10" s="26" t="n">
+        <v>15.4</v>
+      </c>
+      <c r="E10" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="F10" s="6" t="n">
+        <v>35</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>11</v>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="I10" s="6" t="n">
+        <v>15.7</v>
+      </c>
+      <c r="J10" s="6" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="K10" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="L10" s="8" t="inlineStr"/>
+    </row>
+    <row r="11" ht="22" customHeight="1">
+      <c r="A11" s="33" t="n">
+        <v>6</v>
+      </c>
+      <c r="B11" s="8" t="inlineStr">
+        <is>
+          <t>Format ekspor PNG</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="n">
+        <v>28</v>
+      </c>
+      <c r="D11" s="26" t="n">
+        <v>30.2</v>
+      </c>
+      <c r="E11" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="F11" s="6" t="n">
+        <v>66</v>
+      </c>
+      <c r="G11" s="6" t="n">
+        <v>11</v>
+      </c>
+      <c r="H11" s="6" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="I11" s="6" t="n">
+        <v>30.5</v>
+      </c>
+      <c r="J11" s="6" t="n">
+        <v>29.3</v>
+      </c>
+      <c r="K11" s="6" t="n">
+        <v>-1.2</v>
+      </c>
+      <c r="L11" s="8" t="inlineStr"/>
+    </row>
+    <row r="12" ht="22" customHeight="1">
+      <c r="A12" s="33" t="n">
+        <v>7</v>
+      </c>
+      <c r="B12" s="8" t="inlineStr">
+        <is>
+          <t>Pernyataan benar tentang Canva</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="n">
+        <v>31</v>
+      </c>
+      <c r="D12" s="26" t="n">
+        <v>33.7</v>
+      </c>
+      <c r="E12" s="6" t="n">
+        <v>13</v>
+      </c>
+      <c r="F12" s="6" t="n">
+        <v>60</v>
+      </c>
+      <c r="G12" s="6" t="n">
+        <v>11</v>
+      </c>
+      <c r="H12" s="6" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="I12" s="6" t="n">
+        <v>34</v>
+      </c>
+      <c r="J12" s="6" t="n">
+        <v>32.5</v>
+      </c>
+      <c r="K12" s="6" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="L12" s="8" t="inlineStr"/>
+    </row>
+    <row r="13" ht="22" customHeight="1">
+      <c r="A13" s="33" t="n">
+        <v>8</v>
+      </c>
+      <c r="B13" s="8" t="inlineStr">
+        <is>
+          <t>Makna warna ungu liturgi</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="n">
+        <v>24</v>
+      </c>
+      <c r="D13" s="26" t="n">
+        <v>26</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="F13" s="6" t="n">
+        <v>64</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>11</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="I13" s="6" t="n">
+        <v>26</v>
+      </c>
+      <c r="J13" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K13" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L13" s="8" t="inlineStr"/>
+    </row>
+    <row r="14" ht="22" customHeight="1">
+      <c r="A14" s="33" t="n">
+        <v>9</v>
+      </c>
+      <c r="B14" s="8" t="inlineStr">
+        <is>
+          <t>Format ekspor MP4</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="n">
+        <v>22</v>
+      </c>
+      <c r="D14" s="26" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="E14" s="6" t="n">
+        <v>12</v>
+      </c>
+      <c r="F14" s="6" t="n">
+        <v>38</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>11</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="I14" s="6" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="J14" s="6" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="K14" s="6" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="L14" s="8" t="inlineStr"/>
+    </row>
+    <row r="15" ht="22" customHeight="1">
+      <c r="A15" s="33" t="n">
+        <v>10</v>
+      </c>
+      <c r="B15" s="8" t="inlineStr">
+        <is>
+          <t>Batas jumlah warna dan font</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="n">
+        <v>48</v>
+      </c>
+      <c r="D15" s="28" t="n">
+        <v>52.2</v>
+      </c>
+      <c r="E15" s="6" t="n">
+        <v>16</v>
+      </c>
+      <c r="F15" s="6" t="n">
+        <v>100</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>11</v>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="I15" s="6" t="n">
+        <v>53</v>
+      </c>
+      <c r="J15" s="6" t="n">
+        <v>48.5</v>
+      </c>
+      <c r="K15" s="6" t="n">
+        <v>-4.5</v>
+      </c>
+      <c r="L15" s="8" t="inlineStr">
+        <is>
+          <t>Butir paling lama dibaca — redaksi opsinya panjang.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="22" customHeight="1">
+      <c r="A16" s="33" t="n">
+        <v>11</v>
+      </c>
+      <c r="B16" s="8" t="inlineStr">
+        <is>
+          <t>Menu panel kiri</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="n">
+        <v>29</v>
+      </c>
+      <c r="D16" s="26" t="n">
+        <v>31.8</v>
+      </c>
+      <c r="E16" s="6" t="n">
+        <v>12</v>
+      </c>
+      <c r="F16" s="6" t="n">
+        <v>76</v>
+      </c>
+      <c r="G16" s="6" t="n">
+        <v>11</v>
+      </c>
+      <c r="H16" s="6" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="I16" s="6" t="n">
+        <v>29.4</v>
+      </c>
+      <c r="J16" s="6" t="n">
+        <v>33.8</v>
+      </c>
+      <c r="K16" s="6" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="L16" s="8" t="inlineStr"/>
+    </row>
+    <row r="17" ht="22" customHeight="1">
+      <c r="A17" s="33" t="n">
+        <v>12</v>
+      </c>
+      <c r="B17" s="8" t="inlineStr">
+        <is>
+          <t>Tiga pendiri Canva</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="n">
+        <v>33</v>
+      </c>
+      <c r="D17" s="26" t="n">
+        <v>35.6</v>
+      </c>
+      <c r="E17" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="F17" s="6" t="n">
+        <v>90</v>
+      </c>
+      <c r="G17" s="6" t="n">
+        <v>11</v>
+      </c>
+      <c r="H17" s="6" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="I17" s="6" t="n">
+        <v>35.4</v>
+      </c>
+      <c r="J17" s="6" t="n">
+        <v>36.3</v>
+      </c>
+      <c r="K17" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="L17" s="8" t="inlineStr"/>
+    </row>
+    <row r="18" ht="22" customHeight="1">
+      <c r="A18" s="33" t="n">
+        <v>13</v>
+      </c>
+      <c r="B18" s="8" t="inlineStr">
+        <is>
+          <t>Eyedropper</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="n">
+        <v>28</v>
+      </c>
+      <c r="D18" s="26" t="n">
+        <v>30.5</v>
+      </c>
+      <c r="E18" s="6" t="n">
+        <v>14</v>
+      </c>
+      <c r="F18" s="6" t="n">
+        <v>94</v>
+      </c>
+      <c r="G18" s="6" t="n">
+        <v>11</v>
+      </c>
+      <c r="H18" s="6" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="I18" s="6" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="J18" s="6" t="n">
+        <v>44</v>
+      </c>
+      <c r="K18" s="6" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="L18" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Yang salah berpikir jauh lebih lama — butir membingungkan.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="22" customHeight="1">
+      <c r="A19" s="33" t="n">
+        <v>14</v>
+      </c>
+      <c r="B19" s="8" t="inlineStr">
+        <is>
+          <t>Ukuran Instagram Feed</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="n">
+        <v>23</v>
+      </c>
+      <c r="D19" s="26" t="n">
+        <v>25.4</v>
+      </c>
+      <c r="E19" s="6" t="n">
+        <v>12</v>
+      </c>
+      <c r="F19" s="6" t="n">
+        <v>42</v>
+      </c>
+      <c r="G19" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="H19" s="6" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="I19" s="6" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="J19" s="6" t="n">
+        <v>31.5</v>
+      </c>
+      <c r="K19" s="6" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="L19" s="8" t="inlineStr"/>
+    </row>
+    <row r="20" ht="22" customHeight="1">
+      <c r="A20" s="33" t="n">
+        <v>15</v>
+      </c>
+      <c r="B20" s="8" t="inlineStr">
+        <is>
+          <t>Empat nilai berkarya</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="n">
+        <v>41</v>
+      </c>
+      <c r="D20" s="28" t="n">
+        <v>45.6</v>
+      </c>
+      <c r="E20" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="F20" s="6" t="n">
+        <v>132</v>
+      </c>
+      <c r="G20" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="H20" s="6" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="I20" s="6" t="n">
+        <v>55.3</v>
+      </c>
+      <c r="J20" s="6" t="n">
+        <v>23</v>
+      </c>
+      <c r="K20" s="6" t="n">
+        <v>-32.3</v>
+      </c>
+      <c r="L20" s="8" t="inlineStr">
+        <is>
+          <t>Butir paling lama dibaca — redaksi opsinya panjang.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="22" customHeight="1">
+      <c r="A21" s="33" t="n">
+        <v>16</v>
+      </c>
+      <c r="B21" s="8" t="inlineStr">
+        <is>
+          <t>Urutan langkah template</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="n">
+        <v>29</v>
+      </c>
+      <c r="D21" s="26" t="n">
+        <v>31.4</v>
+      </c>
+      <c r="E21" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="F21" s="6" t="n">
+        <v>69</v>
+      </c>
+      <c r="G21" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="H21" s="6" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="I21" s="6" t="n">
+        <v>25.4</v>
+      </c>
+      <c r="J21" s="6" t="n">
+        <v>37.4</v>
+      </c>
+      <c r="K21" s="6" t="n">
+        <v>12</v>
+      </c>
+      <c r="L21" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Yang salah berpikir jauh lebih lama — butir membingungkan.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="22" customHeight="1">
+      <c r="A22" s="33" t="n">
+        <v>17</v>
+      </c>
+      <c r="B22" s="8" t="inlineStr">
+        <is>
+          <t>Komentar pada elemen</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="n">
+        <v>55</v>
+      </c>
+      <c r="D22" s="28" t="n">
+        <v>59.8</v>
+      </c>
+      <c r="E22" s="6" t="n">
+        <v>11</v>
+      </c>
+      <c r="F22" s="6" t="n">
+        <v>343</v>
+      </c>
+      <c r="G22" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="H22" s="6" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="I22" s="6" t="n">
+        <v>21</v>
+      </c>
+      <c r="J22" s="6" t="n">
+        <v>69.5</v>
+      </c>
+      <c r="K22" s="6" t="n">
+        <v>48.5</v>
+      </c>
+      <c r="L22" s="8" t="inlineStr">
+        <is>
+          <t>Butir paling lama dibaca — redaksi opsinya panjang. Yang salah berpikir jauh lebih lama — butir membingungkan.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="22" customHeight="1">
+      <c r="A23" s="33" t="n">
+        <v>18</v>
+      </c>
+      <c r="B23" s="8" t="inlineStr">
+        <is>
+          <t>Etika AI</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="n">
+        <v>28</v>
+      </c>
+      <c r="D23" s="26" t="n">
+        <v>30.8</v>
+      </c>
+      <c r="E23" s="6" t="n">
+        <v>12</v>
+      </c>
+      <c r="F23" s="6" t="n">
+        <v>46</v>
+      </c>
+      <c r="G23" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="H23" s="6" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="I23" s="6" t="n">
+        <v>29.1</v>
+      </c>
+      <c r="J23" s="6" t="n">
+        <v>34.7</v>
+      </c>
+      <c r="K23" s="6" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="L23" s="8" t="inlineStr"/>
+    </row>
+    <row r="24" ht="22" customHeight="1">
+      <c r="A24" s="33" t="n">
+        <v>19</v>
+      </c>
+      <c r="B24" s="8" t="inlineStr">
+        <is>
+          <t>Skema warna monokromatik</t>
+        </is>
+      </c>
+      <c r="C24" s="6" t="n">
+        <v>31</v>
+      </c>
+      <c r="D24" s="26" t="n">
+        <v>33.9</v>
+      </c>
+      <c r="E24" s="6" t="n">
+        <v>17</v>
+      </c>
+      <c r="F24" s="6" t="n">
+        <v>70</v>
+      </c>
+      <c r="G24" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="H24" s="6" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="I24" s="6" t="n">
+        <v>38.5</v>
+      </c>
+      <c r="J24" s="6" t="n">
+        <v>27</v>
+      </c>
+      <c r="K24" s="6" t="n">
+        <v>-11.5</v>
+      </c>
+      <c r="L24" s="8" t="inlineStr"/>
+    </row>
+    <row r="25" ht="22" customHeight="1">
+      <c r="A25" s="33" t="n">
+        <v>20</v>
+      </c>
+      <c r="B25" s="8" t="inlineStr">
+        <is>
+          <t>Esensi tujuan pelatihan</t>
+        </is>
+      </c>
+      <c r="C25" s="6" t="n">
+        <v>24</v>
+      </c>
+      <c r="D25" s="26" t="n">
+        <v>25.9</v>
+      </c>
+      <c r="E25" s="6" t="n">
+        <v>11</v>
+      </c>
+      <c r="F25" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="G25" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="H25" s="6" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="I25" s="6" t="n">
+        <v>25.9</v>
+      </c>
+      <c r="J25" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K25" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L25" s="8" t="inlineStr"/>
+    </row>
+    <row r="66" ht="22" customHeight="1">
+      <c r="A66" s="3" t="inlineStr">
+        <is>
+          <t>B. MATRIKS WAKTU PENUH — 15 SESI x 20 BUTIR (detik)</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="34" customHeight="1">
+      <c r="A67" s="4" t="inlineStr">
+        <is>
+          <t>Nama</t>
+        </is>
+      </c>
+      <c r="B67" s="4" t="inlineStr">
+        <is>
+          <t>Q1</t>
+        </is>
+      </c>
+      <c r="C67" s="4" t="inlineStr">
+        <is>
+          <t>Q2</t>
+        </is>
+      </c>
+      <c r="D67" s="4" t="inlineStr">
+        <is>
+          <t>Q3</t>
+        </is>
+      </c>
+      <c r="E67" s="4" t="inlineStr">
+        <is>
+          <t>Q4</t>
+        </is>
+      </c>
+      <c r="F67" s="4" t="inlineStr">
+        <is>
+          <t>Q5</t>
+        </is>
+      </c>
+      <c r="G67" s="4" t="inlineStr">
+        <is>
+          <t>Q6</t>
+        </is>
+      </c>
+      <c r="H67" s="4" t="inlineStr">
+        <is>
+          <t>Q7</t>
+        </is>
+      </c>
+      <c r="I67" s="4" t="inlineStr">
+        <is>
+          <t>Q8</t>
+        </is>
+      </c>
+      <c r="J67" s="4" t="inlineStr">
+        <is>
+          <t>Q9</t>
+        </is>
+      </c>
+      <c r="K67" s="4" t="inlineStr">
+        <is>
+          <t>Q10</t>
+        </is>
+      </c>
+      <c r="L67" s="4" t="inlineStr">
+        <is>
+          <t>Q11</t>
+        </is>
+      </c>
+      <c r="M67" s="4" t="inlineStr">
+        <is>
+          <t>Q12</t>
+        </is>
+      </c>
+      <c r="N67" s="4" t="inlineStr">
+        <is>
+          <t>Q13</t>
+        </is>
+      </c>
+      <c r="O67" s="4" t="inlineStr">
+        <is>
+          <t>Q14</t>
+        </is>
+      </c>
+      <c r="P67" s="4" t="inlineStr">
+        <is>
+          <t>Q15</t>
+        </is>
+      </c>
+      <c r="Q67" s="4" t="inlineStr">
+        <is>
+          <t>Q16</t>
+        </is>
+      </c>
+      <c r="R67" s="4" t="inlineStr">
+        <is>
+          <t>Q17</t>
+        </is>
+      </c>
+      <c r="S67" s="4" t="inlineStr">
+        <is>
+          <t>Q18</t>
+        </is>
+      </c>
+      <c r="T67" s="4" t="inlineStr">
+        <is>
+          <t>Q19</t>
+        </is>
+      </c>
+      <c r="U67" s="4" t="inlineStr">
+        <is>
+          <t>Q20</t>
+        </is>
+      </c>
+      <c r="V67" s="4" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="37" t="inlineStr">
+        <is>
+          <t>Agnes Nurak</t>
+        </is>
+      </c>
+      <c r="B68" s="56" t="n">
+        <v>32</v>
+      </c>
+      <c r="C68" s="56" t="n">
+        <v>17</v>
+      </c>
+      <c r="D68" s="56" t="n">
+        <v>22</v>
+      </c>
+      <c r="E68" s="56" t="n">
+        <v>31</v>
+      </c>
+      <c r="F68" s="56" t="n">
+        <v>17</v>
+      </c>
+      <c r="G68" s="56" t="n">
+        <v>32</v>
+      </c>
+      <c r="H68" s="56" t="n">
+        <v>31</v>
+      </c>
+      <c r="I68" s="56" t="n">
+        <v>29</v>
+      </c>
+      <c r="J68" s="56" t="n">
+        <v>24</v>
+      </c>
+      <c r="K68" s="56" t="n">
+        <v>39</v>
+      </c>
+      <c r="L68" s="56" t="n">
+        <v>23</v>
+      </c>
+      <c r="M68" s="56" t="n">
+        <v>13</v>
+      </c>
+      <c r="N68" s="56" t="n">
+        <v>21</v>
+      </c>
+      <c r="O68" s="56" t="n">
+        <v>16</v>
+      </c>
+      <c r="P68" s="56" t="n">
+        <v>32</v>
+      </c>
+      <c r="Q68" s="56" t="n">
+        <v>15</v>
+      </c>
+      <c r="R68" s="56" t="n">
+        <v>20</v>
+      </c>
+      <c r="S68" s="56" t="n">
+        <v>35</v>
+      </c>
+      <c r="T68" s="56" t="n">
+        <v>18</v>
+      </c>
+      <c r="U68" s="56" t="n">
+        <v>38</v>
+      </c>
+      <c r="V68" s="57" t="n">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="37" t="inlineStr">
+        <is>
+          <t>Mien</t>
+        </is>
+      </c>
+      <c r="B69" s="56" t="n">
+        <v>38</v>
+      </c>
+      <c r="C69" s="58" t="n">
+        <v>51</v>
+      </c>
+      <c r="D69" s="56" t="n">
+        <v>29</v>
+      </c>
+      <c r="E69" s="56" t="n">
+        <v>31</v>
+      </c>
+      <c r="F69" s="56" t="n">
+        <v>35</v>
+      </c>
+      <c r="G69" s="58" t="n">
+        <v>66</v>
+      </c>
+      <c r="H69" s="58" t="n">
+        <v>60</v>
+      </c>
+      <c r="I69" s="58" t="n">
+        <v>64</v>
+      </c>
+      <c r="J69" s="56" t="n">
+        <v>37</v>
+      </c>
+      <c r="K69" s="58" t="n">
+        <v>57</v>
+      </c>
+      <c r="L69" s="56" t="n">
+        <v>34</v>
+      </c>
+      <c r="M69" s="58" t="n">
+        <v>62</v>
+      </c>
+      <c r="N69" s="56" t="n">
+        <v>32</v>
+      </c>
+      <c r="O69" s="56" t="n">
+        <v>23</v>
+      </c>
+      <c r="P69" s="56" t="n">
+        <v>35</v>
+      </c>
+      <c r="Q69" s="56" t="n">
+        <v>33</v>
+      </c>
+      <c r="R69" s="56" t="n">
+        <v>22</v>
+      </c>
+      <c r="S69" s="58" t="n">
+        <v>46</v>
+      </c>
+      <c r="T69" s="58" t="n">
+        <v>53</v>
+      </c>
+      <c r="U69" s="58" t="n">
+        <v>50</v>
+      </c>
+      <c r="V69" s="57" t="n">
+        <v>858</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="37" t="inlineStr">
+        <is>
+          <t>LESLY MARCHRITH NUSALY</t>
+        </is>
+      </c>
+      <c r="B70" s="56" t="n">
+        <v>13</v>
+      </c>
+      <c r="C70" s="56" t="n">
+        <v>9</v>
+      </c>
+      <c r="D70" s="56" t="n">
+        <v>11</v>
+      </c>
+      <c r="E70" s="56" t="n">
+        <v>19</v>
+      </c>
+      <c r="F70" s="59" t="n">
+        <v>5</v>
+      </c>
+      <c r="G70" s="56" t="n">
+        <v>9</v>
+      </c>
+      <c r="H70" s="56" t="n">
+        <v>13</v>
+      </c>
+      <c r="I70" s="56" t="n">
+        <v>7</v>
+      </c>
+      <c r="J70" s="56" t="n">
+        <v>12</v>
+      </c>
+      <c r="K70" s="56" t="n">
+        <v>16</v>
+      </c>
+      <c r="L70" s="56" t="n">
+        <v>12</v>
+      </c>
+      <c r="M70" s="56" t="n">
+        <v>16</v>
+      </c>
+      <c r="N70" s="56" t="n">
+        <v>23</v>
+      </c>
+      <c r="O70" s="56" t="n">
+        <v>12</v>
+      </c>
+      <c r="P70" s="56" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q70" s="56" t="n">
+        <v>32</v>
+      </c>
+      <c r="R70" s="56" t="n">
+        <v>11</v>
+      </c>
+      <c r="S70" s="56" t="n">
+        <v>12</v>
+      </c>
+      <c r="T70" s="56" t="n">
+        <v>17</v>
+      </c>
+      <c r="U70" s="56" t="n">
+        <v>11</v>
+      </c>
+      <c r="V70" s="57" t="n">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="37" t="inlineStr">
+        <is>
+          <t>Gerarda Ina</t>
+        </is>
+      </c>
+      <c r="B71" s="56" t="n">
+        <v>31</v>
+      </c>
+      <c r="C71" s="56" t="n">
+        <v>40</v>
+      </c>
+      <c r="D71" s="58" t="n">
+        <v>66</v>
+      </c>
+      <c r="E71" s="58" t="n">
+        <v>67</v>
+      </c>
+      <c r="F71" s="56" t="n">
+        <v>6</v>
+      </c>
+      <c r="G71" s="58" t="n">
+        <v>45</v>
+      </c>
+      <c r="H71" s="58" t="n">
+        <v>49</v>
+      </c>
+      <c r="I71" s="56" t="n">
+        <v>14</v>
+      </c>
+      <c r="J71" s="56" t="n">
+        <v>38</v>
+      </c>
+      <c r="K71" s="58" t="n">
+        <v>66</v>
+      </c>
+      <c r="L71" s="56" t="n">
+        <v>27</v>
+      </c>
+      <c r="M71" s="56" t="n">
+        <v>31</v>
+      </c>
+      <c r="N71" s="56" t="n">
+        <v>19</v>
+      </c>
+      <c r="O71" s="56" t="n">
+        <v>42</v>
+      </c>
+      <c r="P71" s="58" t="n">
+        <v>132</v>
+      </c>
+      <c r="Q71" s="56" t="n">
+        <v>23</v>
+      </c>
+      <c r="R71" s="58" t="n">
+        <v>343</v>
+      </c>
+      <c r="S71" s="56" t="n">
+        <v>30</v>
+      </c>
+      <c r="T71" s="56" t="n">
+        <v>31</v>
+      </c>
+      <c r="U71" s="56" t="n">
+        <v>21</v>
+      </c>
+      <c r="V71" s="57" t="n">
+        <v>1121</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="37" t="inlineStr">
+        <is>
+          <t>Mirza Caroline</t>
+        </is>
+      </c>
+      <c r="B72" s="56" t="n">
+        <v>19</v>
+      </c>
+      <c r="C72" s="56" t="n">
+        <v>15</v>
+      </c>
+      <c r="D72" s="56" t="n">
+        <v>20</v>
+      </c>
+      <c r="E72" s="58" t="n">
+        <v>45</v>
+      </c>
+      <c r="F72" s="56" t="n">
+        <v>11</v>
+      </c>
+      <c r="G72" s="56" t="n">
+        <v>22</v>
+      </c>
+      <c r="H72" s="56" t="n">
+        <v>24</v>
+      </c>
+      <c r="I72" s="56" t="n">
+        <v>11</v>
+      </c>
+      <c r="J72" s="56" t="n">
+        <v>25</v>
+      </c>
+      <c r="K72" s="56" t="n">
+        <v>43</v>
+      </c>
+      <c r="L72" s="56" t="n">
+        <v>13</v>
+      </c>
+      <c r="M72" s="56" t="n">
+        <v>10</v>
+      </c>
+      <c r="N72" s="56" t="n">
+        <v>25</v>
+      </c>
+      <c r="O72" s="56" t="n">
+        <v>19</v>
+      </c>
+      <c r="P72" s="56" t="n">
+        <v>24</v>
+      </c>
+      <c r="Q72" s="56" t="n">
+        <v>21</v>
+      </c>
+      <c r="R72" s="56" t="n">
+        <v>17</v>
+      </c>
+      <c r="S72" s="56" t="n">
+        <v>26</v>
+      </c>
+      <c r="T72" s="56" t="n">
+        <v>18</v>
+      </c>
+      <c r="U72" s="56" t="n">
+        <v>14</v>
+      </c>
+      <c r="V72" s="57" t="n">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="37" t="inlineStr">
+        <is>
+          <t>wisye pangalila</t>
+        </is>
+      </c>
+      <c r="B73" s="56" t="n">
+        <v>18</v>
+      </c>
+      <c r="C73" s="56" t="n">
+        <v>17</v>
+      </c>
+      <c r="D73" s="56" t="n">
+        <v>23</v>
+      </c>
+      <c r="E73" s="56" t="n">
+        <v>29</v>
+      </c>
+      <c r="F73" s="56" t="n">
+        <v>12</v>
+      </c>
+      <c r="G73" s="56" t="n">
+        <v>9</v>
+      </c>
+      <c r="H73" s="56" t="n">
+        <v>16</v>
+      </c>
+      <c r="I73" s="56" t="n">
+        <v>27</v>
+      </c>
+      <c r="J73" s="56" t="n">
+        <v>15</v>
+      </c>
+      <c r="K73" s="56" t="n">
+        <v>41</v>
+      </c>
+      <c r="L73" s="56" t="n">
+        <v>37</v>
+      </c>
+      <c r="M73" s="56" t="n">
+        <v>28</v>
+      </c>
+      <c r="N73" s="56" t="n">
+        <v>14</v>
+      </c>
+      <c r="O73" s="56" t="n">
+        <v>14</v>
+      </c>
+      <c r="P73" s="58" t="n">
+        <v>47</v>
+      </c>
+      <c r="Q73" s="56" t="n">
+        <v>15</v>
+      </c>
+      <c r="R73" s="56" t="n">
+        <v>24</v>
+      </c>
+      <c r="S73" s="56" t="n">
+        <v>15</v>
+      </c>
+      <c r="T73" s="58" t="n">
+        <v>70</v>
+      </c>
+      <c r="U73" s="56" t="n">
+        <v>18</v>
+      </c>
+      <c r="V73" s="57" t="n">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="37" t="inlineStr">
+        <is>
+          <t>Yovita</t>
+        </is>
+      </c>
+      <c r="B74" s="58" t="n">
+        <v>47</v>
+      </c>
+      <c r="C74" s="56" t="n">
+        <v>26</v>
+      </c>
+      <c r="D74" s="56" t="n">
+        <v>28</v>
+      </c>
+      <c r="E74" s="58" t="n">
+        <v>62</v>
+      </c>
+      <c r="F74" s="56" t="n">
+        <v>20</v>
+      </c>
+      <c r="G74" s="56" t="n">
+        <v>24</v>
+      </c>
+      <c r="H74" s="56" t="n">
+        <v>26</v>
+      </c>
+      <c r="I74" s="58" t="n">
+        <v>57</v>
+      </c>
+      <c r="J74" s="56" t="n">
+        <v>32</v>
+      </c>
+      <c r="K74" s="58" t="n">
+        <v>100</v>
+      </c>
+      <c r="L74" s="56" t="n">
+        <v>39</v>
+      </c>
+      <c r="M74" s="56" t="n">
+        <v>42</v>
+      </c>
+      <c r="N74" s="56" t="n">
+        <v>32</v>
+      </c>
+      <c r="O74" s="56" t="n">
+        <v>30</v>
+      </c>
+      <c r="P74" s="58" t="n">
+        <v>69</v>
+      </c>
+      <c r="Q74" s="58" t="n">
+        <v>69</v>
+      </c>
+      <c r="R74" s="58" t="n">
+        <v>78</v>
+      </c>
+      <c r="S74" s="56" t="n">
+        <v>38</v>
+      </c>
+      <c r="T74" s="56" t="n">
+        <v>42</v>
+      </c>
+      <c r="U74" s="56" t="n">
+        <v>29</v>
+      </c>
+      <c r="V74" s="57" t="n">
+        <v>890</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="37" t="inlineStr">
+        <is>
+          <t>Netty Nusaly</t>
+        </is>
+      </c>
+      <c r="B75" s="56" t="n">
+        <v>12</v>
+      </c>
+      <c r="C75" s="56" t="n">
+        <v>9</v>
+      </c>
+      <c r="D75" s="56" t="n">
+        <v>23</v>
+      </c>
+      <c r="E75" s="56" t="n">
+        <v>21</v>
+      </c>
+      <c r="F75" s="56" t="n">
+        <v>16</v>
+      </c>
+      <c r="G75" s="56" t="n">
+        <v>29</v>
+      </c>
+      <c r="H75" s="56" t="n">
+        <v>41</v>
+      </c>
+      <c r="I75" s="56" t="n">
+        <v>22</v>
+      </c>
+      <c r="J75" s="56" t="n">
+        <v>15</v>
+      </c>
+      <c r="K75" s="56" t="n">
+        <v>31</v>
+      </c>
+      <c r="L75" s="56" t="n">
+        <v>37</v>
+      </c>
+      <c r="M75" s="56" t="n">
+        <v>33</v>
+      </c>
+      <c r="N75" s="56" t="n">
+        <v>24</v>
+      </c>
+      <c r="O75" s="56" t="n">
+        <v>35</v>
+      </c>
+      <c r="P75" s="56" t="n">
+        <v>26</v>
+      </c>
+      <c r="Q75" s="56" t="n">
+        <v>28</v>
+      </c>
+      <c r="R75" s="56" t="n">
+        <v>27</v>
+      </c>
+      <c r="S75" s="56" t="n">
+        <v>32</v>
+      </c>
+      <c r="T75" s="56" t="n">
+        <v>33</v>
+      </c>
+      <c r="U75" s="56" t="n">
+        <v>26</v>
+      </c>
+      <c r="V75" s="57" t="n">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="37" t="inlineStr">
+        <is>
+          <t>Ivo Emelia</t>
+        </is>
+      </c>
+      <c r="B76" s="56" t="n">
+        <v>43</v>
+      </c>
+      <c r="C76" s="56" t="n">
+        <v>28</v>
+      </c>
+      <c r="D76" s="56" t="n">
+        <v>13</v>
+      </c>
+      <c r="E76" s="56" t="n">
+        <v>26</v>
+      </c>
+      <c r="F76" s="56" t="n">
+        <v>7</v>
+      </c>
+      <c r="G76" s="56" t="n">
+        <v>19</v>
+      </c>
+      <c r="H76" s="56" t="n">
+        <v>25</v>
+      </c>
+      <c r="I76" s="56" t="n">
+        <v>16</v>
+      </c>
+      <c r="J76" s="56" t="n">
+        <v>13</v>
+      </c>
+      <c r="K76" s="56" t="n">
+        <v>31</v>
+      </c>
+      <c r="L76" s="56" t="n">
+        <v>14</v>
+      </c>
+      <c r="M76" s="56" t="n">
+        <v>39</v>
+      </c>
+      <c r="N76" s="56" t="n">
+        <v>19</v>
+      </c>
+      <c r="O76" s="56" t="n">
+        <v>35</v>
+      </c>
+      <c r="P76" s="58" t="n">
+        <v>57</v>
+      </c>
+      <c r="Q76" s="56" t="n">
+        <v>41</v>
+      </c>
+      <c r="R76" s="56" t="n">
+        <v>29</v>
+      </c>
+      <c r="S76" s="56" t="n">
+        <v>31</v>
+      </c>
+      <c r="T76" s="56" t="n">
+        <v>31</v>
+      </c>
+      <c r="U76" s="56" t="n">
+        <v>26</v>
+      </c>
+      <c r="V76" s="57" t="n">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="37" t="inlineStr">
+        <is>
+          <t>Marsia Sairina</t>
+        </is>
+      </c>
+      <c r="B77" s="56" t="n">
+        <v>21</v>
+      </c>
+      <c r="C77" s="56" t="n">
+        <v>20</v>
+      </c>
+      <c r="D77" s="56" t="n">
+        <v>22</v>
+      </c>
+      <c r="E77" s="56" t="n">
+        <v>28</v>
+      </c>
+      <c r="F77" s="56" t="n">
+        <v>16</v>
+      </c>
+      <c r="G77" s="56" t="n">
+        <v>23</v>
+      </c>
+      <c r="H77" s="56" t="n">
+        <v>31</v>
+      </c>
+      <c r="I77" s="56" t="n">
+        <v>22</v>
+      </c>
+      <c r="J77" s="56" t="n">
+        <v>21</v>
+      </c>
+      <c r="K77" s="58" t="n">
+        <v>56</v>
+      </c>
+      <c r="L77" s="56" t="n">
+        <v>38</v>
+      </c>
+      <c r="M77" s="56" t="n">
+        <v>28</v>
+      </c>
+      <c r="N77" s="56" t="n">
+        <v>33</v>
+      </c>
+      <c r="O77" s="56" t="n">
+        <v>28</v>
+      </c>
+      <c r="P77" s="56" t="n">
+        <v>26</v>
+      </c>
+      <c r="Q77" s="56" t="n">
+        <v>37</v>
+      </c>
+      <c r="R77" s="56" t="n">
+        <v>27</v>
+      </c>
+      <c r="S77" s="56" t="n">
+        <v>43</v>
+      </c>
+      <c r="T77" s="56" t="n">
+        <v>26</v>
+      </c>
+      <c r="U77" s="56" t="n">
+        <v>26</v>
+      </c>
+      <c r="V77" s="57" t="n">
+        <v>572</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="37" t="inlineStr">
+        <is>
+          <t>Silvya Runturambi</t>
+        </is>
+      </c>
+      <c r="B78" s="56" t="n">
+        <v>12</v>
+      </c>
+      <c r="C78" s="56" t="n">
+        <v>19</v>
+      </c>
+      <c r="D78" s="58" t="n">
+        <v>47</v>
+      </c>
+      <c r="E78" s="56" t="n">
+        <v>10</v>
+      </c>
+      <c r="F78" s="56" t="n">
+        <v>24</v>
+      </c>
+      <c r="G78" s="58" t="n">
+        <v>54</v>
+      </c>
+      <c r="H78" s="58" t="n">
+        <v>55</v>
+      </c>
+      <c r="I78" s="56" t="n">
+        <v>17</v>
+      </c>
+      <c r="J78" s="56" t="n">
+        <v>38</v>
+      </c>
+      <c r="K78" s="58" t="n">
+        <v>94</v>
+      </c>
+      <c r="L78" s="58" t="n">
+        <v>76</v>
+      </c>
+      <c r="M78" s="58" t="n">
+        <v>90</v>
+      </c>
+      <c r="N78" s="58" t="n">
+        <v>94</v>
+      </c>
+      <c r="O78" s="60" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P78" s="60" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q78" s="60" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="R78" s="60" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="S78" s="60" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T78" s="60" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U78" s="60" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="V78" s="57" t="n">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="37" t="inlineStr">
+        <is>
+          <t>Maria</t>
+        </is>
+      </c>
+      <c r="B79" s="56" t="n">
+        <v>8</v>
+      </c>
+      <c r="C79" s="56" t="n">
+        <v>11</v>
+      </c>
+      <c r="D79" s="56" t="n">
+        <v>24</v>
+      </c>
+      <c r="E79" s="60" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F79" s="60" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G79" s="60" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H79" s="60" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I79" s="60" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J79" s="60" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K79" s="60" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L79" s="60" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M79" s="60" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N79" s="60" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O79" s="60" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P79" s="60" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q79" s="60" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="R79" s="60" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="S79" s="60" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T79" s="60" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U79" s="60" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="V79" s="57" t="n">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="37" t="inlineStr">
+        <is>
+          <t>Ivonne runturambi</t>
+        </is>
+      </c>
+      <c r="B80" s="56" t="n">
+        <v>21</v>
+      </c>
+      <c r="C80" s="56" t="n">
+        <v>20</v>
+      </c>
+      <c r="D80" s="60" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E80" s="60" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F80" s="60" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G80" s="60" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H80" s="60" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I80" s="60" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J80" s="60" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K80" s="60" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L80" s="60" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M80" s="60" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N80" s="60" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O80" s="60" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P80" s="60" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q80" s="60" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="R80" s="60" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="S80" s="60" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T80" s="60" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U80" s="60" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="V80" s="57" t="n">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="37" t="inlineStr">
+        <is>
+          <t>Tintin tityn</t>
+        </is>
+      </c>
+      <c r="B81" s="60" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C81" s="60" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D81" s="60" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E81" s="60" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F81" s="60" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G81" s="60" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H81" s="60" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I81" s="60" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J81" s="60" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K81" s="60" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L81" s="60" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M81" s="60" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N81" s="60" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O81" s="60" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P81" s="60" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q81" s="60" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="R81" s="60" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="S81" s="60" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T81" s="60" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U81" s="60" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="V81" s="57" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="37" t="inlineStr">
+        <is>
+          <t>Yovita*</t>
+        </is>
+      </c>
+      <c r="B82" s="60" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C82" s="60" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D82" s="60" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E82" s="60" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F82" s="60" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G82" s="60" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H82" s="60" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I82" s="60" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J82" s="60" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K82" s="60" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L82" s="60" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M82" s="60" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N82" s="60" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O82" s="60" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P82" s="60" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q82" s="60" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="R82" s="60" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="S82" s="60" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T82" s="60" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U82" s="60" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="V82" s="57" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" ht="32" customHeight="1">
+      <c r="A84" s="15" t="inlineStr">
+        <is>
+          <t>Merah = 5 detik atau kurang (terlalu cepat untuk membaca soal) · hijau = wajar · kuning = 45 detik atau lebih · abu-abu = butir tidak dijawab. Total 218 sel waktu terisi dari 300 sel yang mungkin; sisanya adalah butir yang memang tidak dijawab pada sesi terputus.</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" ht="22" customHeight="1">
+      <c r="A86" s="3" t="inlineStr">
+        <is>
+          <t>C. DASAR FORENSIK PENGELUARAN SESI QA TESTER (VINCENT)</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" ht="34" customHeight="1">
+      <c r="A87" s="4" t="inlineStr">
+        <is>
+          <t>Butir</t>
+        </is>
+      </c>
+      <c r="B87" s="4" t="inlineStr">
+        <is>
+          <t>Waktu Vincent
+(detik)</t>
+        </is>
+      </c>
+      <c r="C87" s="4" t="inlineStr">
+        <is>
+          <t>Rata-rata
+15 peserta</t>
+        </is>
+      </c>
+      <c r="D87" s="4" t="inlineStr">
+        <is>
+          <t>Selisih</t>
+        </is>
+      </c>
+      <c r="E87" s="4" t="inlineStr">
+        <is>
+          <t>Penilaian</t>
+        </is>
+      </c>
+      <c r="F87" s="4" t="inlineStr"/>
+      <c r="G87" s="4" t="inlineStr"/>
+      <c r="H87" s="4" t="inlineStr"/>
+      <c r="I87" s="4" t="inlineStr"/>
+      <c r="J87" s="4" t="inlineStr"/>
+      <c r="K87" s="4" t="inlineStr"/>
+      <c r="L87" s="4" t="inlineStr"/>
+    </row>
+    <row r="88" ht="18" customHeight="1">
+      <c r="A88" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="B88" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="C88" s="6" t="n">
+        <v>24.2</v>
+      </c>
+      <c r="D88" s="6" t="n">
+        <v>-23.2</v>
+      </c>
+      <c r="E88" s="8" t="inlineStr">
+        <is>
+          <t>Satu detik — mustahil untuk membaca soal beserta empat opsinya.</t>
+        </is>
+      </c>
+      <c r="F88" s="9" t="n"/>
+      <c r="G88" s="9" t="n"/>
+      <c r="H88" s="9" t="n"/>
+      <c r="I88" s="9" t="n"/>
+      <c r="J88" s="9" t="n"/>
+      <c r="K88" s="9" t="n"/>
+      <c r="L88" s="10" t="n"/>
+    </row>
+    <row r="89" ht="18" customHeight="1">
+      <c r="A89" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="B89" s="17" t="n">
+        <v>64</v>
+      </c>
+      <c r="C89" s="6" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="D89" s="6" t="n">
+        <v>42.3</v>
+      </c>
+      <c r="E89" s="8" t="inlineStr">
+        <is>
+          <t>Wajar.</t>
+        </is>
+      </c>
+      <c r="F89" s="9" t="n"/>
+      <c r="G89" s="9" t="n"/>
+      <c r="H89" s="9" t="n"/>
+      <c r="I89" s="9" t="n"/>
+      <c r="J89" s="9" t="n"/>
+      <c r="K89" s="9" t="n"/>
+      <c r="L89" s="10" t="n"/>
+    </row>
+    <row r="90" ht="18" customHeight="1">
+      <c r="A90" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="B90" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="C90" s="6" t="n">
+        <v>27.3</v>
+      </c>
+      <c r="D90" s="6" t="n">
+        <v>-26.3</v>
+      </c>
+      <c r="E90" s="8" t="inlineStr">
+        <is>
+          <t>Satu detik — mustahil untuk membaca soal beserta empat opsinya.</t>
+        </is>
+      </c>
+      <c r="F90" s="9" t="n"/>
+      <c r="G90" s="9" t="n"/>
+      <c r="H90" s="9" t="n"/>
+      <c r="I90" s="9" t="n"/>
+      <c r="J90" s="9" t="n"/>
+      <c r="K90" s="9" t="n"/>
+      <c r="L90" s="10" t="n"/>
+    </row>
+    <row r="91" ht="18" customHeight="1">
+      <c r="A91" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="B91" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="C91" s="6" t="n">
+        <v>33.5</v>
+      </c>
+      <c r="D91" s="6" t="n">
+        <v>-32.5</v>
+      </c>
+      <c r="E91" s="8" t="inlineStr">
+        <is>
+          <t>Satu detik — mustahil untuk membaca soal beserta empat opsinya.</t>
+        </is>
+      </c>
+      <c r="F91" s="9" t="n"/>
+      <c r="G91" s="9" t="n"/>
+      <c r="H91" s="9" t="n"/>
+      <c r="I91" s="9" t="n"/>
+      <c r="J91" s="9" t="n"/>
+      <c r="K91" s="9" t="n"/>
+      <c r="L91" s="10" t="n"/>
+    </row>
+    <row r="92" ht="18" customHeight="1">
+      <c r="A92" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="B92" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="C92" s="6" t="n">
+        <v>15.4</v>
+      </c>
+      <c r="D92" s="6" t="n">
+        <v>-14.4</v>
+      </c>
+      <c r="E92" s="8" t="inlineStr">
+        <is>
+          <t>Satu detik — mustahil untuk membaca soal beserta empat opsinya.</t>
+        </is>
+      </c>
+      <c r="F92" s="9" t="n"/>
+      <c r="G92" s="9" t="n"/>
+      <c r="H92" s="9" t="n"/>
+      <c r="I92" s="9" t="n"/>
+      <c r="J92" s="9" t="n"/>
+      <c r="K92" s="9" t="n"/>
+      <c r="L92" s="10" t="n"/>
+    </row>
+    <row r="93" ht="18" customHeight="1">
+      <c r="A93" s="24" t="n">
+        <v>6</v>
+      </c>
+      <c r="B93" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="C93" s="6" t="n">
+        <v>30.2</v>
+      </c>
+      <c r="D93" s="6" t="n">
+        <v>-29.2</v>
+      </c>
+      <c r="E93" s="8" t="inlineStr">
+        <is>
+          <t>Satu detik — mustahil untuk membaca soal beserta empat opsinya.</t>
+        </is>
+      </c>
+      <c r="F93" s="9" t="n"/>
+      <c r="G93" s="9" t="n"/>
+      <c r="H93" s="9" t="n"/>
+      <c r="I93" s="9" t="n"/>
+      <c r="J93" s="9" t="n"/>
+      <c r="K93" s="9" t="n"/>
+      <c r="L93" s="10" t="n"/>
+    </row>
+    <row r="94" ht="18" customHeight="1">
+      <c r="A94" s="24" t="n">
+        <v>7</v>
+      </c>
+      <c r="B94" s="28" t="n">
+        <v>3</v>
+      </c>
+      <c r="C94" s="6" t="n">
+        <v>33.7</v>
+      </c>
+      <c r="D94" s="6" t="n">
+        <v>-30.7</v>
+      </c>
+      <c r="E94" s="8" t="inlineStr">
+        <is>
+          <t>Di bawah 5 detik; masih terlalu cepat untuk dibaca.</t>
+        </is>
+      </c>
+      <c r="F94" s="9" t="n"/>
+      <c r="G94" s="9" t="n"/>
+      <c r="H94" s="9" t="n"/>
+      <c r="I94" s="9" t="n"/>
+      <c r="J94" s="9" t="n"/>
+      <c r="K94" s="9" t="n"/>
+      <c r="L94" s="10" t="n"/>
+    </row>
+    <row r="95" ht="18" customHeight="1">
+      <c r="A95" s="24" t="n">
+        <v>8</v>
+      </c>
+      <c r="B95" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="C95" s="6" t="n">
+        <v>26</v>
+      </c>
+      <c r="D95" s="6" t="n">
+        <v>-25</v>
+      </c>
+      <c r="E95" s="8" t="inlineStr">
+        <is>
+          <t>Satu detik — mustahil untuk membaca soal beserta empat opsinya.</t>
+        </is>
+      </c>
+      <c r="F95" s="9" t="n"/>
+      <c r="G95" s="9" t="n"/>
+      <c r="H95" s="9" t="n"/>
+      <c r="I95" s="9" t="n"/>
+      <c r="J95" s="9" t="n"/>
+      <c r="K95" s="9" t="n"/>
+      <c r="L95" s="10" t="n"/>
+    </row>
+    <row r="96" ht="18" customHeight="1">
+      <c r="A96" s="24" t="n">
+        <v>9</v>
+      </c>
+      <c r="B96" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="C96" s="6" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="D96" s="6" t="n">
+        <v>-23.5</v>
+      </c>
+      <c r="E96" s="8" t="inlineStr">
+        <is>
+          <t>Satu detik — mustahil untuk membaca soal beserta empat opsinya.</t>
+        </is>
+      </c>
+      <c r="F96" s="9" t="n"/>
+      <c r="G96" s="9" t="n"/>
+      <c r="H96" s="9" t="n"/>
+      <c r="I96" s="9" t="n"/>
+      <c r="J96" s="9" t="n"/>
+      <c r="K96" s="9" t="n"/>
+      <c r="L96" s="10" t="n"/>
+    </row>
+    <row r="97" ht="18" customHeight="1">
+      <c r="A97" s="24" t="n">
+        <v>10</v>
+      </c>
+      <c r="B97" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="C97" s="6" t="n">
+        <v>52.2</v>
+      </c>
+      <c r="D97" s="6" t="n">
+        <v>-51.2</v>
+      </c>
+      <c r="E97" s="8" t="inlineStr">
+        <is>
+          <t>Satu detik — mustahil untuk membaca soal beserta empat opsinya.</t>
+        </is>
+      </c>
+      <c r="F97" s="9" t="n"/>
+      <c r="G97" s="9" t="n"/>
+      <c r="H97" s="9" t="n"/>
+      <c r="I97" s="9" t="n"/>
+      <c r="J97" s="9" t="n"/>
+      <c r="K97" s="9" t="n"/>
+      <c r="L97" s="10" t="n"/>
+    </row>
+    <row r="98" ht="18" customHeight="1">
+      <c r="A98" s="24" t="n">
+        <v>11</v>
+      </c>
+      <c r="B98" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="C98" s="6" t="n">
+        <v>31.8</v>
+      </c>
+      <c r="D98" s="6" t="n">
+        <v>-30.8</v>
+      </c>
+      <c r="E98" s="8" t="inlineStr">
+        <is>
+          <t>Satu detik — mustahil untuk membaca soal beserta empat opsinya.</t>
+        </is>
+      </c>
+      <c r="F98" s="9" t="n"/>
+      <c r="G98" s="9" t="n"/>
+      <c r="H98" s="9" t="n"/>
+      <c r="I98" s="9" t="n"/>
+      <c r="J98" s="9" t="n"/>
+      <c r="K98" s="9" t="n"/>
+      <c r="L98" s="10" t="n"/>
+    </row>
+    <row r="99" ht="18" customHeight="1">
+      <c r="A99" s="24" t="n">
+        <v>12</v>
+      </c>
+      <c r="B99" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="C99" s="6" t="n">
+        <v>35.6</v>
+      </c>
+      <c r="D99" s="6" t="n">
+        <v>-34.6</v>
+      </c>
+      <c r="E99" s="8" t="inlineStr">
+        <is>
+          <t>Satu detik — mustahil untuk membaca soal beserta empat opsinya.</t>
+        </is>
+      </c>
+      <c r="F99" s="9" t="n"/>
+      <c r="G99" s="9" t="n"/>
+      <c r="H99" s="9" t="n"/>
+      <c r="I99" s="9" t="n"/>
+      <c r="J99" s="9" t="n"/>
+      <c r="K99" s="9" t="n"/>
+      <c r="L99" s="10" t="n"/>
+    </row>
+    <row r="100" ht="18" customHeight="1">
+      <c r="A100" s="24" t="n">
+        <v>13</v>
+      </c>
+      <c r="B100" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="C100" s="6" t="n">
+        <v>30.5</v>
+      </c>
+      <c r="D100" s="6" t="n">
+        <v>-29.5</v>
+      </c>
+      <c r="E100" s="8" t="inlineStr">
+        <is>
+          <t>Satu detik — mustahil untuk membaca soal beserta empat opsinya.</t>
+        </is>
+      </c>
+      <c r="F100" s="9" t="n"/>
+      <c r="G100" s="9" t="n"/>
+      <c r="H100" s="9" t="n"/>
+      <c r="I100" s="9" t="n"/>
+      <c r="J100" s="9" t="n"/>
+      <c r="K100" s="9" t="n"/>
+      <c r="L100" s="10" t="n"/>
+    </row>
+    <row r="101" ht="18" customHeight="1">
+      <c r="A101" s="24" t="n">
+        <v>14</v>
+      </c>
+      <c r="B101" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="C101" s="6" t="n">
+        <v>25.4</v>
+      </c>
+      <c r="D101" s="6" t="n">
+        <v>-24.4</v>
+      </c>
+      <c r="E101" s="8" t="inlineStr">
+        <is>
+          <t>Satu detik — mustahil untuk membaca soal beserta empat opsinya.</t>
+        </is>
+      </c>
+      <c r="F101" s="9" t="n"/>
+      <c r="G101" s="9" t="n"/>
+      <c r="H101" s="9" t="n"/>
+      <c r="I101" s="9" t="n"/>
+      <c r="J101" s="9" t="n"/>
+      <c r="K101" s="9" t="n"/>
+      <c r="L101" s="10" t="n"/>
+    </row>
+    <row r="102" ht="18" customHeight="1">
+      <c r="A102" s="24" t="n">
+        <v>15</v>
+      </c>
+      <c r="B102" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="C102" s="6" t="n">
+        <v>45.6</v>
+      </c>
+      <c r="D102" s="6" t="n">
+        <v>-44.6</v>
+      </c>
+      <c r="E102" s="8" t="inlineStr">
+        <is>
+          <t>Satu detik — mustahil untuk membaca soal beserta empat opsinya.</t>
+        </is>
+      </c>
+      <c r="F102" s="9" t="n"/>
+      <c r="G102" s="9" t="n"/>
+      <c r="H102" s="9" t="n"/>
+      <c r="I102" s="9" t="n"/>
+      <c r="J102" s="9" t="n"/>
+      <c r="K102" s="9" t="n"/>
+      <c r="L102" s="10" t="n"/>
+    </row>
+    <row r="103" ht="18" customHeight="1">
+      <c r="A103" s="24" t="n">
+        <v>16</v>
+      </c>
+      <c r="B103" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="C103" s="6" t="n">
+        <v>31.4</v>
+      </c>
+      <c r="D103" s="6" t="n">
+        <v>-30.4</v>
+      </c>
+      <c r="E103" s="8" t="inlineStr">
+        <is>
+          <t>Satu detik — mustahil untuk membaca soal beserta empat opsinya.</t>
+        </is>
+      </c>
+      <c r="F103" s="9" t="n"/>
+      <c r="G103" s="9" t="n"/>
+      <c r="H103" s="9" t="n"/>
+      <c r="I103" s="9" t="n"/>
+      <c r="J103" s="9" t="n"/>
+      <c r="K103" s="9" t="n"/>
+      <c r="L103" s="10" t="n"/>
+    </row>
+    <row r="104" ht="18" customHeight="1">
+      <c r="A104" s="24" t="n">
+        <v>17</v>
+      </c>
+      <c r="B104" s="28" t="n">
+        <v>2</v>
+      </c>
+      <c r="C104" s="6" t="n">
+        <v>59.8</v>
+      </c>
+      <c r="D104" s="6" t="n">
+        <v>-57.8</v>
+      </c>
+      <c r="E104" s="8" t="inlineStr">
+        <is>
+          <t>Di bawah 5 detik; masih terlalu cepat untuk dibaca.</t>
+        </is>
+      </c>
+      <c r="F104" s="9" t="n"/>
+      <c r="G104" s="9" t="n"/>
+      <c r="H104" s="9" t="n"/>
+      <c r="I104" s="9" t="n"/>
+      <c r="J104" s="9" t="n"/>
+      <c r="K104" s="9" t="n"/>
+      <c r="L104" s="10" t="n"/>
+    </row>
+    <row r="105" ht="18" customHeight="1">
+      <c r="A105" s="24" t="n">
+        <v>18</v>
+      </c>
+      <c r="B105" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="C105" s="6" t="n">
+        <v>30.8</v>
+      </c>
+      <c r="D105" s="6" t="n">
+        <v>-29.8</v>
+      </c>
+      <c r="E105" s="8" t="inlineStr">
+        <is>
+          <t>Satu detik — mustahil untuk membaca soal beserta empat opsinya.</t>
+        </is>
+      </c>
+      <c r="F105" s="9" t="n"/>
+      <c r="G105" s="9" t="n"/>
+      <c r="H105" s="9" t="n"/>
+      <c r="I105" s="9" t="n"/>
+      <c r="J105" s="9" t="n"/>
+      <c r="K105" s="9" t="n"/>
+      <c r="L105" s="10" t="n"/>
+    </row>
+    <row r="106" ht="18" customHeight="1">
+      <c r="A106" s="24" t="n">
+        <v>19</v>
+      </c>
+      <c r="B106" s="28" t="n">
+        <v>2</v>
+      </c>
+      <c r="C106" s="6" t="n">
+        <v>33.9</v>
+      </c>
+      <c r="D106" s="6" t="n">
+        <v>-31.9</v>
+      </c>
+      <c r="E106" s="8" t="inlineStr">
+        <is>
+          <t>Di bawah 5 detik; masih terlalu cepat untuk dibaca.</t>
+        </is>
+      </c>
+      <c r="F106" s="9" t="n"/>
+      <c r="G106" s="9" t="n"/>
+      <c r="H106" s="9" t="n"/>
+      <c r="I106" s="9" t="n"/>
+      <c r="J106" s="9" t="n"/>
+      <c r="K106" s="9" t="n"/>
+      <c r="L106" s="10" t="n"/>
+    </row>
+    <row r="107" ht="18" customHeight="1">
+      <c r="A107" s="24" t="n">
+        <v>20</v>
+      </c>
+      <c r="B107" s="28" t="n">
+        <v>2</v>
+      </c>
+      <c r="C107" s="6" t="n">
+        <v>25.9</v>
+      </c>
+      <c r="D107" s="6" t="n">
+        <v>-23.9</v>
+      </c>
+      <c r="E107" s="8" t="inlineStr">
+        <is>
+          <t>Di bawah 5 detik; masih terlalu cepat untuk dibaca.</t>
+        </is>
+      </c>
+      <c r="F107" s="9" t="n"/>
+      <c r="G107" s="9" t="n"/>
+      <c r="H107" s="9" t="n"/>
+      <c r="I107" s="9" t="n"/>
+      <c r="J107" s="9" t="n"/>
+      <c r="K107" s="9" t="n"/>
+      <c r="L107" s="10" t="n"/>
+    </row>
+    <row r="109" ht="40" customHeight="1">
+      <c r="A109" s="15" t="inlineStr">
+        <is>
+          <t>Dari 20 butir, 15 dijawab Vincent dalam waktu persis 1 detik. Membaca satu butir post-test beserta keempat opsinya membutuhkan sekurang-kurangnya beberapa detik; rata-rata 15 peserta lain adalah 31.7 detik per butir. Pola satu detik berulang adalah tanda penelusuran otomatis atau klik cepat untuk menguji jalannya kuis, bukan pengerjaan soal.</t>
+        </is>
+      </c>
+    </row>
+    <row r="110" ht="40" customHeight="1">
+      <c r="A110" s="15" t="inlineStr">
+        <is>
+          <t>Waktu total sesi Vincent 1 menit 28 detik untuk 20 butir, sementara rata-rata sesi tuntas peserta lain adalah 10 menit 18 detik.</t>
+        </is>
+      </c>
+    </row>
+    <row r="111" ht="40" customHeight="1">
+      <c r="A111" s="15" t="inlineStr">
+        <is>
+          <t>Vincent juga tidak muncul pada daftar 37 peserta pre-test, sehingga tidak dapat masuk analisis berpasangan dalam keadaan apa pun.</t>
+        </is>
+      </c>
+    </row>
+    <row r="112" ht="40" customHeight="1">
+      <c r="A112" s="15" t="inlineStr">
+        <is>
+          <t>Atas ketiga dasar itu sesi ini dikeluarkan dari seluruh perhitungan. Dampaknya terhadap angka agregat kecil dan dilaporkan penuh pada sheet 09 Metodologi bagian C: rata-rata turun 0,19 butir, akurasi turun 0,96 poin persen.</t>
+        </is>
+      </c>
+    </row>
+    <row r="114" ht="22" customHeight="1">
+      <c r="A114" s="3" t="inlineStr">
+        <is>
+          <t>D. TEMUAN</t>
+        </is>
+      </c>
+    </row>
+    <row r="115" ht="40" customHeight="1">
+      <c r="A115" s="15" t="inlineStr">
+        <is>
+          <t>Rata-rata waktu per butir 31.7 detik, dengan rentang 5 sampai 343 detik. Sebagai pembanding, pre-test yang dijalankan live mencatat rata-rata 17-18 detik per butir.</t>
+        </is>
+      </c>
+    </row>
+    <row r="116" ht="40" customHeight="1">
+      <c r="A116" s="15" t="inlineStr">
+        <is>
+          <t>Jawaban benar rata-rata memakan 30.5 detik, jawaban salah 34.2 detik — selisih 3.7 detik. Peserta yang menjawab salah justru berpikir sedikit lebih lama, sehingga tidak ada bukti kesalahan disebabkan oleh terburu-buru.</t>
+        </is>
+      </c>
+    </row>
+    <row r="117" ht="40" customHeight="1">
+      <c r="A117" s="15" t="inlineStr">
+        <is>
+          <t>Meskipun kuis dibuka tiga hari, tidak ada sesi tuntas yang memakai waktu ekstrem: yang tercepat 4 menit 28 detik dan yang terlama 18 menit 41 detik. Artinya peserta mengerjakan dalam satu duduk, bukan mencicil selama tiga hari.</t>
+        </is>
+      </c>
+    </row>
+    <row r="118" ht="40" customHeight="1">
+      <c r="A118" s="15" t="inlineStr">
+        <is>
+          <t>Perlu dicatat bahwa waktu tercatat hanya menghitung durasi butir terbuka di layar. Dalam mode take-home, peserta dapat membuka materi pada perangkat lain tanpa terekam sebagai waktu pengerjaan. Karena itu waktu yang wajar pada tabel ini bukan bukti bahwa pengerjaan dilakukan tanpa membuka materi.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="35">
+    <mergeCell ref="E96:L96"/>
+    <mergeCell ref="E106:L106"/>
+    <mergeCell ref="A84:L84"/>
+    <mergeCell ref="A66:L66"/>
+    <mergeCell ref="A118:L118"/>
+    <mergeCell ref="E98:L98"/>
+    <mergeCell ref="E92:L92"/>
+    <mergeCell ref="A2:L2"/>
+    <mergeCell ref="A86:L86"/>
+    <mergeCell ref="E88:L88"/>
+    <mergeCell ref="E107:L107"/>
+    <mergeCell ref="A116:L116"/>
+    <mergeCell ref="E94:L94"/>
+    <mergeCell ref="E103:L103"/>
+    <mergeCell ref="A109:L109"/>
+    <mergeCell ref="A4:L4"/>
+    <mergeCell ref="A112:L112"/>
+    <mergeCell ref="E90:L90"/>
+    <mergeCell ref="E105:L105"/>
+    <mergeCell ref="E99:L99"/>
+    <mergeCell ref="A115:L115"/>
+    <mergeCell ref="E95:L95"/>
+    <mergeCell ref="A111:L111"/>
+    <mergeCell ref="A117:L117"/>
+    <mergeCell ref="E89:L89"/>
+    <mergeCell ref="E104:L104"/>
+    <mergeCell ref="A114:L114"/>
+    <mergeCell ref="E101:L101"/>
+    <mergeCell ref="E100:L100"/>
+    <mergeCell ref="E91:L91"/>
+    <mergeCell ref="A1:L1"/>
+    <mergeCell ref="E97:L97"/>
+    <mergeCell ref="A110:L110"/>
+    <mergeCell ref="E102:L102"/>
+    <mergeCell ref="E93:L93"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 

--- a/LAPORAN_POSTTEST_DAN_PERBANDINGAN_CANVA.xlsx
+++ b/LAPORAN_POSTTEST_DAN_PERBANDINGAN_CANVA.xlsx
@@ -208,7 +208,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="61">
+  <cellXfs count="60">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -299,9 +299,6 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -4025,17 +4022,17 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="51" t="inlineStr">
+      <c r="A5" s="50" t="inlineStr">
         <is>
           <t>Peserta</t>
         </is>
       </c>
-      <c r="B5" s="51" t="inlineStr">
+      <c r="B5" s="50" t="inlineStr">
         <is>
           <t>Pre-test</t>
         </is>
       </c>
-      <c r="C5" s="51" t="inlineStr">
+      <c r="C5" s="50" t="inlineStr">
         <is>
           <t>Post-test</t>
         </is>
@@ -4047,10 +4044,10 @@
           <t>Agnes Nurak</t>
         </is>
       </c>
-      <c r="B6" s="52" t="n">
+      <c r="B6" s="51" t="n">
         <v>6</v>
       </c>
-      <c r="C6" s="52" t="n">
+      <c r="C6" s="51" t="n">
         <v>20</v>
       </c>
     </row>
@@ -4060,10 +4057,10 @@
           <t>wisye pangalila</t>
         </is>
       </c>
-      <c r="B7" s="52" t="n">
+      <c r="B7" s="51" t="n">
         <v>8</v>
       </c>
-      <c r="C7" s="52" t="n">
+      <c r="C7" s="51" t="n">
         <v>14</v>
       </c>
     </row>
@@ -4073,10 +4070,10 @@
           <t>Mirza Caroline</t>
         </is>
       </c>
-      <c r="B8" s="52" t="n">
+      <c r="B8" s="51" t="n">
         <v>9</v>
       </c>
-      <c r="C8" s="52" t="n">
+      <c r="C8" s="51" t="n">
         <v>14</v>
       </c>
     </row>
@@ -4086,10 +4083,10 @@
           <t>Ivo Emelia</t>
         </is>
       </c>
-      <c r="B9" s="52" t="n">
+      <c r="B9" s="51" t="n">
         <v>6</v>
       </c>
-      <c r="C9" s="52" t="n">
+      <c r="C9" s="51" t="n">
         <v>10</v>
       </c>
     </row>
@@ -4099,10 +4096,10 @@
           <t>LESLY MARCHRITH NUSALY</t>
         </is>
       </c>
-      <c r="B10" s="52" t="n">
+      <c r="B10" s="51" t="n">
         <v>12</v>
       </c>
-      <c r="C10" s="52" t="n">
+      <c r="C10" s="51" t="n">
         <v>15</v>
       </c>
     </row>
@@ -4112,10 +4109,10 @@
           <t>Gerarda Ina</t>
         </is>
       </c>
-      <c r="B11" s="52" t="n">
+      <c r="B11" s="51" t="n">
         <v>12</v>
       </c>
-      <c r="C11" s="52" t="n">
+      <c r="C11" s="51" t="n">
         <v>15</v>
       </c>
     </row>
@@ -4125,10 +4122,10 @@
           <t>Yovita</t>
         </is>
       </c>
-      <c r="B12" s="52" t="n">
+      <c r="B12" s="51" t="n">
         <v>10</v>
       </c>
-      <c r="C12" s="52" t="n">
+      <c r="C12" s="51" t="n">
         <v>13</v>
       </c>
     </row>
@@ -4138,10 +4135,10 @@
           <t>Marsia Sairina</t>
         </is>
       </c>
-      <c r="B13" s="52" t="n">
+      <c r="B13" s="51" t="n">
         <v>6</v>
       </c>
-      <c r="C13" s="52" t="n">
+      <c r="C13" s="51" t="n">
         <v>8</v>
       </c>
     </row>
@@ -4153,17 +4150,17 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="51" t="inlineStr">
+      <c r="A35" s="50" t="inlineStr">
         <is>
           <t>Konstruk</t>
         </is>
       </c>
-      <c r="B35" s="51" t="inlineStr">
+      <c r="B35" s="50" t="inlineStr">
         <is>
           <t>p pre</t>
         </is>
       </c>
-      <c r="C35" s="51" t="inlineStr">
+      <c r="C35" s="50" t="inlineStr">
         <is>
           <t>p post</t>
         </is>
@@ -4175,10 +4172,10 @@
           <t>Ukuran kanvas per platform</t>
         </is>
       </c>
-      <c r="B36" s="52" t="n">
+      <c r="B36" s="51" t="n">
         <v>0.19</v>
       </c>
-      <c r="C36" s="52" t="n">
+      <c r="C36" s="51" t="n">
         <v>0.53</v>
       </c>
     </row>
@@ -4188,10 +4185,10 @@
           <t>Tujuan pelatihan</t>
         </is>
       </c>
-      <c r="B37" s="52" t="n">
+      <c r="B37" s="51" t="n">
         <v>0.32</v>
       </c>
-      <c r="C37" s="52" t="n">
+      <c r="C37" s="51" t="n">
         <v>0.67</v>
       </c>
     </row>
@@ -4201,10 +4198,10 @@
           <t>Asal usul Canva (Fusion Books)</t>
         </is>
       </c>
-      <c r="B38" s="52" t="n">
+      <c r="B38" s="51" t="n">
         <v>0.14</v>
       </c>
-      <c r="C38" s="52" t="n">
+      <c r="C38" s="51" t="n">
         <v>0.47</v>
       </c>
     </row>
@@ -4214,10 +4211,10 @@
           <t>Format ekspor PNG untuk gambar</t>
         </is>
       </c>
-      <c r="B39" s="52" t="n">
+      <c r="B39" s="51" t="n">
         <v>0.22</v>
       </c>
-      <c r="C39" s="52" t="n">
+      <c r="C39" s="51" t="n">
         <v>0.53</v>
       </c>
     </row>
@@ -4227,10 +4224,10 @@
           <t>Pernyataan benar tentang Canva</t>
         </is>
       </c>
-      <c r="B40" s="52" t="n">
+      <c r="B40" s="51" t="n">
         <v>0.32</v>
       </c>
-      <c r="C40" s="52" t="n">
+      <c r="C40" s="51" t="n">
         <v>0.6</v>
       </c>
     </row>
@@ -4240,10 +4237,10 @@
           <t>Kolaborasi tim real-time</t>
         </is>
       </c>
-      <c r="B41" s="52" t="n">
+      <c r="B41" s="51" t="n">
         <v>0.43</v>
       </c>
-      <c r="C41" s="52" t="n">
+      <c r="C41" s="51" t="n">
         <v>0.67</v>
       </c>
     </row>
@@ -4253,10 +4250,10 @@
           <t>Hierarki visual — pernyataan yang berten</t>
         </is>
       </c>
-      <c r="B42" s="52" t="n">
+      <c r="B42" s="51" t="n">
         <v>0.43</v>
       </c>
-      <c r="C42" s="52" t="n">
+      <c r="C42" s="51" t="n">
         <v>0.6</v>
       </c>
     </row>
@@ -4266,10 +4263,10 @@
           <t>Batas jumlah font dan warna</t>
         </is>
       </c>
-      <c r="B43" s="52" t="n">
+      <c r="B43" s="51" t="n">
         <v>0.43</v>
       </c>
-      <c r="C43" s="52" t="n">
+      <c r="C43" s="51" t="n">
         <v>0.6</v>
       </c>
     </row>
@@ -4279,10 +4276,10 @@
           <t>Menu panel kiri editor</t>
         </is>
       </c>
-      <c r="B44" s="52" t="n">
+      <c r="B44" s="51" t="n">
         <v>0.22</v>
       </c>
-      <c r="C44" s="52" t="n">
+      <c r="C44" s="51" t="n">
         <v>0.33</v>
       </c>
     </row>
@@ -4292,10 +4289,10 @@
           <t>Empat nilai berkarya dengan hati</t>
         </is>
       </c>
-      <c r="B45" s="52" t="n">
+      <c r="B45" s="51" t="n">
         <v>0.35</v>
       </c>
-      <c r="C45" s="52" t="n">
+      <c r="C45" s="51" t="n">
         <v>0.47</v>
       </c>
     </row>
@@ -4305,10 +4302,10 @@
           <t>Teori warna (skema warna)</t>
         </is>
       </c>
-      <c r="B46" s="52" t="n">
+      <c r="B46" s="51" t="n">
         <v>0.3</v>
       </c>
-      <c r="C46" s="52" t="n">
+      <c r="C46" s="51" t="n">
         <v>0.4</v>
       </c>
     </row>
@@ -4318,10 +4315,10 @@
           <t>Paket harga Canva</t>
         </is>
       </c>
-      <c r="B47" s="52" t="n">
+      <c r="B47" s="51" t="n">
         <v>0.46</v>
       </c>
-      <c r="C47" s="52" t="n">
+      <c r="C47" s="51" t="n">
         <v>0.47</v>
       </c>
     </row>
@@ -4331,10 +4328,10 @@
           <t>Urutan langkah prosedural di editor</t>
         </is>
       </c>
-      <c r="B48" s="52" t="n">
+      <c r="B48" s="51" t="n">
         <v>0.46</v>
       </c>
-      <c r="C48" s="52" t="n">
+      <c r="C48" s="51" t="n">
         <v>0.33</v>
       </c>
     </row>
@@ -4344,10 +4341,10 @@
           <t>Komentar pada elemen desain</t>
         </is>
       </c>
-      <c r="B49" s="52" t="n">
+      <c r="B49" s="51" t="n">
         <v>0.43</v>
       </c>
-      <c r="C49" s="52" t="n">
+      <c r="C49" s="51" t="n">
         <v>0.13</v>
       </c>
     </row>
@@ -4359,12 +4356,12 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="51" t="inlineStr">
+      <c r="A79" s="50" t="inlineStr">
         <is>
           <t>Konstruk</t>
         </is>
       </c>
-      <c r="B79" s="51" t="inlineStr">
+      <c r="B79" s="50" t="inlineStr">
         <is>
           <t>Perubahan p</t>
         </is>
@@ -4376,7 +4373,7 @@
           <t>Komentar pada elemen desain</t>
         </is>
       </c>
-      <c r="B80" s="52" t="n">
+      <c r="B80" s="51" t="n">
         <v>-0.3</v>
       </c>
     </row>
@@ -4386,7 +4383,7 @@
           <t>Urutan langkah prosedural di editor</t>
         </is>
       </c>
-      <c r="B81" s="52" t="n">
+      <c r="B81" s="51" t="n">
         <v>-0.13</v>
       </c>
     </row>
@@ -4396,7 +4393,7 @@
           <t>Paket harga Canva</t>
         </is>
       </c>
-      <c r="B82" s="52" t="n">
+      <c r="B82" s="51" t="n">
         <v>0.01</v>
       </c>
     </row>
@@ -4406,7 +4403,7 @@
           <t>Teori warna (skema warna)</t>
         </is>
       </c>
-      <c r="B83" s="52" t="n">
+      <c r="B83" s="51" t="n">
         <v>0.1</v>
       </c>
     </row>
@@ -4416,7 +4413,7 @@
           <t>Empat nilai berkarya dengan hati</t>
         </is>
       </c>
-      <c r="B84" s="52" t="n">
+      <c r="B84" s="51" t="n">
         <v>0.12</v>
       </c>
     </row>
@@ -4426,7 +4423,7 @@
           <t>Menu panel kiri editor</t>
         </is>
       </c>
-      <c r="B85" s="52" t="n">
+      <c r="B85" s="51" t="n">
         <v>0.12</v>
       </c>
     </row>
@@ -4436,7 +4433,7 @@
           <t>Hierarki visual — pernyataan yang berten</t>
         </is>
       </c>
-      <c r="B86" s="52" t="n">
+      <c r="B86" s="51" t="n">
         <v>0.17</v>
       </c>
     </row>
@@ -4446,7 +4443,7 @@
           <t>Batas jumlah font dan warna</t>
         </is>
       </c>
-      <c r="B87" s="52" t="n">
+      <c r="B87" s="51" t="n">
         <v>0.17</v>
       </c>
     </row>
@@ -4456,7 +4453,7 @@
           <t>Kolaborasi tim real-time</t>
         </is>
       </c>
-      <c r="B88" s="52" t="n">
+      <c r="B88" s="51" t="n">
         <v>0.23</v>
       </c>
     </row>
@@ -4466,7 +4463,7 @@
           <t>Pernyataan benar tentang Canva</t>
         </is>
       </c>
-      <c r="B89" s="52" t="n">
+      <c r="B89" s="51" t="n">
         <v>0.28</v>
       </c>
     </row>
@@ -4476,7 +4473,7 @@
           <t>Format ekspor PNG untuk gambar</t>
         </is>
       </c>
-      <c r="B90" s="52" t="n">
+      <c r="B90" s="51" t="n">
         <v>0.32</v>
       </c>
     </row>
@@ -4486,7 +4483,7 @@
           <t>Asal usul Canva (Fusion Books)</t>
         </is>
       </c>
-      <c r="B91" s="52" t="n">
+      <c r="B91" s="51" t="n">
         <v>0.33</v>
       </c>
     </row>
@@ -4496,7 +4493,7 @@
           <t>Tujuan pelatihan</t>
         </is>
       </c>
-      <c r="B92" s="52" t="n">
+      <c r="B92" s="51" t="n">
         <v>0.34</v>
       </c>
     </row>
@@ -4506,7 +4503,7 @@
           <t>Ukuran kanvas per platform</t>
         </is>
       </c>
-      <c r="B93" s="52" t="n">
+      <c r="B93" s="51" t="n">
         <v>0.34</v>
       </c>
     </row>
@@ -4518,22 +4515,22 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="51" t="inlineStr">
+      <c r="A119" s="50" t="inlineStr">
         <is>
           <t>Butir</t>
         </is>
       </c>
-      <c r="B119" s="51" t="inlineStr">
+      <c r="B119" s="50" t="inlineStr">
         <is>
           <t>p</t>
         </is>
       </c>
-      <c r="C119" s="51" t="inlineStr">
+      <c r="C119" s="50" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="D119" s="51" t="inlineStr">
+      <c r="D119" s="50" t="inlineStr">
         <is>
           <t>r-pbis</t>
         </is>
@@ -4545,13 +4542,13 @@
           <t>Q8</t>
         </is>
       </c>
-      <c r="B120" s="52" t="n">
+      <c r="B120" s="51" t="n">
         <v>0.73</v>
       </c>
-      <c r="C120" s="52" t="n">
+      <c r="C120" s="51" t="n">
         <v>1</v>
       </c>
-      <c r="D120" s="52" t="n">
+      <c r="D120" s="51" t="n">
         <v>0.86</v>
       </c>
     </row>
@@ -4561,13 +4558,13 @@
           <t>Q1</t>
         </is>
       </c>
-      <c r="B121" s="52" t="n">
+      <c r="B121" s="51" t="n">
         <v>0.67</v>
       </c>
-      <c r="C121" s="52" t="n">
+      <c r="C121" s="51" t="n">
         <v>0.75</v>
       </c>
-      <c r="D121" s="52" t="n">
+      <c r="D121" s="51" t="n">
         <v>0.48</v>
       </c>
     </row>
@@ -4577,13 +4574,13 @@
           <t>Q20</t>
         </is>
       </c>
-      <c r="B122" s="52" t="n">
+      <c r="B122" s="51" t="n">
         <v>0.67</v>
       </c>
-      <c r="C122" s="52" t="n">
+      <c r="C122" s="51" t="n">
         <v>1</v>
       </c>
-      <c r="D122" s="52" t="n">
+      <c r="D122" s="51" t="n">
         <v>0.87</v>
       </c>
     </row>
@@ -4593,13 +4590,13 @@
           <t>Q4</t>
         </is>
       </c>
-      <c r="B123" s="52" t="n">
+      <c r="B123" s="51" t="n">
         <v>0.6</v>
       </c>
-      <c r="C123" s="52" t="n">
+      <c r="C123" s="51" t="n">
         <v>1</v>
       </c>
-      <c r="D123" s="52" t="n">
+      <c r="D123" s="51" t="n">
         <v>0.88</v>
       </c>
     </row>
@@ -4609,13 +4606,13 @@
           <t>Q7</t>
         </is>
       </c>
-      <c r="B124" s="52" t="n">
+      <c r="B124" s="51" t="n">
         <v>0.6</v>
       </c>
-      <c r="C124" s="52" t="n">
+      <c r="C124" s="51" t="n">
         <v>1</v>
       </c>
-      <c r="D124" s="52" t="n">
+      <c r="D124" s="51" t="n">
         <v>0.65</v>
       </c>
     </row>
@@ -4625,13 +4622,13 @@
           <t>Q9</t>
         </is>
       </c>
-      <c r="B125" s="52" t="n">
+      <c r="B125" s="51" t="n">
         <v>0.6</v>
       </c>
-      <c r="C125" s="52" t="n">
+      <c r="C125" s="51" t="n">
         <v>1</v>
       </c>
-      <c r="D125" s="52" t="n">
+      <c r="D125" s="51" t="n">
         <v>0.76</v>
       </c>
     </row>
@@ -4641,13 +4638,13 @@
           <t>Q10</t>
         </is>
       </c>
-      <c r="B126" s="52" t="n">
+      <c r="B126" s="51" t="n">
         <v>0.6</v>
       </c>
-      <c r="C126" s="52" t="n">
+      <c r="C126" s="51" t="n">
         <v>1</v>
       </c>
-      <c r="D126" s="52" t="n">
+      <c r="D126" s="51" t="n">
         <v>0.73</v>
       </c>
     </row>
@@ -4657,13 +4654,13 @@
           <t>Q6</t>
         </is>
       </c>
-      <c r="B127" s="52" t="n">
+      <c r="B127" s="51" t="n">
         <v>0.53</v>
       </c>
-      <c r="C127" s="52" t="n">
+      <c r="C127" s="51" t="n">
         <v>0.75</v>
       </c>
-      <c r="D127" s="52" t="n">
+      <c r="D127" s="51" t="n">
         <v>0.59</v>
       </c>
     </row>
@@ -4673,13 +4670,13 @@
           <t>Q12</t>
         </is>
       </c>
-      <c r="B128" s="52" t="n">
+      <c r="B128" s="51" t="n">
         <v>0.53</v>
       </c>
-      <c r="C128" s="52" t="n">
+      <c r="C128" s="51" t="n">
         <v>1</v>
       </c>
-      <c r="D128" s="52" t="n">
+      <c r="D128" s="51" t="n">
         <v>0.74</v>
       </c>
     </row>
@@ -4689,13 +4686,13 @@
           <t>Q13</t>
         </is>
       </c>
-      <c r="B129" s="52" t="n">
+      <c r="B129" s="51" t="n">
         <v>0.53</v>
       </c>
-      <c r="C129" s="52" t="n">
+      <c r="C129" s="51" t="n">
         <v>0.75</v>
       </c>
-      <c r="D129" s="52" t="n">
+      <c r="D129" s="51" t="n">
         <v>0.72</v>
       </c>
     </row>
@@ -4705,13 +4702,13 @@
           <t>Q14</t>
         </is>
       </c>
-      <c r="B130" s="52" t="n">
+      <c r="B130" s="51" t="n">
         <v>0.53</v>
       </c>
-      <c r="C130" s="52" t="n">
+      <c r="C130" s="51" t="n">
         <v>1</v>
       </c>
-      <c r="D130" s="52" t="n">
+      <c r="D130" s="51" t="n">
         <v>0.87</v>
       </c>
     </row>
@@ -4721,13 +4718,13 @@
           <t>Q2</t>
         </is>
       </c>
-      <c r="B131" s="52" t="n">
+      <c r="B131" s="51" t="n">
         <v>0.47</v>
       </c>
-      <c r="C131" s="52" t="n">
+      <c r="C131" s="51" t="n">
         <v>0.25</v>
       </c>
-      <c r="D131" s="52" t="n">
+      <c r="D131" s="51" t="n">
         <v>0.2</v>
       </c>
     </row>
@@ -4737,13 +4734,13 @@
           <t>Q5</t>
         </is>
       </c>
-      <c r="B132" s="52" t="n">
+      <c r="B132" s="51" t="n">
         <v>0.47</v>
       </c>
-      <c r="C132" s="52" t="n">
+      <c r="C132" s="51" t="n">
         <v>1</v>
       </c>
-      <c r="D132" s="52" t="n">
+      <c r="D132" s="51" t="n">
         <v>0.7</v>
       </c>
     </row>
@@ -4753,13 +4750,13 @@
           <t>Q15</t>
         </is>
       </c>
-      <c r="B133" s="52" t="n">
+      <c r="B133" s="51" t="n">
         <v>0.47</v>
       </c>
-      <c r="C133" s="52" t="n">
+      <c r="C133" s="51" t="n">
         <v>0.5</v>
       </c>
-      <c r="D133" s="52" t="n">
+      <c r="D133" s="51" t="n">
         <v>0.51</v>
       </c>
     </row>
@@ -4769,13 +4766,13 @@
           <t>Q18</t>
         </is>
       </c>
-      <c r="B134" s="52" t="n">
+      <c r="B134" s="51" t="n">
         <v>0.47</v>
       </c>
-      <c r="C134" s="52" t="n">
+      <c r="C134" s="51" t="n">
         <v>0.75</v>
       </c>
-      <c r="D134" s="52" t="n">
+      <c r="D134" s="51" t="n">
         <v>0.76</v>
       </c>
     </row>
@@ -4785,13 +4782,13 @@
           <t>Q19</t>
         </is>
       </c>
-      <c r="B135" s="52" t="n">
+      <c r="B135" s="51" t="n">
         <v>0.4</v>
       </c>
-      <c r="C135" s="52" t="n">
+      <c r="C135" s="51" t="n">
         <v>1</v>
       </c>
-      <c r="D135" s="52" t="n">
+      <c r="D135" s="51" t="n">
         <v>0.75</v>
       </c>
     </row>
@@ -4801,13 +4798,13 @@
           <t>Q11</t>
         </is>
       </c>
-      <c r="B136" s="52" t="n">
+      <c r="B136" s="51" t="n">
         <v>0.33</v>
       </c>
-      <c r="C136" s="52" t="n">
+      <c r="C136" s="51" t="n">
         <v>0.5</v>
       </c>
-      <c r="D136" s="52" t="n">
+      <c r="D136" s="51" t="n">
         <v>0.5600000000000001</v>
       </c>
     </row>
@@ -4817,13 +4814,13 @@
           <t>Q16</t>
         </is>
       </c>
-      <c r="B137" s="52" t="n">
+      <c r="B137" s="51" t="n">
         <v>0.33</v>
       </c>
-      <c r="C137" s="52" t="n">
+      <c r="C137" s="51" t="n">
         <v>0.75</v>
       </c>
-      <c r="D137" s="52" t="n">
+      <c r="D137" s="51" t="n">
         <v>0.6</v>
       </c>
     </row>
@@ -4833,13 +4830,13 @@
           <t>Q3</t>
         </is>
       </c>
-      <c r="B138" s="52" t="n">
+      <c r="B138" s="51" t="n">
         <v>0.27</v>
       </c>
-      <c r="C138" s="52" t="n">
+      <c r="C138" s="51" t="n">
         <v>0.75</v>
       </c>
-      <c r="D138" s="52" t="n">
+      <c r="D138" s="51" t="n">
         <v>0.62</v>
       </c>
     </row>
@@ -4849,13 +4846,13 @@
           <t>Q17</t>
         </is>
       </c>
-      <c r="B139" s="52" t="n">
+      <c r="B139" s="51" t="n">
         <v>0.13</v>
       </c>
-      <c r="C139" s="52" t="n">
+      <c r="C139" s="51" t="n">
         <v>0.5</v>
       </c>
-      <c r="D139" s="52" t="n">
+      <c r="D139" s="51" t="n">
         <v>0.55</v>
       </c>
     </row>
@@ -4867,12 +4864,12 @@
       </c>
     </row>
     <row r="180">
-      <c r="A180" s="51" t="inlineStr">
+      <c r="A180" s="50" t="inlineStr">
         <is>
           <t>Status sesi</t>
         </is>
       </c>
-      <c r="B180" s="51" t="inlineStr">
+      <c r="B180" s="50" t="inlineStr">
         <is>
           <t>Jumlah</t>
         </is>
@@ -4884,7 +4881,7 @@
           <t>Tuntas 20/20</t>
         </is>
       </c>
-      <c r="B181" s="52" t="n">
+      <c r="B181" s="51" t="n">
         <v>10</v>
       </c>
     </row>
@@ -4894,7 +4891,7 @@
           <t>Terputus sebagian</t>
         </is>
       </c>
-      <c r="B182" s="52" t="n">
+      <c r="B182" s="51" t="n">
         <v>3</v>
       </c>
     </row>
@@ -4904,7 +4901,7 @@
           <t>Nol jawaban</t>
         </is>
       </c>
-      <c r="B183" s="52" t="n">
+      <c r="B183" s="51" t="n">
         <v>2</v>
       </c>
     </row>
@@ -4916,12 +4913,12 @@
       </c>
     </row>
     <row r="186">
-      <c r="A186" s="51" t="inlineStr">
+      <c r="A186" s="50" t="inlineStr">
         <is>
           <t>Jawaban benar</t>
         </is>
       </c>
-      <c r="B186" s="51" t="inlineStr">
+      <c r="B186" s="50" t="inlineStr">
         <is>
           <t>Jumlah sesi</t>
         </is>
@@ -4931,7 +4928,7 @@
       <c r="A187" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="B187" s="52" t="n">
+      <c r="B187" s="51" t="n">
         <v>2</v>
       </c>
     </row>
@@ -4939,7 +4936,7 @@
       <c r="A188" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="B188" s="52" t="n">
+      <c r="B188" s="51" t="n">
         <v>1</v>
       </c>
     </row>
@@ -4947,7 +4944,7 @@
       <c r="A189" s="19" t="n">
         <v>2</v>
       </c>
-      <c r="B189" s="52" t="n">
+      <c r="B189" s="51" t="n">
         <v>1</v>
       </c>
     </row>
@@ -4955,7 +4952,7 @@
       <c r="A190" s="19" t="n">
         <v>3</v>
       </c>
-      <c r="B190" s="52" t="n">
+      <c r="B190" s="51" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4963,7 +4960,7 @@
       <c r="A191" s="19" t="n">
         <v>4</v>
       </c>
-      <c r="B191" s="52" t="n">
+      <c r="B191" s="51" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4971,7 +4968,7 @@
       <c r="A192" s="19" t="n">
         <v>5</v>
       </c>
-      <c r="B192" s="52" t="n">
+      <c r="B192" s="51" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4979,7 +4976,7 @@
       <c r="A193" s="19" t="n">
         <v>6</v>
       </c>
-      <c r="B193" s="52" t="n">
+      <c r="B193" s="51" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4987,7 +4984,7 @@
       <c r="A194" s="19" t="n">
         <v>7</v>
       </c>
-      <c r="B194" s="52" t="n">
+      <c r="B194" s="51" t="n">
         <v>1</v>
       </c>
     </row>
@@ -4995,7 +4992,7 @@
       <c r="A195" s="19" t="n">
         <v>8</v>
       </c>
-      <c r="B195" s="52" t="n">
+      <c r="B195" s="51" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5003,7 +5000,7 @@
       <c r="A196" s="19" t="n">
         <v>9</v>
       </c>
-      <c r="B196" s="52" t="n">
+      <c r="B196" s="51" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5011,7 +5008,7 @@
       <c r="A197" s="19" t="n">
         <v>10</v>
       </c>
-      <c r="B197" s="52" t="n">
+      <c r="B197" s="51" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5019,7 +5016,7 @@
       <c r="A198" s="19" t="n">
         <v>11</v>
       </c>
-      <c r="B198" s="52" t="n">
+      <c r="B198" s="51" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5027,7 +5024,7 @@
       <c r="A199" s="19" t="n">
         <v>12</v>
       </c>
-      <c r="B199" s="52" t="n">
+      <c r="B199" s="51" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5035,7 +5032,7 @@
       <c r="A200" s="19" t="n">
         <v>13</v>
       </c>
-      <c r="B200" s="52" t="n">
+      <c r="B200" s="51" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5043,7 +5040,7 @@
       <c r="A201" s="19" t="n">
         <v>14</v>
       </c>
-      <c r="B201" s="52" t="n">
+      <c r="B201" s="51" t="n">
         <v>2</v>
       </c>
     </row>
@@ -5051,7 +5048,7 @@
       <c r="A202" s="19" t="n">
         <v>15</v>
       </c>
-      <c r="B202" s="52" t="n">
+      <c r="B202" s="51" t="n">
         <v>2</v>
       </c>
     </row>
@@ -5059,7 +5056,7 @@
       <c r="A203" s="19" t="n">
         <v>16</v>
       </c>
-      <c r="B203" s="52" t="n">
+      <c r="B203" s="51" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5067,7 +5064,7 @@
       <c r="A204" s="19" t="n">
         <v>17</v>
       </c>
-      <c r="B204" s="52" t="n">
+      <c r="B204" s="51" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5075,7 +5072,7 @@
       <c r="A205" s="19" t="n">
         <v>18</v>
       </c>
-      <c r="B205" s="52" t="n">
+      <c r="B205" s="51" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5083,7 +5080,7 @@
       <c r="A206" s="19" t="n">
         <v>19</v>
       </c>
-      <c r="B206" s="52" t="n">
+      <c r="B206" s="51" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5091,7 +5088,7 @@
       <c r="A207" s="19" t="n">
         <v>20</v>
       </c>
-      <c r="B207" s="52" t="n">
+      <c r="B207" s="51" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5103,12 +5100,12 @@
       </c>
     </row>
     <row r="228">
-      <c r="A228" s="51" t="inlineStr">
+      <c r="A228" s="50" t="inlineStr">
         <is>
           <t>Basis</t>
         </is>
       </c>
-      <c r="B228" s="51" t="inlineStr">
+      <c r="B228" s="50" t="inlineStr">
         <is>
           <t>Rata-rata benar</t>
         </is>
@@ -5120,7 +5117,7 @@
           <t>Pre-test 37 sesi</t>
         </is>
       </c>
-      <c r="B229" s="52" t="n">
+      <c r="B229" s="51" t="n">
         <v>6.46</v>
       </c>
     </row>
@@ -5130,7 +5127,7 @@
           <t>Post-test 15 sesi</t>
         </is>
       </c>
-      <c r="B230" s="52" t="n">
+      <c r="B230" s="51" t="n">
         <v>9.93</v>
       </c>
     </row>
@@ -5140,7 +5137,7 @@
           <t>Post-test 10 tuntas</t>
         </is>
       </c>
-      <c r="B231" s="52" t="n">
+      <c r="B231" s="51" t="n">
         <v>13.9</v>
       </c>
     </row>
@@ -5150,7 +5147,7 @@
           <t>Berpasangan pre (8)</t>
         </is>
       </c>
-      <c r="B232" s="52" t="n">
+      <c r="B232" s="51" t="n">
         <v>8.619999999999999</v>
       </c>
     </row>
@@ -5160,7 +5157,7 @@
           <t>Berpasangan post (8)</t>
         </is>
       </c>
-      <c r="B233" s="52" t="n">
+      <c r="B233" s="51" t="n">
         <v>13.62</v>
       </c>
     </row>
@@ -5172,12 +5169,12 @@
       </c>
     </row>
     <row r="254">
-      <c r="A254" s="51" t="inlineStr">
+      <c r="A254" s="50" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="B254" s="51" t="inlineStr">
+      <c r="B254" s="50" t="inlineStr">
         <is>
           <t>Jumlah opsi</t>
         </is>
@@ -5189,7 +5186,7 @@
           <t>Pengecoh hidup</t>
         </is>
       </c>
-      <c r="B255" s="52" t="n">
+      <c r="B255" s="51" t="n">
         <v>35</v>
       </c>
     </row>
@@ -5199,7 +5196,7 @@
           <t>Pengecoh mati</t>
         </is>
       </c>
-      <c r="B256" s="52" t="n">
+      <c r="B256" s="51" t="n">
         <v>25</v>
       </c>
     </row>
@@ -5384,107 +5381,107 @@
       <c r="A5" s="20" t="n">
         <v>1</v>
       </c>
-      <c r="B5" s="37" t="inlineStr">
+      <c r="B5" s="36" t="inlineStr">
         <is>
           <t>Agnes Nurak</t>
         </is>
       </c>
-      <c r="C5" s="53" t="inlineStr">
+      <c r="C5" s="52" t="inlineStr">
         <is>
           <t>Kolaborasi real-time dengan fitur edit bersama</t>
         </is>
       </c>
-      <c r="D5" s="53" t="inlineStr">
+      <c r="D5" s="52" t="inlineStr">
         <is>
           <t>Bisnis buku tahunan sekolah bernama Fusion Books</t>
         </is>
       </c>
-      <c r="E5" s="53" t="inlineStr">
+      <c r="E5" s="52" t="inlineStr">
         <is>
           <t>Brand Kit</t>
         </is>
       </c>
-      <c r="F5" s="53" t="inlineStr">
+      <c r="F5" s="52" t="inlineStr">
         <is>
           <t>Gunakan sebanyak mungkin jenis font agar desain terlihat beragam dan kaya</t>
         </is>
       </c>
-      <c r="G5" s="53" t="inlineStr">
+      <c r="G5" s="52" t="inlineStr">
         <is>
           <t>Rp 95.000</t>
         </is>
       </c>
-      <c r="H5" s="53" t="inlineStr">
+      <c r="H5" s="52" t="inlineStr">
         <is>
           <t>PNG (kualitas tinggi, cocok untuk media sosial dan WhatsApp)</t>
         </is>
       </c>
-      <c r="I5" s="53" t="inlineStr">
+      <c r="I5" s="52" t="inlineStr">
         <is>
           <t>(1), (3), dan (4)</t>
         </is>
       </c>
-      <c r="J5" s="53" t="inlineStr">
+      <c r="J5" s="52" t="inlineStr">
         <is>
           <t>Pertobatan, penyesalan, kerendahan hati, dan persiapan batin</t>
         </is>
       </c>
-      <c r="K5" s="53" t="inlineStr">
+      <c r="K5" s="52" t="inlineStr">
         <is>
           <t>MP4 (video berkualitas untuk presentasi dan konten video)</t>
         </is>
       </c>
-      <c r="L5" s="53" t="inlineStr">
+      <c r="L5" s="52" t="inlineStr">
         <is>
           <t>Desain perlu diperbaiki: gunakan maksimal 2-4 warna utama dan 2-3 jenis font agar terbaca dengan baik</t>
         </is>
       </c>
-      <c r="M5" s="53" t="inlineStr">
+      <c r="M5" s="52" t="inlineStr">
         <is>
           <t>Pengaturan resolusi layar monitor</t>
         </is>
       </c>
-      <c r="N5" s="53" t="inlineStr">
+      <c r="N5" s="52" t="inlineStr">
         <is>
           <t>Melanie Perkins, Cliff Obrecht, dan Cameron Adams</t>
         </is>
       </c>
-      <c r="O5" s="53" t="inlineStr">
+      <c r="O5" s="52" t="inlineStr">
         <is>
           <t>Eyedropper — ambil warna dari elemen/foto</t>
         </is>
       </c>
-      <c r="P5" s="53" t="inlineStr">
+      <c r="P5" s="52" t="inlineStr">
         <is>
           <t>1080 x 1080 px (Instagram Feed)</t>
         </is>
       </c>
-      <c r="Q5" s="53" t="inlineStr">
+      <c r="Q5" s="52" t="inlineStr">
         <is>
           <t>Inovasi tanpa batas dalam setiap desain</t>
         </is>
       </c>
-      <c r="R5" s="53" t="inlineStr">
+      <c r="R5" s="52" t="inlineStr">
         <is>
           <t>Login → Pilih menu Template → Pilih jenis desain → Cari template → Klik 'Gunakan template ini'</t>
         </is>
       </c>
-      <c r="S5" s="53" t="inlineStr">
+      <c r="S5" s="52" t="inlineStr">
         <is>
           <t>Komentar langsung pada elemen desain di Canva</t>
         </is>
       </c>
-      <c r="T5" s="53" t="inlineStr">
+      <c r="T5" s="52" t="inlineStr">
         <is>
           <t>Menggunakan fitur AI Canva untuk membuat konten yang memfitnah atau menyebarkan informasi palsu</t>
         </is>
       </c>
-      <c r="U5" s="53" t="inlineStr">
+      <c r="U5" s="52" t="inlineStr">
         <is>
           <t>Satu warna dasar dengan berbagai gradasi dan tingkat kecerahan berbeda</t>
         </is>
       </c>
-      <c r="V5" s="53" t="inlineStr">
+      <c r="V5" s="52" t="inlineStr">
         <is>
           <t>Canva adalah sarana untuk berkarya, berkomunikasi efektif, dan memberikan dampak positif bagi sesama</t>
         </is>
@@ -5494,107 +5491,107 @@
       <c r="A6" s="20" t="n">
         <v>2</v>
       </c>
-      <c r="B6" s="37" t="inlineStr">
+      <c r="B6" s="36" t="inlineStr">
         <is>
           <t>Mien</t>
         </is>
       </c>
-      <c r="C6" s="53" t="inlineStr">
+      <c r="C6" s="52" t="inlineStr">
         <is>
           <t>Kolaborasi real-time dengan fitur edit bersama</t>
         </is>
       </c>
-      <c r="D6" s="54" t="inlineStr">
+      <c r="D6" s="53" t="inlineStr">
         <is>
           <t>Platform desain logo online berbayar</t>
         </is>
       </c>
-      <c r="E6" s="53" t="inlineStr">
+      <c r="E6" s="52" t="inlineStr">
         <is>
           <t>Brand Kit</t>
         </is>
       </c>
-      <c r="F6" s="53" t="inlineStr">
+      <c r="F6" s="52" t="inlineStr">
         <is>
           <t>Gunakan sebanyak mungkin jenis font agar desain terlihat beragam dan kaya</t>
         </is>
       </c>
-      <c r="G6" s="53" t="inlineStr">
+      <c r="G6" s="52" t="inlineStr">
         <is>
           <t>Rp 95.000</t>
         </is>
       </c>
-      <c r="H6" s="53" t="inlineStr">
+      <c r="H6" s="52" t="inlineStr">
         <is>
           <t>PNG (kualitas tinggi, cocok untuk media sosial dan WhatsApp)</t>
         </is>
       </c>
-      <c r="I6" s="53" t="inlineStr">
+      <c r="I6" s="52" t="inlineStr">
         <is>
           <t>(1), (3), dan (4)</t>
         </is>
       </c>
-      <c r="J6" s="53" t="inlineStr">
+      <c r="J6" s="52" t="inlineStr">
         <is>
           <t>Pertobatan, penyesalan, kerendahan hati, dan persiapan batin</t>
         </is>
       </c>
-      <c r="K6" s="53" t="inlineStr">
+      <c r="K6" s="52" t="inlineStr">
         <is>
           <t>MP4 (video berkualitas untuk presentasi dan konten video)</t>
         </is>
       </c>
-      <c r="L6" s="53" t="inlineStr">
+      <c r="L6" s="52" t="inlineStr">
         <is>
           <t>Desain perlu diperbaiki: gunakan maksimal 2-4 warna utama dan 2-3 jenis font agar terbaca dengan baik</t>
         </is>
       </c>
-      <c r="M6" s="53" t="inlineStr">
+      <c r="M6" s="52" t="inlineStr">
         <is>
           <t>Pengaturan resolusi layar monitor</t>
         </is>
       </c>
-      <c r="N6" s="53" t="inlineStr">
+      <c r="N6" s="52" t="inlineStr">
         <is>
           <t>Melanie Perkins, Cliff Obrecht, dan Cameron Adams</t>
         </is>
       </c>
-      <c r="O6" s="53" t="inlineStr">
+      <c r="O6" s="52" t="inlineStr">
         <is>
           <t>Eyedropper — ambil warna dari elemen/foto</t>
         </is>
       </c>
-      <c r="P6" s="53" t="inlineStr">
+      <c r="P6" s="52" t="inlineStr">
         <is>
           <t>1080 x 1080 px (Instagram Feed)</t>
         </is>
       </c>
-      <c r="Q6" s="54" t="inlineStr">
+      <c r="Q6" s="53" t="inlineStr">
         <is>
           <t>Ketulusan dalam berkarya untuk memuliakan Tuhan</t>
         </is>
       </c>
-      <c r="R6" s="53" t="inlineStr">
+      <c r="R6" s="52" t="inlineStr">
         <is>
           <t>Login → Pilih menu Template → Pilih jenis desain → Cari template → Klik 'Gunakan template ini'</t>
         </is>
       </c>
-      <c r="S6" s="53" t="inlineStr">
+      <c r="S6" s="52" t="inlineStr">
         <is>
           <t>Komentar langsung pada elemen desain di Canva</t>
         </is>
       </c>
-      <c r="T6" s="53" t="inlineStr">
+      <c r="T6" s="52" t="inlineStr">
         <is>
           <t>Menggunakan fitur AI Canva untuk membuat konten yang memfitnah atau menyebarkan informasi palsu</t>
         </is>
       </c>
-      <c r="U6" s="53" t="inlineStr">
+      <c r="U6" s="52" t="inlineStr">
         <is>
           <t>Satu warna dasar dengan berbagai gradasi dan tingkat kecerahan berbeda</t>
         </is>
       </c>
-      <c r="V6" s="53" t="inlineStr">
+      <c r="V6" s="52" t="inlineStr">
         <is>
           <t>Canva adalah sarana untuk berkarya, berkomunikasi efektif, dan memberikan dampak positif bagi sesama</t>
         </is>
@@ -5604,107 +5601,107 @@
       <c r="A7" s="20" t="n">
         <v>3</v>
       </c>
-      <c r="B7" s="37" t="inlineStr">
+      <c r="B7" s="36" t="inlineStr">
         <is>
           <t>LESLY MARCHRITH NUSALY</t>
         </is>
       </c>
-      <c r="C7" s="53" t="inlineStr">
+      <c r="C7" s="52" t="inlineStr">
         <is>
           <t>Kolaborasi real-time dengan fitur edit bersama</t>
         </is>
       </c>
-      <c r="D7" s="53" t="inlineStr">
+      <c r="D7" s="52" t="inlineStr">
         <is>
           <t>Bisnis buku tahunan sekolah bernama Fusion Books</t>
         </is>
       </c>
-      <c r="E7" s="54" t="inlineStr">
+      <c r="E7" s="53" t="inlineStr">
         <is>
           <t>Warna Elemen Manual</t>
         </is>
       </c>
-      <c r="F7" s="53" t="inlineStr">
+      <c r="F7" s="52" t="inlineStr">
         <is>
           <t>Gunakan sebanyak mungkin jenis font agar desain terlihat beragam dan kaya</t>
         </is>
       </c>
-      <c r="G7" s="53" t="inlineStr">
+      <c r="G7" s="52" t="inlineStr">
         <is>
           <t>Rp 95.000</t>
         </is>
       </c>
-      <c r="H7" s="53" t="inlineStr">
+      <c r="H7" s="52" t="inlineStr">
         <is>
           <t>PNG (kualitas tinggi, cocok untuk media sosial dan WhatsApp)</t>
         </is>
       </c>
-      <c r="I7" s="53" t="inlineStr">
+      <c r="I7" s="52" t="inlineStr">
         <is>
           <t>(1), (3), dan (4)</t>
         </is>
       </c>
-      <c r="J7" s="53" t="inlineStr">
+      <c r="J7" s="52" t="inlineStr">
         <is>
           <t>Pertobatan, penyesalan, kerendahan hati, dan persiapan batin</t>
         </is>
       </c>
-      <c r="K7" s="53" t="inlineStr">
+      <c r="K7" s="52" t="inlineStr">
         <is>
           <t>MP4 (video berkualitas untuk presentasi dan konten video)</t>
         </is>
       </c>
-      <c r="L7" s="53" t="inlineStr">
+      <c r="L7" s="52" t="inlineStr">
         <is>
           <t>Desain perlu diperbaiki: gunakan maksimal 2-4 warna utama dan 2-3 jenis font agar terbaca dengan baik</t>
         </is>
       </c>
-      <c r="M7" s="54" t="inlineStr">
+      <c r="M7" s="53" t="inlineStr">
         <is>
           <t>Teks dan pilihan font</t>
         </is>
       </c>
-      <c r="N7" s="53" t="inlineStr">
+      <c r="N7" s="52" t="inlineStr">
         <is>
           <t>Melanie Perkins, Cliff Obrecht, dan Cameron Adams</t>
         </is>
       </c>
-      <c r="O7" s="53" t="inlineStr">
+      <c r="O7" s="52" t="inlineStr">
         <is>
           <t>Eyedropper — ambil warna dari elemen/foto</t>
         </is>
       </c>
-      <c r="P7" s="53" t="inlineStr">
+      <c r="P7" s="52" t="inlineStr">
         <is>
           <t>1080 x 1080 px (Instagram Feed)</t>
         </is>
       </c>
-      <c r="Q7" s="54" t="inlineStr">
+      <c r="Q7" s="53" t="inlineStr">
         <is>
           <t>Tanggung jawab atas setiap karya yang dibuat</t>
         </is>
       </c>
-      <c r="R7" s="54" t="inlineStr">
+      <c r="R7" s="53" t="inlineStr">
         <is>
           <t>Login → Klik Buat Desain → Pilih Elemen → Temukan Template → Edit</t>
         </is>
       </c>
-      <c r="S7" s="54" t="inlineStr">
+      <c r="S7" s="53" t="inlineStr">
         <is>
           <t>Penyimpanan cloud agar file dapat diakses kapan saja</t>
         </is>
       </c>
-      <c r="T7" s="53" t="inlineStr">
+      <c r="T7" s="52" t="inlineStr">
         <is>
           <t>Menggunakan fitur AI Canva untuk membuat konten yang memfitnah atau menyebarkan informasi palsu</t>
         </is>
       </c>
-      <c r="U7" s="53" t="inlineStr">
+      <c r="U7" s="52" t="inlineStr">
         <is>
           <t>Satu warna dasar dengan berbagai gradasi dan tingkat kecerahan berbeda</t>
         </is>
       </c>
-      <c r="V7" s="53" t="inlineStr">
+      <c r="V7" s="52" t="inlineStr">
         <is>
           <t>Canva adalah sarana untuk berkarya, berkomunikasi efektif, dan memberikan dampak positif bagi sesama</t>
         </is>
@@ -5714,107 +5711,107 @@
       <c r="A8" s="20" t="n">
         <v>4</v>
       </c>
-      <c r="B8" s="37" t="inlineStr">
+      <c r="B8" s="36" t="inlineStr">
         <is>
           <t>Gerarda Ina</t>
         </is>
       </c>
-      <c r="C8" s="53" t="inlineStr">
+      <c r="C8" s="52" t="inlineStr">
         <is>
           <t>Kolaborasi real-time dengan fitur edit bersama</t>
         </is>
       </c>
-      <c r="D8" s="53" t="inlineStr">
+      <c r="D8" s="52" t="inlineStr">
         <is>
           <t>Bisnis buku tahunan sekolah bernama Fusion Books</t>
         </is>
       </c>
-      <c r="E8" s="53" t="inlineStr">
+      <c r="E8" s="52" t="inlineStr">
         <is>
           <t>Brand Kit</t>
         </is>
       </c>
-      <c r="F8" s="53" t="inlineStr">
+      <c r="F8" s="52" t="inlineStr">
         <is>
           <t>Gunakan sebanyak mungkin jenis font agar desain terlihat beragam dan kaya</t>
         </is>
       </c>
-      <c r="G8" s="53" t="inlineStr">
+      <c r="G8" s="52" t="inlineStr">
         <is>
           <t>Rp 95.000</t>
         </is>
       </c>
-      <c r="H8" s="54" t="inlineStr">
+      <c r="H8" s="53" t="inlineStr">
         <is>
           <t>PDF (karena untuk keperluan cetak)</t>
         </is>
       </c>
-      <c r="I8" s="53" t="inlineStr">
+      <c r="I8" s="52" t="inlineStr">
         <is>
           <t>(1), (3), dan (4)</t>
         </is>
       </c>
-      <c r="J8" s="53" t="inlineStr">
+      <c r="J8" s="52" t="inlineStr">
         <is>
           <t>Pertobatan, penyesalan, kerendahan hati, dan persiapan batin</t>
         </is>
       </c>
-      <c r="K8" s="53" t="inlineStr">
+      <c r="K8" s="52" t="inlineStr">
         <is>
           <t>MP4 (video berkualitas untuk presentasi dan konten video)</t>
         </is>
       </c>
-      <c r="L8" s="53" t="inlineStr">
+      <c r="L8" s="52" t="inlineStr">
         <is>
           <t>Desain perlu diperbaiki: gunakan maksimal 2-4 warna utama dan 2-3 jenis font agar terbaca dengan baik</t>
         </is>
       </c>
-      <c r="M8" s="54" t="inlineStr">
+      <c r="M8" s="53" t="inlineStr">
         <is>
           <t>Unggahan file dari perangkat</t>
         </is>
       </c>
-      <c r="N8" s="53" t="inlineStr">
+      <c r="N8" s="52" t="inlineStr">
         <is>
           <t>Melanie Perkins, Cliff Obrecht, dan Cameron Adams</t>
         </is>
       </c>
-      <c r="O8" s="54" t="inlineStr">
+      <c r="O8" s="53" t="inlineStr">
         <is>
           <t>Brand Kit — simpan warna brand</t>
         </is>
       </c>
-      <c r="P8" s="53" t="inlineStr">
+      <c r="P8" s="52" t="inlineStr">
         <is>
           <t>1080 x 1080 px (Instagram Feed)</t>
         </is>
       </c>
-      <c r="Q8" s="53" t="inlineStr">
+      <c r="Q8" s="52" t="inlineStr">
         <is>
           <t>Inovasi tanpa batas dalam setiap desain</t>
         </is>
       </c>
-      <c r="R8" s="53" t="inlineStr">
+      <c r="R8" s="52" t="inlineStr">
         <is>
           <t>Login → Pilih menu Template → Pilih jenis desain → Cari template → Klik 'Gunakan template ini'</t>
         </is>
       </c>
-      <c r="S8" s="54" t="inlineStr">
+      <c r="S8" s="53" t="inlineStr">
         <is>
           <t>Penyimpanan cloud agar file dapat diakses kapan saja</t>
         </is>
       </c>
-      <c r="T8" s="54" t="inlineStr">
+      <c r="T8" s="53" t="inlineStr">
         <is>
           <t>Menggunakan template AI Canva untuk mendukung kegiatan pelayanan gereja</t>
         </is>
       </c>
-      <c r="U8" s="53" t="inlineStr">
+      <c r="U8" s="52" t="inlineStr">
         <is>
           <t>Satu warna dasar dengan berbagai gradasi dan tingkat kecerahan berbeda</t>
         </is>
       </c>
-      <c r="V8" s="53" t="inlineStr">
+      <c r="V8" s="52" t="inlineStr">
         <is>
           <t>Canva adalah sarana untuk berkarya, berkomunikasi efektif, dan memberikan dampak positif bagi sesama</t>
         </is>
@@ -5824,107 +5821,107 @@
       <c r="A9" s="20" t="n">
         <v>5</v>
       </c>
-      <c r="B9" s="37" t="inlineStr">
+      <c r="B9" s="36" t="inlineStr">
         <is>
           <t>Mirza Caroline</t>
         </is>
       </c>
-      <c r="C9" s="53" t="inlineStr">
+      <c r="C9" s="52" t="inlineStr">
         <is>
           <t>Kolaborasi real-time dengan fitur edit bersama</t>
         </is>
       </c>
-      <c r="D9" s="53" t="inlineStr">
+      <c r="D9" s="52" t="inlineStr">
         <is>
           <t>Bisnis buku tahunan sekolah bernama Fusion Books</t>
         </is>
       </c>
-      <c r="E9" s="54" t="inlineStr">
+      <c r="E9" s="53" t="inlineStr">
         <is>
           <t>Eyedropper Tool</t>
         </is>
       </c>
-      <c r="F9" s="53" t="inlineStr">
+      <c r="F9" s="52" t="inlineStr">
         <is>
           <t>Gunakan sebanyak mungkin jenis font agar desain terlihat beragam dan kaya</t>
         </is>
       </c>
-      <c r="G9" s="53" t="inlineStr">
+      <c r="G9" s="52" t="inlineStr">
         <is>
           <t>Rp 95.000</t>
         </is>
       </c>
-      <c r="H9" s="53" t="inlineStr">
+      <c r="H9" s="52" t="inlineStr">
         <is>
           <t>PNG (kualitas tinggi, cocok untuk media sosial dan WhatsApp)</t>
         </is>
       </c>
-      <c r="I9" s="54" t="inlineStr">
+      <c r="I9" s="53" t="inlineStr">
         <is>
           <t>(1), (2), (3), dan (4)</t>
         </is>
       </c>
-      <c r="J9" s="53" t="inlineStr">
+      <c r="J9" s="52" t="inlineStr">
         <is>
           <t>Pertobatan, penyesalan, kerendahan hati, dan persiapan batin</t>
         </is>
       </c>
-      <c r="K9" s="53" t="inlineStr">
+      <c r="K9" s="52" t="inlineStr">
         <is>
           <t>MP4 (video berkualitas untuk presentasi dan konten video)</t>
         </is>
       </c>
-      <c r="L9" s="53" t="inlineStr">
+      <c r="L9" s="52" t="inlineStr">
         <is>
           <t>Desain perlu diperbaiki: gunakan maksimal 2-4 warna utama dan 2-3 jenis font agar terbaca dengan baik</t>
         </is>
       </c>
-      <c r="M9" s="54" t="inlineStr">
+      <c r="M9" s="53" t="inlineStr">
         <is>
           <t>Unggahan file dari perangkat</t>
         </is>
       </c>
-      <c r="N9" s="53" t="inlineStr">
+      <c r="N9" s="52" t="inlineStr">
         <is>
           <t>Melanie Perkins, Cliff Obrecht, dan Cameron Adams</t>
         </is>
       </c>
-      <c r="O9" s="53" t="inlineStr">
+      <c r="O9" s="52" t="inlineStr">
         <is>
           <t>Eyedropper — ambil warna dari elemen/foto</t>
         </is>
       </c>
-      <c r="P9" s="53" t="inlineStr">
+      <c r="P9" s="52" t="inlineStr">
         <is>
           <t>1080 x 1080 px (Instagram Feed)</t>
         </is>
       </c>
-      <c r="Q9" s="53" t="inlineStr">
+      <c r="Q9" s="52" t="inlineStr">
         <is>
           <t>Inovasi tanpa batas dalam setiap desain</t>
         </is>
       </c>
-      <c r="R9" s="54" t="inlineStr">
+      <c r="R9" s="53" t="inlineStr">
         <is>
           <t>Login → Klik Buat Desain → Pilih Elemen → Temukan Template → Edit</t>
         </is>
       </c>
-      <c r="S9" s="54" t="inlineStr">
+      <c r="S9" s="53" t="inlineStr">
         <is>
           <t>Download desain lalu kirim via email beserta catatan revisi</t>
         </is>
       </c>
-      <c r="T9" s="53" t="inlineStr">
+      <c r="T9" s="52" t="inlineStr">
         <is>
           <t>Menggunakan fitur AI Canva untuk membuat konten yang memfitnah atau menyebarkan informasi palsu</t>
         </is>
       </c>
-      <c r="U9" s="54" t="inlineStr">
+      <c r="U9" s="53" t="inlineStr">
         <is>
           <t>Kombinasi tiga warna yang membentuk segitiga pada roda warna</t>
         </is>
       </c>
-      <c r="V9" s="53" t="inlineStr">
+      <c r="V9" s="52" t="inlineStr">
         <is>
           <t>Canva adalah sarana untuk berkarya, berkomunikasi efektif, dan memberikan dampak positif bagi sesama</t>
         </is>
@@ -5934,107 +5931,107 @@
       <c r="A10" s="20" t="n">
         <v>6</v>
       </c>
-      <c r="B10" s="37" t="inlineStr">
+      <c r="B10" s="36" t="inlineStr">
         <is>
           <t>wisye pangalila</t>
         </is>
       </c>
-      <c r="C10" s="54" t="inlineStr">
+      <c r="C10" s="53" t="inlineStr">
         <is>
           <t>Template berbagi pakai</t>
         </is>
       </c>
-      <c r="D10" s="54" t="inlineStr">
+      <c r="D10" s="53" t="inlineStr">
         <is>
           <t>Aplikasi edit foto berbasis mobile</t>
         </is>
       </c>
-      <c r="E10" s="54" t="inlineStr">
+      <c r="E10" s="53" t="inlineStr">
         <is>
           <t>Warna Elemen Manual</t>
         </is>
       </c>
-      <c r="F10" s="53" t="inlineStr">
+      <c r="F10" s="52" t="inlineStr">
         <is>
           <t>Gunakan sebanyak mungkin jenis font agar desain terlihat beragam dan kaya</t>
         </is>
       </c>
-      <c r="G10" s="54" t="inlineStr">
+      <c r="G10" s="53" t="inlineStr">
         <is>
           <t>Rp 75.000</t>
         </is>
       </c>
-      <c r="H10" s="53" t="inlineStr">
+      <c r="H10" s="52" t="inlineStr">
         <is>
           <t>PNG (kualitas tinggi, cocok untuk media sosial dan WhatsApp)</t>
         </is>
       </c>
-      <c r="I10" s="53" t="inlineStr">
+      <c r="I10" s="52" t="inlineStr">
         <is>
           <t>(1), (3), dan (4)</t>
         </is>
       </c>
-      <c r="J10" s="53" t="inlineStr">
+      <c r="J10" s="52" t="inlineStr">
         <is>
           <t>Pertobatan, penyesalan, kerendahan hati, dan persiapan batin</t>
         </is>
       </c>
-      <c r="K10" s="53" t="inlineStr">
+      <c r="K10" s="52" t="inlineStr">
         <is>
           <t>MP4 (video berkualitas untuk presentasi dan konten video)</t>
         </is>
       </c>
-      <c r="L10" s="54" t="inlineStr">
+      <c r="L10" s="53" t="inlineStr">
         <is>
           <t>Desain perlu diperbaiki hanya pada pemilihan warna, jumlah font sudah ideal</t>
         </is>
       </c>
-      <c r="M10" s="53" t="inlineStr">
+      <c r="M10" s="52" t="inlineStr">
         <is>
           <t>Pengaturan resolusi layar monitor</t>
         </is>
       </c>
-      <c r="N10" s="53" t="inlineStr">
+      <c r="N10" s="52" t="inlineStr">
         <is>
           <t>Melanie Perkins, Cliff Obrecht, dan Cameron Adams</t>
         </is>
       </c>
-      <c r="O10" s="53" t="inlineStr">
+      <c r="O10" s="52" t="inlineStr">
         <is>
           <t>Eyedropper — ambil warna dari elemen/foto</t>
         </is>
       </c>
-      <c r="P10" s="53" t="inlineStr">
+      <c r="P10" s="52" t="inlineStr">
         <is>
           <t>1080 x 1080 px (Instagram Feed)</t>
         </is>
       </c>
-      <c r="Q10" s="53" t="inlineStr">
+      <c r="Q10" s="52" t="inlineStr">
         <is>
           <t>Inovasi tanpa batas dalam setiap desain</t>
         </is>
       </c>
-      <c r="R10" s="53" t="inlineStr">
+      <c r="R10" s="52" t="inlineStr">
         <is>
           <t>Login → Pilih menu Template → Pilih jenis desain → Cari template → Klik 'Gunakan template ini'</t>
         </is>
       </c>
-      <c r="S10" s="54" t="inlineStr">
+      <c r="S10" s="53" t="inlineStr">
         <is>
           <t>Share tautan desain tanpa akses edit</t>
         </is>
       </c>
-      <c r="T10" s="53" t="inlineStr">
+      <c r="T10" s="52" t="inlineStr">
         <is>
           <t>Menggunakan fitur AI Canva untuk membuat konten yang memfitnah atau menyebarkan informasi palsu</t>
         </is>
       </c>
-      <c r="U10" s="53" t="inlineStr">
+      <c r="U10" s="52" t="inlineStr">
         <is>
           <t>Satu warna dasar dengan berbagai gradasi dan tingkat kecerahan berbeda</t>
         </is>
       </c>
-      <c r="V10" s="53" t="inlineStr">
+      <c r="V10" s="52" t="inlineStr">
         <is>
           <t>Canva adalah sarana untuk berkarya, berkomunikasi efektif, dan memberikan dampak positif bagi sesama</t>
         </is>
@@ -6044,107 +6041,107 @@
       <c r="A11" s="20" t="n">
         <v>7</v>
       </c>
-      <c r="B11" s="37" t="inlineStr">
+      <c r="B11" s="36" t="inlineStr">
         <is>
           <t>Yovita</t>
         </is>
       </c>
-      <c r="C11" s="54" t="inlineStr">
+      <c r="C11" s="53" t="inlineStr">
         <is>
           <t>Template berbagi pakai</t>
         </is>
       </c>
-      <c r="D11" s="54" t="inlineStr">
+      <c r="D11" s="53" t="inlineStr">
         <is>
           <t>Aplikasi edit foto berbasis mobile</t>
         </is>
       </c>
-      <c r="E11" s="53" t="inlineStr">
+      <c r="E11" s="52" t="inlineStr">
         <is>
           <t>Brand Kit</t>
         </is>
       </c>
-      <c r="F11" s="53" t="inlineStr">
+      <c r="F11" s="52" t="inlineStr">
         <is>
           <t>Gunakan sebanyak mungkin jenis font agar desain terlihat beragam dan kaya</t>
         </is>
       </c>
-      <c r="G11" s="53" t="inlineStr">
+      <c r="G11" s="52" t="inlineStr">
         <is>
           <t>Rp 95.000</t>
         </is>
       </c>
-      <c r="H11" s="54" t="inlineStr">
+      <c r="H11" s="53" t="inlineStr">
         <is>
           <t>PDF (karena untuk keperluan cetak)</t>
         </is>
       </c>
-      <c r="I11" s="53" t="inlineStr">
+      <c r="I11" s="52" t="inlineStr">
         <is>
           <t>(1), (3), dan (4)</t>
         </is>
       </c>
-      <c r="J11" s="53" t="inlineStr">
+      <c r="J11" s="52" t="inlineStr">
         <is>
           <t>Pertobatan, penyesalan, kerendahan hati, dan persiapan batin</t>
         </is>
       </c>
-      <c r="K11" s="54" t="inlineStr">
+      <c r="K11" s="53" t="inlineStr">
         <is>
           <t>PNG (kualitas gambar tertinggi)</t>
         </is>
       </c>
-      <c r="L11" s="53" t="inlineStr">
+      <c r="L11" s="52" t="inlineStr">
         <is>
           <t>Desain perlu diperbaiki: gunakan maksimal 2-4 warna utama dan 2-3 jenis font agar terbaca dengan baik</t>
         </is>
       </c>
-      <c r="M11" s="53" t="inlineStr">
+      <c r="M11" s="52" t="inlineStr">
         <is>
           <t>Pengaturan resolusi layar monitor</t>
         </is>
       </c>
-      <c r="N11" s="54" t="inlineStr">
+      <c r="N11" s="53" t="inlineStr">
         <is>
           <t>Melanie Perkins, Cameron Adams, dan Mark Zuckerberg</t>
         </is>
       </c>
-      <c r="O11" s="53" t="inlineStr">
+      <c r="O11" s="52" t="inlineStr">
         <is>
           <t>Eyedropper — ambil warna dari elemen/foto</t>
         </is>
       </c>
-      <c r="P11" s="53" t="inlineStr">
+      <c r="P11" s="52" t="inlineStr">
         <is>
           <t>1080 x 1080 px (Instagram Feed)</t>
         </is>
       </c>
-      <c r="Q11" s="53" t="inlineStr">
+      <c r="Q11" s="52" t="inlineStr">
         <is>
           <t>Inovasi tanpa batas dalam setiap desain</t>
         </is>
       </c>
-      <c r="R11" s="54" t="inlineStr">
+      <c r="R11" s="53" t="inlineStr">
         <is>
           <t>Login → Klik Buat Desain → Pilih Elemen → Temukan Template → Edit</t>
         </is>
       </c>
-      <c r="S11" s="54" t="inlineStr">
+      <c r="S11" s="53" t="inlineStr">
         <is>
           <t>Penyimpanan cloud agar file dapat diakses kapan saja</t>
         </is>
       </c>
-      <c r="T11" s="53" t="inlineStr">
+      <c r="T11" s="52" t="inlineStr">
         <is>
           <t>Menggunakan fitur AI Canva untuk membuat konten yang memfitnah atau menyebarkan informasi palsu</t>
         </is>
       </c>
-      <c r="U11" s="53" t="inlineStr">
+      <c r="U11" s="52" t="inlineStr">
         <is>
           <t>Satu warna dasar dengan berbagai gradasi dan tingkat kecerahan berbeda</t>
         </is>
       </c>
-      <c r="V11" s="53" t="inlineStr">
+      <c r="V11" s="52" t="inlineStr">
         <is>
           <t>Canva adalah sarana untuk berkarya, berkomunikasi efektif, dan memberikan dampak positif bagi sesama</t>
         </is>
@@ -6154,107 +6151,107 @@
       <c r="A12" s="20" t="n">
         <v>8</v>
       </c>
-      <c r="B12" s="37" t="inlineStr">
+      <c r="B12" s="36" t="inlineStr">
         <is>
           <t>Netty Nusaly</t>
         </is>
       </c>
-      <c r="C12" s="53" t="inlineStr">
+      <c r="C12" s="52" t="inlineStr">
         <is>
           <t>Kolaborasi real-time dengan fitur edit bersama</t>
         </is>
       </c>
-      <c r="D12" s="53" t="inlineStr">
+      <c r="D12" s="52" t="inlineStr">
         <is>
           <t>Bisnis buku tahunan sekolah bernama Fusion Books</t>
         </is>
       </c>
-      <c r="E12" s="54" t="inlineStr">
+      <c r="E12" s="53" t="inlineStr">
         <is>
           <t>Warna Elemen Manual</t>
         </is>
       </c>
-      <c r="F12" s="53" t="inlineStr">
+      <c r="F12" s="52" t="inlineStr">
         <is>
           <t>Gunakan sebanyak mungkin jenis font agar desain terlihat beragam dan kaya</t>
         </is>
       </c>
-      <c r="G12" s="54" t="inlineStr">
+      <c r="G12" s="53" t="inlineStr">
         <is>
           <t>Rp 75.000</t>
         </is>
       </c>
-      <c r="H12" s="53" t="inlineStr">
+      <c r="H12" s="52" t="inlineStr">
         <is>
           <t>PNG (kualitas tinggi, cocok untuk media sosial dan WhatsApp)</t>
         </is>
       </c>
-      <c r="I12" s="54" t="inlineStr">
+      <c r="I12" s="53" t="inlineStr">
         <is>
           <t>(1), (2), dan (3)</t>
         </is>
       </c>
-      <c r="J12" s="53" t="inlineStr">
+      <c r="J12" s="52" t="inlineStr">
         <is>
           <t>Pertobatan, penyesalan, kerendahan hati, dan persiapan batin</t>
         </is>
       </c>
-      <c r="K12" s="53" t="inlineStr">
+      <c r="K12" s="52" t="inlineStr">
         <is>
           <t>MP4 (video berkualitas untuk presentasi dan konten video)</t>
         </is>
       </c>
-      <c r="L12" s="53" t="inlineStr">
+      <c r="L12" s="52" t="inlineStr">
         <is>
           <t>Desain perlu diperbaiki: gunakan maksimal 2-4 warna utama dan 2-3 jenis font agar terbaca dengan baik</t>
         </is>
       </c>
-      <c r="M12" s="54" t="inlineStr">
+      <c r="M12" s="53" t="inlineStr">
         <is>
           <t>Unggahan file dari perangkat</t>
         </is>
       </c>
-      <c r="N12" s="53" t="inlineStr">
+      <c r="N12" s="52" t="inlineStr">
         <is>
           <t>Melanie Perkins, Cliff Obrecht, dan Cameron Adams</t>
         </is>
       </c>
-      <c r="O12" s="53" t="inlineStr">
+      <c r="O12" s="52" t="inlineStr">
         <is>
           <t>Eyedropper — ambil warna dari elemen/foto</t>
         </is>
       </c>
-      <c r="P12" s="53" t="inlineStr">
+      <c r="P12" s="52" t="inlineStr">
         <is>
           <t>1080 x 1080 px (Instagram Feed)</t>
         </is>
       </c>
-      <c r="Q12" s="54" t="inlineStr">
+      <c r="Q12" s="53" t="inlineStr">
         <is>
           <t>Semangat melayani untuk menginspirasi sesama</t>
         </is>
       </c>
-      <c r="R12" s="54" t="inlineStr">
+      <c r="R12" s="53" t="inlineStr">
         <is>
           <t>Login → Pilih menu Proyek → Cari Template → Download → Edit Offline</t>
         </is>
       </c>
-      <c r="S12" s="54" t="inlineStr">
+      <c r="S12" s="53" t="inlineStr">
         <is>
           <t>Download desain lalu kirim via email beserta catatan revisi</t>
         </is>
       </c>
-      <c r="T12" s="53" t="inlineStr">
+      <c r="T12" s="52" t="inlineStr">
         <is>
           <t>Menggunakan fitur AI Canva untuk membuat konten yang memfitnah atau menyebarkan informasi palsu</t>
         </is>
       </c>
-      <c r="U12" s="54" t="inlineStr">
+      <c r="U12" s="53" t="inlineStr">
         <is>
           <t>Kombinasi tiga warna yang membentuk segitiga pada roda warna</t>
         </is>
       </c>
-      <c r="V12" s="53" t="inlineStr">
+      <c r="V12" s="52" t="inlineStr">
         <is>
           <t>Canva adalah sarana untuk berkarya, berkomunikasi efektif, dan memberikan dampak positif bagi sesama</t>
         </is>
@@ -6264,107 +6261,107 @@
       <c r="A13" s="20" t="n">
         <v>9</v>
       </c>
-      <c r="B13" s="37" t="inlineStr">
+      <c r="B13" s="36" t="inlineStr">
         <is>
           <t>Ivo Emelia</t>
         </is>
       </c>
-      <c r="C13" s="53" t="inlineStr">
+      <c r="C13" s="52" t="inlineStr">
         <is>
           <t>Kolaborasi real-time dengan fitur edit bersama</t>
         </is>
       </c>
-      <c r="D13" s="54" t="inlineStr">
+      <c r="D13" s="53" t="inlineStr">
         <is>
           <t>Aplikasi edit foto berbasis mobile</t>
         </is>
       </c>
-      <c r="E13" s="54" t="inlineStr">
+      <c r="E13" s="53" t="inlineStr">
         <is>
           <t>Gradien Warna</t>
         </is>
       </c>
-      <c r="F13" s="53" t="inlineStr">
+      <c r="F13" s="52" t="inlineStr">
         <is>
           <t>Gunakan sebanyak mungkin jenis font agar desain terlihat beragam dan kaya</t>
         </is>
       </c>
-      <c r="G13" s="54" t="inlineStr">
+      <c r="G13" s="53" t="inlineStr">
         <is>
           <t>Rp 75.000</t>
         </is>
       </c>
-      <c r="H13" s="54" t="inlineStr">
+      <c r="H13" s="53" t="inlineStr">
         <is>
           <t>PDF (karena untuk keperluan cetak)</t>
         </is>
       </c>
-      <c r="I13" s="53" t="inlineStr">
+      <c r="I13" s="52" t="inlineStr">
         <is>
           <t>(1), (3), dan (4)</t>
         </is>
       </c>
-      <c r="J13" s="53" t="inlineStr">
+      <c r="J13" s="52" t="inlineStr">
         <is>
           <t>Pertobatan, penyesalan, kerendahan hati, dan persiapan batin</t>
         </is>
       </c>
-      <c r="K13" s="53" t="inlineStr">
+      <c r="K13" s="52" t="inlineStr">
         <is>
           <t>MP4 (video berkualitas untuk presentasi dan konten video)</t>
         </is>
       </c>
-      <c r="L13" s="53" t="inlineStr">
+      <c r="L13" s="52" t="inlineStr">
         <is>
           <t>Desain perlu diperbaiki: gunakan maksimal 2-4 warna utama dan 2-3 jenis font agar terbaca dengan baik</t>
         </is>
       </c>
-      <c r="M13" s="53" t="inlineStr">
+      <c r="M13" s="52" t="inlineStr">
         <is>
           <t>Pengaturan resolusi layar monitor</t>
         </is>
       </c>
-      <c r="N13" s="54" t="inlineStr">
+      <c r="N13" s="53" t="inlineStr">
         <is>
           <t>Melanie Perkins, Cameron Adams, dan Mark Zuckerberg</t>
         </is>
       </c>
-      <c r="O13" s="54" t="inlineStr">
+      <c r="O13" s="53" t="inlineStr">
         <is>
           <t>Filter — sesuaikan tone warna gambar</t>
         </is>
       </c>
-      <c r="P13" s="54" t="inlineStr">
+      <c r="P13" s="53" t="inlineStr">
         <is>
           <t>1080 x 1920 px (Instagram Story)</t>
         </is>
       </c>
-      <c r="Q13" s="53" t="inlineStr">
+      <c r="Q13" s="52" t="inlineStr">
         <is>
           <t>Inovasi tanpa batas dalam setiap desain</t>
         </is>
       </c>
-      <c r="R13" s="53" t="inlineStr">
+      <c r="R13" s="52" t="inlineStr">
         <is>
           <t>Login → Pilih menu Template → Pilih jenis desain → Cari template → Klik 'Gunakan template ini'</t>
         </is>
       </c>
-      <c r="S13" s="54" t="inlineStr">
+      <c r="S13" s="53" t="inlineStr">
         <is>
           <t>Download desain lalu kirim via email beserta catatan revisi</t>
         </is>
       </c>
-      <c r="T13" s="54" t="inlineStr">
+      <c r="T13" s="53" t="inlineStr">
         <is>
           <t>Memanfaatkan fitur AI Canva untuk menghasilkan konten yang membangun dan menginspirasi</t>
         </is>
       </c>
-      <c r="U13" s="54" t="inlineStr">
+      <c r="U13" s="53" t="inlineStr">
         <is>
           <t>Kombinasi tiga warna yang membentuk segitiga pada roda warna</t>
         </is>
       </c>
-      <c r="V13" s="53" t="inlineStr">
+      <c r="V13" s="52" t="inlineStr">
         <is>
           <t>Canva adalah sarana untuk berkarya, berkomunikasi efektif, dan memberikan dampak positif bagi sesama</t>
         </is>
@@ -6374,107 +6371,107 @@
       <c r="A14" s="20" t="n">
         <v>10</v>
       </c>
-      <c r="B14" s="37" t="inlineStr">
+      <c r="B14" s="36" t="inlineStr">
         <is>
           <t>Marsia Sairina</t>
         </is>
       </c>
-      <c r="C14" s="53" t="inlineStr">
+      <c r="C14" s="52" t="inlineStr">
         <is>
           <t>Kolaborasi real-time dengan fitur edit bersama</t>
         </is>
       </c>
-      <c r="D14" s="54" t="inlineStr">
+      <c r="D14" s="53" t="inlineStr">
         <is>
           <t>Platform desain logo online berbayar</t>
         </is>
       </c>
-      <c r="E14" s="54" t="inlineStr">
+      <c r="E14" s="53" t="inlineStr">
         <is>
           <t>Gradien Warna</t>
         </is>
       </c>
-      <c r="F14" s="54" t="inlineStr">
+      <c r="F14" s="53" t="inlineStr">
         <is>
           <t>Gunakan warna kontras untuk menonjolkan elemen penting</t>
         </is>
       </c>
-      <c r="G14" s="53" t="inlineStr">
+      <c r="G14" s="52" t="inlineStr">
         <is>
           <t>Rp 95.000</t>
         </is>
       </c>
-      <c r="H14" s="53" t="inlineStr">
+      <c r="H14" s="52" t="inlineStr">
         <is>
           <t>PNG (kualitas tinggi, cocok untuk media sosial dan WhatsApp)</t>
         </is>
       </c>
-      <c r="I14" s="53" t="inlineStr">
+      <c r="I14" s="52" t="inlineStr">
         <is>
           <t>(1), (3), dan (4)</t>
         </is>
       </c>
-      <c r="J14" s="53" t="inlineStr">
+      <c r="J14" s="52" t="inlineStr">
         <is>
           <t>Pertobatan, penyesalan, kerendahan hati, dan persiapan batin</t>
         </is>
       </c>
-      <c r="K14" s="54" t="inlineStr">
+      <c r="K14" s="53" t="inlineStr">
         <is>
           <t>GIF (untuk animasi singkat)</t>
         </is>
       </c>
-      <c r="L14" s="54" t="inlineStr">
+      <c r="L14" s="53" t="inlineStr">
         <is>
           <t>Desain perlu diperbaiki hanya pada pemilihan warna, jumlah font sudah ideal</t>
         </is>
       </c>
-      <c r="M14" s="54" t="inlineStr">
+      <c r="M14" s="53" t="inlineStr">
         <is>
           <t>Unggahan file dari perangkat</t>
         </is>
       </c>
-      <c r="N14" s="54" t="inlineStr">
+      <c r="N14" s="53" t="inlineStr">
         <is>
           <t>Melanie Perkins, Cameron Adams, dan Mark Zuckerberg</t>
         </is>
       </c>
-      <c r="O14" s="53" t="inlineStr">
+      <c r="O14" s="52" t="inlineStr">
         <is>
           <t>Eyedropper — ambil warna dari elemen/foto</t>
         </is>
       </c>
-      <c r="P14" s="54" t="inlineStr">
+      <c r="P14" s="53" t="inlineStr">
         <is>
           <t>1280 x 720 px (YouTube Thumbnail)</t>
         </is>
       </c>
-      <c r="Q14" s="53" t="inlineStr">
+      <c r="Q14" s="52" t="inlineStr">
         <is>
           <t>Inovasi tanpa batas dalam setiap desain</t>
         </is>
       </c>
-      <c r="R14" s="54" t="inlineStr">
+      <c r="R14" s="53" t="inlineStr">
         <is>
           <t>Login → Pilih menu Unggahan → Import Template → Gunakan</t>
         </is>
       </c>
-      <c r="S14" s="54" t="inlineStr">
+      <c r="S14" s="53" t="inlineStr">
         <is>
           <t>Download desain lalu kirim via email beserta catatan revisi</t>
         </is>
       </c>
-      <c r="T14" s="54" t="inlineStr">
+      <c r="T14" s="53" t="inlineStr">
         <is>
           <t>Memanfaatkan fitur AI Canva untuk menghasilkan konten yang membangun dan menginspirasi</t>
         </is>
       </c>
-      <c r="U14" s="54" t="inlineStr">
+      <c r="U14" s="53" t="inlineStr">
         <is>
           <t>Kombinasi tiga warna yang membentuk segitiga pada roda warna</t>
         </is>
       </c>
-      <c r="V14" s="53" t="inlineStr">
+      <c r="V14" s="52" t="inlineStr">
         <is>
           <t>Canva adalah sarana untuk berkarya, berkomunikasi efektif, dan memberikan dampak positif bagi sesama</t>
         </is>
@@ -6484,107 +6481,107 @@
       <c r="A15" s="20" t="n">
         <v>11</v>
       </c>
-      <c r="B15" s="37" t="inlineStr">
+      <c r="B15" s="36" t="inlineStr">
         <is>
           <t>Silvya Runturambi</t>
         </is>
       </c>
-      <c r="C15" s="53" t="inlineStr">
+      <c r="C15" s="52" t="inlineStr">
         <is>
           <t>Kolaborasi real-time dengan fitur edit bersama</t>
         </is>
       </c>
-      <c r="D15" s="54" t="inlineStr">
+      <c r="D15" s="53" t="inlineStr">
         <is>
           <t>Layanan cetak undangan digital</t>
         </is>
       </c>
-      <c r="E15" s="54" t="inlineStr">
+      <c r="E15" s="53" t="inlineStr">
         <is>
           <t>Warna Elemen Manual</t>
         </is>
       </c>
-      <c r="F15" s="54" t="inlineStr">
+      <c r="F15" s="53" t="inlineStr">
         <is>
           <t>Gunakan warna kontras untuk menonjolkan elemen penting</t>
         </is>
       </c>
-      <c r="G15" s="54" t="inlineStr">
+      <c r="G15" s="53" t="inlineStr">
         <is>
           <t>Rp 75.000</t>
         </is>
       </c>
-      <c r="H15" s="53" t="inlineStr">
+      <c r="H15" s="52" t="inlineStr">
         <is>
           <t>PNG (kualitas tinggi, cocok untuk media sosial dan WhatsApp)</t>
         </is>
       </c>
-      <c r="I15" s="53" t="inlineStr">
+      <c r="I15" s="52" t="inlineStr">
         <is>
           <t>(1), (3), dan (4)</t>
         </is>
       </c>
-      <c r="J15" s="53" t="inlineStr">
+      <c r="J15" s="52" t="inlineStr">
         <is>
           <t>Pertobatan, penyesalan, kerendahan hati, dan persiapan batin</t>
         </is>
       </c>
-      <c r="K15" s="53" t="inlineStr">
+      <c r="K15" s="52" t="inlineStr">
         <is>
           <t>MP4 (video berkualitas untuk presentasi dan konten video)</t>
         </is>
       </c>
-      <c r="L15" s="53" t="inlineStr">
+      <c r="L15" s="52" t="inlineStr">
         <is>
           <t>Desain perlu diperbaiki: gunakan maksimal 2-4 warna utama dan 2-3 jenis font agar terbaca dengan baik</t>
         </is>
       </c>
-      <c r="M15" s="54" t="inlineStr">
+      <c r="M15" s="53" t="inlineStr">
         <is>
           <t>Unggahan file dari perangkat</t>
         </is>
       </c>
-      <c r="N15" s="53" t="inlineStr">
+      <c r="N15" s="52" t="inlineStr">
         <is>
           <t>Melanie Perkins, Cliff Obrecht, dan Cameron Adams</t>
         </is>
       </c>
-      <c r="O15" s="54" t="inlineStr">
+      <c r="O15" s="53" t="inlineStr">
         <is>
           <t>Filter — sesuaikan tone warna gambar</t>
         </is>
       </c>
-      <c r="P15" s="55" t="inlineStr">
+      <c r="P15" s="54" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="Q15" s="55" t="inlineStr">
+      <c r="Q15" s="54" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="R15" s="55" t="inlineStr">
+      <c r="R15" s="54" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="S15" s="55" t="inlineStr">
+      <c r="S15" s="54" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="T15" s="55" t="inlineStr">
+      <c r="T15" s="54" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="U15" s="55" t="inlineStr">
+      <c r="U15" s="54" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="V15" s="55" t="inlineStr">
+      <c r="V15" s="54" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -6594,107 +6591,107 @@
       <c r="A16" s="20" t="n">
         <v>12</v>
       </c>
-      <c r="B16" s="37" t="inlineStr">
+      <c r="B16" s="36" t="inlineStr">
         <is>
           <t>Maria</t>
         </is>
       </c>
-      <c r="C16" s="53" t="inlineStr">
+      <c r="C16" s="52" t="inlineStr">
         <is>
           <t>Kolaborasi real-time dengan fitur edit bersama</t>
         </is>
       </c>
-      <c r="D16" s="53" t="inlineStr">
+      <c r="D16" s="52" t="inlineStr">
         <is>
           <t>Bisnis buku tahunan sekolah bernama Fusion Books</t>
         </is>
       </c>
-      <c r="E16" s="54" t="inlineStr">
+      <c r="E16" s="53" t="inlineStr">
         <is>
           <t>Warna Elemen Manual</t>
         </is>
       </c>
-      <c r="F16" s="55" t="inlineStr">
+      <c r="F16" s="54" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G16" s="55" t="inlineStr">
+      <c r="G16" s="54" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H16" s="55" t="inlineStr">
+      <c r="H16" s="54" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I16" s="55" t="inlineStr">
+      <c r="I16" s="54" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J16" s="55" t="inlineStr">
+      <c r="J16" s="54" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K16" s="55" t="inlineStr">
+      <c r="K16" s="54" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="L16" s="55" t="inlineStr">
+      <c r="L16" s="54" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="M16" s="55" t="inlineStr">
+      <c r="M16" s="54" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="N16" s="55" t="inlineStr">
+      <c r="N16" s="54" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="O16" s="55" t="inlineStr">
+      <c r="O16" s="54" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="P16" s="55" t="inlineStr">
+      <c r="P16" s="54" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="Q16" s="55" t="inlineStr">
+      <c r="Q16" s="54" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="R16" s="55" t="inlineStr">
+      <c r="R16" s="54" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="S16" s="55" t="inlineStr">
+      <c r="S16" s="54" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="T16" s="55" t="inlineStr">
+      <c r="T16" s="54" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="U16" s="55" t="inlineStr">
+      <c r="U16" s="54" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="V16" s="55" t="inlineStr">
+      <c r="V16" s="54" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -6704,107 +6701,107 @@
       <c r="A17" s="20" t="n">
         <v>13</v>
       </c>
-      <c r="B17" s="37" t="inlineStr">
+      <c r="B17" s="36" t="inlineStr">
         <is>
           <t>Ivonne runturambi</t>
         </is>
       </c>
-      <c r="C17" s="54" t="inlineStr">
+      <c r="C17" s="53" t="inlineStr">
         <is>
           <t>Template berbagi pakai</t>
         </is>
       </c>
-      <c r="D17" s="53" t="inlineStr">
+      <c r="D17" s="52" t="inlineStr">
         <is>
           <t>Bisnis buku tahunan sekolah bernama Fusion Books</t>
         </is>
       </c>
-      <c r="E17" s="55" t="inlineStr">
+      <c r="E17" s="54" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F17" s="55" t="inlineStr">
+      <c r="F17" s="54" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G17" s="55" t="inlineStr">
+      <c r="G17" s="54" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H17" s="55" t="inlineStr">
+      <c r="H17" s="54" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I17" s="55" t="inlineStr">
+      <c r="I17" s="54" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J17" s="55" t="inlineStr">
+      <c r="J17" s="54" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K17" s="55" t="inlineStr">
+      <c r="K17" s="54" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="L17" s="55" t="inlineStr">
+      <c r="L17" s="54" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="M17" s="55" t="inlineStr">
+      <c r="M17" s="54" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="N17" s="55" t="inlineStr">
+      <c r="N17" s="54" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="O17" s="55" t="inlineStr">
+      <c r="O17" s="54" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="P17" s="55" t="inlineStr">
+      <c r="P17" s="54" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="Q17" s="55" t="inlineStr">
+      <c r="Q17" s="54" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="R17" s="55" t="inlineStr">
+      <c r="R17" s="54" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="S17" s="55" t="inlineStr">
+      <c r="S17" s="54" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="T17" s="55" t="inlineStr">
+      <c r="T17" s="54" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="U17" s="55" t="inlineStr">
+      <c r="U17" s="54" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="V17" s="55" t="inlineStr">
+      <c r="V17" s="54" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -6814,107 +6811,107 @@
       <c r="A18" s="20" t="n">
         <v>14</v>
       </c>
-      <c r="B18" s="37" t="inlineStr">
+      <c r="B18" s="36" t="inlineStr">
         <is>
           <t>Tintin tityn</t>
         </is>
       </c>
-      <c r="C18" s="55" t="inlineStr">
+      <c r="C18" s="54" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D18" s="55" t="inlineStr">
+      <c r="D18" s="54" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E18" s="55" t="inlineStr">
+      <c r="E18" s="54" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F18" s="55" t="inlineStr">
+      <c r="F18" s="54" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G18" s="55" t="inlineStr">
+      <c r="G18" s="54" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H18" s="55" t="inlineStr">
+      <c r="H18" s="54" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I18" s="55" t="inlineStr">
+      <c r="I18" s="54" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J18" s="55" t="inlineStr">
+      <c r="J18" s="54" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K18" s="55" t="inlineStr">
+      <c r="K18" s="54" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="L18" s="55" t="inlineStr">
+      <c r="L18" s="54" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="M18" s="55" t="inlineStr">
+      <c r="M18" s="54" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="N18" s="55" t="inlineStr">
+      <c r="N18" s="54" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="O18" s="55" t="inlineStr">
+      <c r="O18" s="54" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="P18" s="55" t="inlineStr">
+      <c r="P18" s="54" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="Q18" s="55" t="inlineStr">
+      <c r="Q18" s="54" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="R18" s="55" t="inlineStr">
+      <c r="R18" s="54" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="S18" s="55" t="inlineStr">
+      <c r="S18" s="54" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="T18" s="55" t="inlineStr">
+      <c r="T18" s="54" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="U18" s="55" t="inlineStr">
+      <c r="U18" s="54" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="V18" s="55" t="inlineStr">
+      <c r="V18" s="54" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -6924,107 +6921,107 @@
       <c r="A19" s="20" t="n">
         <v>15</v>
       </c>
-      <c r="B19" s="37" t="inlineStr">
+      <c r="B19" s="36" t="inlineStr">
         <is>
           <t>Yovita*</t>
         </is>
       </c>
-      <c r="C19" s="55" t="inlineStr">
+      <c r="C19" s="54" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D19" s="55" t="inlineStr">
+      <c r="D19" s="54" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E19" s="55" t="inlineStr">
+      <c r="E19" s="54" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F19" s="55" t="inlineStr">
+      <c r="F19" s="54" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G19" s="55" t="inlineStr">
+      <c r="G19" s="54" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H19" s="55" t="inlineStr">
+      <c r="H19" s="54" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I19" s="55" t="inlineStr">
+      <c r="I19" s="54" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J19" s="55" t="inlineStr">
+      <c r="J19" s="54" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K19" s="55" t="inlineStr">
+      <c r="K19" s="54" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="L19" s="55" t="inlineStr">
+      <c r="L19" s="54" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="M19" s="55" t="inlineStr">
+      <c r="M19" s="54" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="N19" s="55" t="inlineStr">
+      <c r="N19" s="54" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="O19" s="55" t="inlineStr">
+      <c r="O19" s="54" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="P19" s="55" t="inlineStr">
+      <c r="P19" s="54" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="Q19" s="55" t="inlineStr">
+      <c r="Q19" s="54" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="R19" s="55" t="inlineStr">
+      <c r="R19" s="54" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="S19" s="55" t="inlineStr">
+      <c r="S19" s="54" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="T19" s="55" t="inlineStr">
+      <c r="T19" s="54" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="U19" s="55" t="inlineStr">
+      <c r="U19" s="54" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="V19" s="55" t="inlineStr">
+      <c r="V19" s="54" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -8681,1216 +8678,1216 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="37" t="inlineStr">
+      <c r="A68" s="36" t="inlineStr">
         <is>
           <t>Agnes Nurak</t>
         </is>
       </c>
-      <c r="B68" s="56" t="n">
+      <c r="B68" s="55" t="n">
         <v>32</v>
       </c>
-      <c r="C68" s="56" t="n">
+      <c r="C68" s="55" t="n">
         <v>17</v>
       </c>
-      <c r="D68" s="56" t="n">
+      <c r="D68" s="55" t="n">
         <v>22</v>
       </c>
-      <c r="E68" s="56" t="n">
+      <c r="E68" s="55" t="n">
         <v>31</v>
       </c>
-      <c r="F68" s="56" t="n">
+      <c r="F68" s="55" t="n">
         <v>17</v>
       </c>
-      <c r="G68" s="56" t="n">
+      <c r="G68" s="55" t="n">
         <v>32</v>
       </c>
-      <c r="H68" s="56" t="n">
+      <c r="H68" s="55" t="n">
         <v>31</v>
       </c>
-      <c r="I68" s="56" t="n">
+      <c r="I68" s="55" t="n">
         <v>29</v>
       </c>
-      <c r="J68" s="56" t="n">
+      <c r="J68" s="55" t="n">
         <v>24</v>
       </c>
-      <c r="K68" s="56" t="n">
+      <c r="K68" s="55" t="n">
         <v>39</v>
       </c>
-      <c r="L68" s="56" t="n">
+      <c r="L68" s="55" t="n">
         <v>23</v>
       </c>
-      <c r="M68" s="56" t="n">
+      <c r="M68" s="55" t="n">
         <v>13</v>
       </c>
-      <c r="N68" s="56" t="n">
+      <c r="N68" s="55" t="n">
         <v>21</v>
       </c>
-      <c r="O68" s="56" t="n">
+      <c r="O68" s="55" t="n">
         <v>16</v>
       </c>
-      <c r="P68" s="56" t="n">
+      <c r="P68" s="55" t="n">
         <v>32</v>
       </c>
-      <c r="Q68" s="56" t="n">
+      <c r="Q68" s="55" t="n">
         <v>15</v>
       </c>
-      <c r="R68" s="56" t="n">
+      <c r="R68" s="55" t="n">
         <v>20</v>
       </c>
-      <c r="S68" s="56" t="n">
+      <c r="S68" s="55" t="n">
         <v>35</v>
       </c>
-      <c r="T68" s="56" t="n">
+      <c r="T68" s="55" t="n">
         <v>18</v>
       </c>
-      <c r="U68" s="56" t="n">
+      <c r="U68" s="55" t="n">
         <v>38</v>
       </c>
-      <c r="V68" s="57" t="n">
+      <c r="V68" s="56" t="n">
         <v>505</v>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="37" t="inlineStr">
+      <c r="A69" s="36" t="inlineStr">
         <is>
           <t>Mien</t>
         </is>
       </c>
-      <c r="B69" s="56" t="n">
+      <c r="B69" s="55" t="n">
         <v>38</v>
       </c>
-      <c r="C69" s="58" t="n">
+      <c r="C69" s="57" t="n">
         <v>51</v>
       </c>
-      <c r="D69" s="56" t="n">
+      <c r="D69" s="55" t="n">
         <v>29</v>
       </c>
-      <c r="E69" s="56" t="n">
+      <c r="E69" s="55" t="n">
         <v>31</v>
       </c>
-      <c r="F69" s="56" t="n">
+      <c r="F69" s="55" t="n">
         <v>35</v>
       </c>
-      <c r="G69" s="58" t="n">
+      <c r="G69" s="57" t="n">
         <v>66</v>
       </c>
-      <c r="H69" s="58" t="n">
+      <c r="H69" s="57" t="n">
         <v>60</v>
       </c>
-      <c r="I69" s="58" t="n">
+      <c r="I69" s="57" t="n">
         <v>64</v>
       </c>
-      <c r="J69" s="56" t="n">
+      <c r="J69" s="55" t="n">
         <v>37</v>
       </c>
-      <c r="K69" s="58" t="n">
+      <c r="K69" s="57" t="n">
         <v>57</v>
       </c>
-      <c r="L69" s="56" t="n">
+      <c r="L69" s="55" t="n">
         <v>34</v>
       </c>
-      <c r="M69" s="58" t="n">
+      <c r="M69" s="57" t="n">
         <v>62</v>
       </c>
-      <c r="N69" s="56" t="n">
+      <c r="N69" s="55" t="n">
         <v>32</v>
       </c>
-      <c r="O69" s="56" t="n">
+      <c r="O69" s="55" t="n">
         <v>23</v>
       </c>
-      <c r="P69" s="56" t="n">
+      <c r="P69" s="55" t="n">
         <v>35</v>
       </c>
-      <c r="Q69" s="56" t="n">
+      <c r="Q69" s="55" t="n">
         <v>33</v>
       </c>
-      <c r="R69" s="56" t="n">
+      <c r="R69" s="55" t="n">
         <v>22</v>
       </c>
-      <c r="S69" s="58" t="n">
+      <c r="S69" s="57" t="n">
         <v>46</v>
       </c>
-      <c r="T69" s="58" t="n">
+      <c r="T69" s="57" t="n">
         <v>53</v>
       </c>
-      <c r="U69" s="58" t="n">
+      <c r="U69" s="57" t="n">
         <v>50</v>
       </c>
-      <c r="V69" s="57" t="n">
+      <c r="V69" s="56" t="n">
         <v>858</v>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="37" t="inlineStr">
+      <c r="A70" s="36" t="inlineStr">
         <is>
           <t>LESLY MARCHRITH NUSALY</t>
         </is>
       </c>
-      <c r="B70" s="56" t="n">
+      <c r="B70" s="55" t="n">
         <v>13</v>
       </c>
-      <c r="C70" s="56" t="n">
+      <c r="C70" s="55" t="n">
         <v>9</v>
       </c>
-      <c r="D70" s="56" t="n">
+      <c r="D70" s="55" t="n">
         <v>11</v>
       </c>
-      <c r="E70" s="56" t="n">
+      <c r="E70" s="55" t="n">
         <v>19</v>
       </c>
-      <c r="F70" s="59" t="n">
+      <c r="F70" s="58" t="n">
         <v>5</v>
       </c>
-      <c r="G70" s="56" t="n">
+      <c r="G70" s="55" t="n">
         <v>9</v>
       </c>
-      <c r="H70" s="56" t="n">
+      <c r="H70" s="55" t="n">
         <v>13</v>
       </c>
-      <c r="I70" s="56" t="n">
+      <c r="I70" s="55" t="n">
         <v>7</v>
       </c>
-      <c r="J70" s="56" t="n">
+      <c r="J70" s="55" t="n">
         <v>12</v>
       </c>
-      <c r="K70" s="56" t="n">
+      <c r="K70" s="55" t="n">
         <v>16</v>
       </c>
-      <c r="L70" s="56" t="n">
+      <c r="L70" s="55" t="n">
         <v>12</v>
       </c>
-      <c r="M70" s="56" t="n">
+      <c r="M70" s="55" t="n">
         <v>16</v>
       </c>
-      <c r="N70" s="56" t="n">
+      <c r="N70" s="55" t="n">
         <v>23</v>
       </c>
-      <c r="O70" s="56" t="n">
+      <c r="O70" s="55" t="n">
         <v>12</v>
       </c>
-      <c r="P70" s="56" t="n">
+      <c r="P70" s="55" t="n">
         <v>8</v>
       </c>
-      <c r="Q70" s="56" t="n">
+      <c r="Q70" s="55" t="n">
         <v>32</v>
       </c>
-      <c r="R70" s="56" t="n">
+      <c r="R70" s="55" t="n">
         <v>11</v>
       </c>
-      <c r="S70" s="56" t="n">
+      <c r="S70" s="55" t="n">
         <v>12</v>
       </c>
-      <c r="T70" s="56" t="n">
+      <c r="T70" s="55" t="n">
         <v>17</v>
       </c>
-      <c r="U70" s="56" t="n">
+      <c r="U70" s="55" t="n">
         <v>11</v>
       </c>
-      <c r="V70" s="57" t="n">
+      <c r="V70" s="56" t="n">
         <v>268</v>
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="37" t="inlineStr">
+      <c r="A71" s="36" t="inlineStr">
         <is>
           <t>Gerarda Ina</t>
         </is>
       </c>
-      <c r="B71" s="56" t="n">
+      <c r="B71" s="55" t="n">
         <v>31</v>
       </c>
-      <c r="C71" s="56" t="n">
+      <c r="C71" s="55" t="n">
         <v>40</v>
       </c>
-      <c r="D71" s="58" t="n">
+      <c r="D71" s="57" t="n">
         <v>66</v>
       </c>
-      <c r="E71" s="58" t="n">
+      <c r="E71" s="57" t="n">
         <v>67</v>
       </c>
-      <c r="F71" s="56" t="n">
+      <c r="F71" s="55" t="n">
         <v>6</v>
       </c>
-      <c r="G71" s="58" t="n">
+      <c r="G71" s="57" t="n">
         <v>45</v>
       </c>
-      <c r="H71" s="58" t="n">
+      <c r="H71" s="57" t="n">
         <v>49</v>
       </c>
-      <c r="I71" s="56" t="n">
+      <c r="I71" s="55" t="n">
         <v>14</v>
       </c>
-      <c r="J71" s="56" t="n">
+      <c r="J71" s="55" t="n">
         <v>38</v>
       </c>
-      <c r="K71" s="58" t="n">
+      <c r="K71" s="57" t="n">
         <v>66</v>
       </c>
-      <c r="L71" s="56" t="n">
+      <c r="L71" s="55" t="n">
         <v>27</v>
       </c>
-      <c r="M71" s="56" t="n">
+      <c r="M71" s="55" t="n">
         <v>31</v>
       </c>
-      <c r="N71" s="56" t="n">
+      <c r="N71" s="55" t="n">
         <v>19</v>
       </c>
-      <c r="O71" s="56" t="n">
+      <c r="O71" s="55" t="n">
         <v>42</v>
       </c>
-      <c r="P71" s="58" t="n">
+      <c r="P71" s="57" t="n">
         <v>132</v>
       </c>
-      <c r="Q71" s="56" t="n">
+      <c r="Q71" s="55" t="n">
         <v>23</v>
       </c>
-      <c r="R71" s="58" t="n">
+      <c r="R71" s="57" t="n">
         <v>343</v>
       </c>
-      <c r="S71" s="56" t="n">
+      <c r="S71" s="55" t="n">
         <v>30</v>
       </c>
-      <c r="T71" s="56" t="n">
+      <c r="T71" s="55" t="n">
         <v>31</v>
       </c>
-      <c r="U71" s="56" t="n">
+      <c r="U71" s="55" t="n">
         <v>21</v>
       </c>
-      <c r="V71" s="57" t="n">
+      <c r="V71" s="56" t="n">
         <v>1121</v>
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="37" t="inlineStr">
+      <c r="A72" s="36" t="inlineStr">
         <is>
           <t>Mirza Caroline</t>
         </is>
       </c>
-      <c r="B72" s="56" t="n">
+      <c r="B72" s="55" t="n">
         <v>19</v>
       </c>
-      <c r="C72" s="56" t="n">
+      <c r="C72" s="55" t="n">
         <v>15</v>
       </c>
-      <c r="D72" s="56" t="n">
+      <c r="D72" s="55" t="n">
         <v>20</v>
       </c>
-      <c r="E72" s="58" t="n">
+      <c r="E72" s="57" t="n">
         <v>45</v>
       </c>
-      <c r="F72" s="56" t="n">
+      <c r="F72" s="55" t="n">
         <v>11</v>
       </c>
-      <c r="G72" s="56" t="n">
+      <c r="G72" s="55" t="n">
         <v>22</v>
       </c>
-      <c r="H72" s="56" t="n">
+      <c r="H72" s="55" t="n">
         <v>24</v>
       </c>
-      <c r="I72" s="56" t="n">
+      <c r="I72" s="55" t="n">
         <v>11</v>
       </c>
-      <c r="J72" s="56" t="n">
+      <c r="J72" s="55" t="n">
         <v>25</v>
       </c>
-      <c r="K72" s="56" t="n">
+      <c r="K72" s="55" t="n">
         <v>43</v>
       </c>
-      <c r="L72" s="56" t="n">
+      <c r="L72" s="55" t="n">
         <v>13</v>
       </c>
-      <c r="M72" s="56" t="n">
+      <c r="M72" s="55" t="n">
         <v>10</v>
       </c>
-      <c r="N72" s="56" t="n">
+      <c r="N72" s="55" t="n">
         <v>25</v>
       </c>
-      <c r="O72" s="56" t="n">
+      <c r="O72" s="55" t="n">
         <v>19</v>
       </c>
-      <c r="P72" s="56" t="n">
+      <c r="P72" s="55" t="n">
         <v>24</v>
       </c>
-      <c r="Q72" s="56" t="n">
+      <c r="Q72" s="55" t="n">
         <v>21</v>
       </c>
-      <c r="R72" s="56" t="n">
+      <c r="R72" s="55" t="n">
         <v>17</v>
       </c>
-      <c r="S72" s="56" t="n">
+      <c r="S72" s="55" t="n">
         <v>26</v>
       </c>
-      <c r="T72" s="56" t="n">
+      <c r="T72" s="55" t="n">
         <v>18</v>
       </c>
-      <c r="U72" s="56" t="n">
+      <c r="U72" s="55" t="n">
         <v>14</v>
       </c>
-      <c r="V72" s="57" t="n">
+      <c r="V72" s="56" t="n">
         <v>422</v>
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="37" t="inlineStr">
+      <c r="A73" s="36" t="inlineStr">
         <is>
           <t>wisye pangalila</t>
         </is>
       </c>
-      <c r="B73" s="56" t="n">
+      <c r="B73" s="55" t="n">
         <v>18</v>
       </c>
-      <c r="C73" s="56" t="n">
+      <c r="C73" s="55" t="n">
         <v>17</v>
       </c>
-      <c r="D73" s="56" t="n">
+      <c r="D73" s="55" t="n">
         <v>23</v>
       </c>
-      <c r="E73" s="56" t="n">
+      <c r="E73" s="55" t="n">
         <v>29</v>
       </c>
-      <c r="F73" s="56" t="n">
+      <c r="F73" s="55" t="n">
         <v>12</v>
       </c>
-      <c r="G73" s="56" t="n">
+      <c r="G73" s="55" t="n">
         <v>9</v>
       </c>
-      <c r="H73" s="56" t="n">
+      <c r="H73" s="55" t="n">
         <v>16</v>
       </c>
-      <c r="I73" s="56" t="n">
+      <c r="I73" s="55" t="n">
         <v>27</v>
       </c>
-      <c r="J73" s="56" t="n">
+      <c r="J73" s="55" t="n">
         <v>15</v>
       </c>
-      <c r="K73" s="56" t="n">
+      <c r="K73" s="55" t="n">
         <v>41</v>
       </c>
-      <c r="L73" s="56" t="n">
+      <c r="L73" s="55" t="n">
         <v>37</v>
       </c>
-      <c r="M73" s="56" t="n">
+      <c r="M73" s="55" t="n">
         <v>28</v>
       </c>
-      <c r="N73" s="56" t="n">
+      <c r="N73" s="55" t="n">
         <v>14</v>
       </c>
-      <c r="O73" s="56" t="n">
+      <c r="O73" s="55" t="n">
         <v>14</v>
       </c>
-      <c r="P73" s="58" t="n">
+      <c r="P73" s="57" t="n">
         <v>47</v>
       </c>
-      <c r="Q73" s="56" t="n">
+      <c r="Q73" s="55" t="n">
         <v>15</v>
       </c>
-      <c r="R73" s="56" t="n">
+      <c r="R73" s="55" t="n">
         <v>24</v>
       </c>
-      <c r="S73" s="56" t="n">
+      <c r="S73" s="55" t="n">
         <v>15</v>
       </c>
-      <c r="T73" s="58" t="n">
+      <c r="T73" s="57" t="n">
         <v>70</v>
       </c>
-      <c r="U73" s="56" t="n">
+      <c r="U73" s="55" t="n">
         <v>18</v>
       </c>
-      <c r="V73" s="57" t="n">
+      <c r="V73" s="56" t="n">
         <v>489</v>
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="37" t="inlineStr">
+      <c r="A74" s="36" t="inlineStr">
         <is>
           <t>Yovita</t>
         </is>
       </c>
-      <c r="B74" s="58" t="n">
+      <c r="B74" s="57" t="n">
         <v>47</v>
       </c>
-      <c r="C74" s="56" t="n">
+      <c r="C74" s="55" t="n">
         <v>26</v>
       </c>
-      <c r="D74" s="56" t="n">
+      <c r="D74" s="55" t="n">
         <v>28</v>
       </c>
-      <c r="E74" s="58" t="n">
+      <c r="E74" s="57" t="n">
         <v>62</v>
       </c>
-      <c r="F74" s="56" t="n">
+      <c r="F74" s="55" t="n">
         <v>20</v>
       </c>
-      <c r="G74" s="56" t="n">
+      <c r="G74" s="55" t="n">
         <v>24</v>
       </c>
-      <c r="H74" s="56" t="n">
+      <c r="H74" s="55" t="n">
         <v>26</v>
       </c>
-      <c r="I74" s="58" t="n">
+      <c r="I74" s="57" t="n">
         <v>57</v>
       </c>
-      <c r="J74" s="56" t="n">
+      <c r="J74" s="55" t="n">
         <v>32</v>
       </c>
-      <c r="K74" s="58" t="n">
+      <c r="K74" s="57" t="n">
         <v>100</v>
       </c>
-      <c r="L74" s="56" t="n">
+      <c r="L74" s="55" t="n">
         <v>39</v>
       </c>
-      <c r="M74" s="56" t="n">
+      <c r="M74" s="55" t="n">
         <v>42</v>
       </c>
-      <c r="N74" s="56" t="n">
+      <c r="N74" s="55" t="n">
         <v>32</v>
       </c>
-      <c r="O74" s="56" t="n">
+      <c r="O74" s="55" t="n">
         <v>30</v>
       </c>
-      <c r="P74" s="58" t="n">
+      <c r="P74" s="57" t="n">
         <v>69</v>
       </c>
-      <c r="Q74" s="58" t="n">
+      <c r="Q74" s="57" t="n">
         <v>69</v>
       </c>
-      <c r="R74" s="58" t="n">
+      <c r="R74" s="57" t="n">
         <v>78</v>
       </c>
-      <c r="S74" s="56" t="n">
+      <c r="S74" s="55" t="n">
         <v>38</v>
       </c>
-      <c r="T74" s="56" t="n">
+      <c r="T74" s="55" t="n">
         <v>42</v>
       </c>
-      <c r="U74" s="56" t="n">
+      <c r="U74" s="55" t="n">
         <v>29</v>
       </c>
-      <c r="V74" s="57" t="n">
+      <c r="V74" s="56" t="n">
         <v>890</v>
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="37" t="inlineStr">
+      <c r="A75" s="36" t="inlineStr">
         <is>
           <t>Netty Nusaly</t>
         </is>
       </c>
-      <c r="B75" s="56" t="n">
+      <c r="B75" s="55" t="n">
         <v>12</v>
       </c>
-      <c r="C75" s="56" t="n">
+      <c r="C75" s="55" t="n">
         <v>9</v>
       </c>
-      <c r="D75" s="56" t="n">
+      <c r="D75" s="55" t="n">
         <v>23</v>
       </c>
-      <c r="E75" s="56" t="n">
+      <c r="E75" s="55" t="n">
         <v>21</v>
       </c>
-      <c r="F75" s="56" t="n">
+      <c r="F75" s="55" t="n">
         <v>16</v>
       </c>
-      <c r="G75" s="56" t="n">
+      <c r="G75" s="55" t="n">
         <v>29</v>
       </c>
-      <c r="H75" s="56" t="n">
+      <c r="H75" s="55" t="n">
         <v>41</v>
       </c>
-      <c r="I75" s="56" t="n">
+      <c r="I75" s="55" t="n">
         <v>22</v>
       </c>
-      <c r="J75" s="56" t="n">
+      <c r="J75" s="55" t="n">
         <v>15</v>
       </c>
-      <c r="K75" s="56" t="n">
+      <c r="K75" s="55" t="n">
         <v>31</v>
       </c>
-      <c r="L75" s="56" t="n">
+      <c r="L75" s="55" t="n">
         <v>37</v>
       </c>
-      <c r="M75" s="56" t="n">
+      <c r="M75" s="55" t="n">
         <v>33</v>
       </c>
-      <c r="N75" s="56" t="n">
+      <c r="N75" s="55" t="n">
         <v>24</v>
       </c>
-      <c r="O75" s="56" t="n">
+      <c r="O75" s="55" t="n">
         <v>35</v>
       </c>
-      <c r="P75" s="56" t="n">
+      <c r="P75" s="55" t="n">
         <v>26</v>
       </c>
-      <c r="Q75" s="56" t="n">
+      <c r="Q75" s="55" t="n">
         <v>28</v>
       </c>
-      <c r="R75" s="56" t="n">
+      <c r="R75" s="55" t="n">
         <v>27</v>
       </c>
-      <c r="S75" s="56" t="n">
+      <c r="S75" s="55" t="n">
         <v>32</v>
       </c>
-      <c r="T75" s="56" t="n">
+      <c r="T75" s="55" t="n">
         <v>33</v>
       </c>
-      <c r="U75" s="56" t="n">
+      <c r="U75" s="55" t="n">
         <v>26</v>
       </c>
-      <c r="V75" s="57" t="n">
+      <c r="V75" s="56" t="n">
         <v>520</v>
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="37" t="inlineStr">
+      <c r="A76" s="36" t="inlineStr">
         <is>
           <t>Ivo Emelia</t>
         </is>
       </c>
-      <c r="B76" s="56" t="n">
+      <c r="B76" s="55" t="n">
         <v>43</v>
       </c>
-      <c r="C76" s="56" t="n">
+      <c r="C76" s="55" t="n">
         <v>28</v>
       </c>
-      <c r="D76" s="56" t="n">
+      <c r="D76" s="55" t="n">
         <v>13</v>
       </c>
-      <c r="E76" s="56" t="n">
+      <c r="E76" s="55" t="n">
         <v>26</v>
       </c>
-      <c r="F76" s="56" t="n">
+      <c r="F76" s="55" t="n">
         <v>7</v>
       </c>
-      <c r="G76" s="56" t="n">
+      <c r="G76" s="55" t="n">
         <v>19</v>
       </c>
-      <c r="H76" s="56" t="n">
+      <c r="H76" s="55" t="n">
         <v>25</v>
       </c>
-      <c r="I76" s="56" t="n">
+      <c r="I76" s="55" t="n">
         <v>16</v>
       </c>
-      <c r="J76" s="56" t="n">
+      <c r="J76" s="55" t="n">
         <v>13</v>
       </c>
-      <c r="K76" s="56" t="n">
+      <c r="K76" s="55" t="n">
         <v>31</v>
       </c>
-      <c r="L76" s="56" t="n">
+      <c r="L76" s="55" t="n">
         <v>14</v>
       </c>
-      <c r="M76" s="56" t="n">
+      <c r="M76" s="55" t="n">
         <v>39</v>
       </c>
-      <c r="N76" s="56" t="n">
+      <c r="N76" s="55" t="n">
         <v>19</v>
       </c>
-      <c r="O76" s="56" t="n">
+      <c r="O76" s="55" t="n">
         <v>35</v>
       </c>
-      <c r="P76" s="58" t="n">
+      <c r="P76" s="57" t="n">
         <v>57</v>
       </c>
-      <c r="Q76" s="56" t="n">
+      <c r="Q76" s="55" t="n">
         <v>41</v>
       </c>
-      <c r="R76" s="56" t="n">
+      <c r="R76" s="55" t="n">
         <v>29</v>
       </c>
-      <c r="S76" s="56" t="n">
+      <c r="S76" s="55" t="n">
         <v>31</v>
       </c>
-      <c r="T76" s="56" t="n">
+      <c r="T76" s="55" t="n">
         <v>31</v>
       </c>
-      <c r="U76" s="56" t="n">
+      <c r="U76" s="55" t="n">
         <v>26</v>
       </c>
-      <c r="V76" s="57" t="n">
+      <c r="V76" s="56" t="n">
         <v>543</v>
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="37" t="inlineStr">
+      <c r="A77" s="36" t="inlineStr">
         <is>
           <t>Marsia Sairina</t>
         </is>
       </c>
-      <c r="B77" s="56" t="n">
+      <c r="B77" s="55" t="n">
         <v>21</v>
       </c>
-      <c r="C77" s="56" t="n">
+      <c r="C77" s="55" t="n">
         <v>20</v>
       </c>
-      <c r="D77" s="56" t="n">
+      <c r="D77" s="55" t="n">
         <v>22</v>
       </c>
-      <c r="E77" s="56" t="n">
+      <c r="E77" s="55" t="n">
         <v>28</v>
       </c>
-      <c r="F77" s="56" t="n">
+      <c r="F77" s="55" t="n">
         <v>16</v>
       </c>
-      <c r="G77" s="56" t="n">
+      <c r="G77" s="55" t="n">
         <v>23</v>
       </c>
-      <c r="H77" s="56" t="n">
+      <c r="H77" s="55" t="n">
         <v>31</v>
       </c>
-      <c r="I77" s="56" t="n">
+      <c r="I77" s="55" t="n">
         <v>22</v>
       </c>
-      <c r="J77" s="56" t="n">
+      <c r="J77" s="55" t="n">
         <v>21</v>
       </c>
-      <c r="K77" s="58" t="n">
+      <c r="K77" s="57" t="n">
         <v>56</v>
       </c>
-      <c r="L77" s="56" t="n">
+      <c r="L77" s="55" t="n">
         <v>38</v>
       </c>
-      <c r="M77" s="56" t="n">
+      <c r="M77" s="55" t="n">
         <v>28</v>
       </c>
-      <c r="N77" s="56" t="n">
+      <c r="N77" s="55" t="n">
         <v>33</v>
       </c>
-      <c r="O77" s="56" t="n">
+      <c r="O77" s="55" t="n">
         <v>28</v>
       </c>
-      <c r="P77" s="56" t="n">
+      <c r="P77" s="55" t="n">
         <v>26</v>
       </c>
-      <c r="Q77" s="56" t="n">
+      <c r="Q77" s="55" t="n">
         <v>37</v>
       </c>
-      <c r="R77" s="56" t="n">
+      <c r="R77" s="55" t="n">
         <v>27</v>
       </c>
-      <c r="S77" s="56" t="n">
+      <c r="S77" s="55" t="n">
         <v>43</v>
       </c>
-      <c r="T77" s="56" t="n">
+      <c r="T77" s="55" t="n">
         <v>26</v>
       </c>
-      <c r="U77" s="56" t="n">
+      <c r="U77" s="55" t="n">
         <v>26</v>
       </c>
-      <c r="V77" s="57" t="n">
+      <c r="V77" s="56" t="n">
         <v>572</v>
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="37" t="inlineStr">
+      <c r="A78" s="36" t="inlineStr">
         <is>
           <t>Silvya Runturambi</t>
         </is>
       </c>
-      <c r="B78" s="56" t="n">
+      <c r="B78" s="55" t="n">
         <v>12</v>
       </c>
-      <c r="C78" s="56" t="n">
+      <c r="C78" s="55" t="n">
         <v>19</v>
       </c>
-      <c r="D78" s="58" t="n">
+      <c r="D78" s="57" t="n">
         <v>47</v>
       </c>
-      <c r="E78" s="56" t="n">
+      <c r="E78" s="55" t="n">
         <v>10</v>
       </c>
-      <c r="F78" s="56" t="n">
+      <c r="F78" s="55" t="n">
         <v>24</v>
       </c>
-      <c r="G78" s="58" t="n">
+      <c r="G78" s="57" t="n">
         <v>54</v>
       </c>
-      <c r="H78" s="58" t="n">
+      <c r="H78" s="57" t="n">
         <v>55</v>
       </c>
-      <c r="I78" s="56" t="n">
+      <c r="I78" s="55" t="n">
         <v>17</v>
       </c>
-      <c r="J78" s="56" t="n">
+      <c r="J78" s="55" t="n">
         <v>38</v>
       </c>
-      <c r="K78" s="58" t="n">
+      <c r="K78" s="57" t="n">
         <v>94</v>
       </c>
-      <c r="L78" s="58" t="n">
+      <c r="L78" s="57" t="n">
         <v>76</v>
       </c>
-      <c r="M78" s="58" t="n">
+      <c r="M78" s="57" t="n">
         <v>90</v>
       </c>
-      <c r="N78" s="58" t="n">
+      <c r="N78" s="57" t="n">
         <v>94</v>
       </c>
-      <c r="O78" s="60" t="inlineStr">
+      <c r="O78" s="59" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="P78" s="60" t="inlineStr">
+      <c r="P78" s="59" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="Q78" s="60" t="inlineStr">
+      <c r="Q78" s="59" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="R78" s="60" t="inlineStr">
+      <c r="R78" s="59" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="S78" s="60" t="inlineStr">
+      <c r="S78" s="59" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="T78" s="60" t="inlineStr">
+      <c r="T78" s="59" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="U78" s="60" t="inlineStr">
+      <c r="U78" s="59" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="V78" s="57" t="n">
+      <c r="V78" s="56" t="n">
         <v>630</v>
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="37" t="inlineStr">
+      <c r="A79" s="36" t="inlineStr">
         <is>
           <t>Maria</t>
         </is>
       </c>
-      <c r="B79" s="56" t="n">
+      <c r="B79" s="55" t="n">
         <v>8</v>
       </c>
-      <c r="C79" s="56" t="n">
+      <c r="C79" s="55" t="n">
         <v>11</v>
       </c>
-      <c r="D79" s="56" t="n">
+      <c r="D79" s="55" t="n">
         <v>24</v>
       </c>
-      <c r="E79" s="60" t="inlineStr">
+      <c r="E79" s="59" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F79" s="60" t="inlineStr">
+      <c r="F79" s="59" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G79" s="60" t="inlineStr">
+      <c r="G79" s="59" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H79" s="60" t="inlineStr">
+      <c r="H79" s="59" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I79" s="60" t="inlineStr">
+      <c r="I79" s="59" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J79" s="60" t="inlineStr">
+      <c r="J79" s="59" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K79" s="60" t="inlineStr">
+      <c r="K79" s="59" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="L79" s="60" t="inlineStr">
+      <c r="L79" s="59" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="M79" s="60" t="inlineStr">
+      <c r="M79" s="59" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="N79" s="60" t="inlineStr">
+      <c r="N79" s="59" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="O79" s="60" t="inlineStr">
+      <c r="O79" s="59" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="P79" s="60" t="inlineStr">
+      <c r="P79" s="59" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="Q79" s="60" t="inlineStr">
+      <c r="Q79" s="59" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="R79" s="60" t="inlineStr">
+      <c r="R79" s="59" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="S79" s="60" t="inlineStr">
+      <c r="S79" s="59" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="T79" s="60" t="inlineStr">
+      <c r="T79" s="59" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="U79" s="60" t="inlineStr">
+      <c r="U79" s="59" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="V79" s="57" t="n">
+      <c r="V79" s="56" t="n">
         <v>43</v>
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="37" t="inlineStr">
+      <c r="A80" s="36" t="inlineStr">
         <is>
           <t>Ivonne runturambi</t>
         </is>
       </c>
-      <c r="B80" s="56" t="n">
+      <c r="B80" s="55" t="n">
         <v>21</v>
       </c>
-      <c r="C80" s="56" t="n">
+      <c r="C80" s="55" t="n">
         <v>20</v>
       </c>
-      <c r="D80" s="60" t="inlineStr">
+      <c r="D80" s="59" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E80" s="60" t="inlineStr">
+      <c r="E80" s="59" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F80" s="60" t="inlineStr">
+      <c r="F80" s="59" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G80" s="60" t="inlineStr">
+      <c r="G80" s="59" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H80" s="60" t="inlineStr">
+      <c r="H80" s="59" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I80" s="60" t="inlineStr">
+      <c r="I80" s="59" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J80" s="60" t="inlineStr">
+      <c r="J80" s="59" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K80" s="60" t="inlineStr">
+      <c r="K80" s="59" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="L80" s="60" t="inlineStr">
+      <c r="L80" s="59" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="M80" s="60" t="inlineStr">
+      <c r="M80" s="59" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="N80" s="60" t="inlineStr">
+      <c r="N80" s="59" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="O80" s="60" t="inlineStr">
+      <c r="O80" s="59" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="P80" s="60" t="inlineStr">
+      <c r="P80" s="59" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="Q80" s="60" t="inlineStr">
+      <c r="Q80" s="59" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="R80" s="60" t="inlineStr">
+      <c r="R80" s="59" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="S80" s="60" t="inlineStr">
+      <c r="S80" s="59" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="T80" s="60" t="inlineStr">
+      <c r="T80" s="59" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="U80" s="60" t="inlineStr">
+      <c r="U80" s="59" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="V80" s="57" t="n">
+      <c r="V80" s="56" t="n">
         <v>41</v>
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="37" t="inlineStr">
+      <c r="A81" s="36" t="inlineStr">
         <is>
           <t>Tintin tityn</t>
         </is>
       </c>
-      <c r="B81" s="60" t="inlineStr">
+      <c r="B81" s="59" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="C81" s="60" t="inlineStr">
+      <c r="C81" s="59" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D81" s="60" t="inlineStr">
+      <c r="D81" s="59" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E81" s="60" t="inlineStr">
+      <c r="E81" s="59" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F81" s="60" t="inlineStr">
+      <c r="F81" s="59" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G81" s="60" t="inlineStr">
+      <c r="G81" s="59" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H81" s="60" t="inlineStr">
+      <c r="H81" s="59" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I81" s="60" t="inlineStr">
+      <c r="I81" s="59" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J81" s="60" t="inlineStr">
+      <c r="J81" s="59" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K81" s="60" t="inlineStr">
+      <c r="K81" s="59" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="L81" s="60" t="inlineStr">
+      <c r="L81" s="59" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="M81" s="60" t="inlineStr">
+      <c r="M81" s="59" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="N81" s="60" t="inlineStr">
+      <c r="N81" s="59" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="O81" s="60" t="inlineStr">
+      <c r="O81" s="59" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="P81" s="60" t="inlineStr">
+      <c r="P81" s="59" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="Q81" s="60" t="inlineStr">
+      <c r="Q81" s="59" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="R81" s="60" t="inlineStr">
+      <c r="R81" s="59" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="S81" s="60" t="inlineStr">
+      <c r="S81" s="59" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="T81" s="60" t="inlineStr">
+      <c r="T81" s="59" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="U81" s="60" t="inlineStr">
+      <c r="U81" s="59" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="V81" s="57" t="n">
+      <c r="V81" s="56" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="37" t="inlineStr">
+      <c r="A82" s="36" t="inlineStr">
         <is>
           <t>Yovita*</t>
         </is>
       </c>
-      <c r="B82" s="60" t="inlineStr">
+      <c r="B82" s="59" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="C82" s="60" t="inlineStr">
+      <c r="C82" s="59" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D82" s="60" t="inlineStr">
+      <c r="D82" s="59" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E82" s="60" t="inlineStr">
+      <c r="E82" s="59" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F82" s="60" t="inlineStr">
+      <c r="F82" s="59" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G82" s="60" t="inlineStr">
+      <c r="G82" s="59" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H82" s="60" t="inlineStr">
+      <c r="H82" s="59" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I82" s="60" t="inlineStr">
+      <c r="I82" s="59" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J82" s="60" t="inlineStr">
+      <c r="J82" s="59" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K82" s="60" t="inlineStr">
+      <c r="K82" s="59" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="L82" s="60" t="inlineStr">
+      <c r="L82" s="59" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="M82" s="60" t="inlineStr">
+      <c r="M82" s="59" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="N82" s="60" t="inlineStr">
+      <c r="N82" s="59" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="O82" s="60" t="inlineStr">
+      <c r="O82" s="59" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="P82" s="60" t="inlineStr">
+      <c r="P82" s="59" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="Q82" s="60" t="inlineStr">
+      <c r="Q82" s="59" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="R82" s="60" t="inlineStr">
+      <c r="R82" s="59" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="S82" s="60" t="inlineStr">
+      <c r="S82" s="59" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="T82" s="60" t="inlineStr">
+      <c r="T82" s="59" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="U82" s="60" t="inlineStr">
+      <c r="U82" s="59" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="V82" s="57" t="n">
+      <c r="V82" s="56" t="n">
         <v>0</v>
       </c>
     </row>
@@ -14088,7 +14085,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V82"/>
+  <dimension ref="A1:V83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -14174,36 +14171,42 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>Akurasi atas
-yang dijawab</t>
+          <t>Akurasi
+Wayground</t>
         </is>
       </c>
       <c r="I5" s="4" t="inlineStr">
         <is>
+          <t>Poin
+Wayground</t>
+        </is>
+      </c>
+      <c r="J5" s="4" t="inlineStr">
+        <is>
           <t>Waktu</t>
         </is>
       </c>
-      <c r="J5" s="4" t="inlineStr">
+      <c r="K5" s="4" t="inlineStr">
         <is>
           <t>Detik/butir</t>
         </is>
       </c>
-      <c r="K5" s="4" t="inlineStr">
+      <c r="L5" s="4" t="inlineStr">
         <is>
           <t>Skor pre-test</t>
         </is>
       </c>
-      <c r="L5" s="4" t="inlineStr">
+      <c r="M5" s="4" t="inlineStr">
         <is>
           <t>Gain</t>
         </is>
       </c>
-      <c r="M5" s="4" t="inlineStr">
+      <c r="N5" s="4" t="inlineStr">
         <is>
           <t>Status sesi</t>
         </is>
       </c>
-      <c r="N5" s="4" t="inlineStr">
+      <c r="O5" s="4" t="inlineStr">
         <is>
           <t>Kategori</t>
         </is>
@@ -14236,28 +14239,31 @@
       <c r="H6" s="6" t="n">
         <v>100</v>
       </c>
-      <c r="I6" s="6" t="inlineStr">
+      <c r="I6" s="16" t="n">
+        <v>12000</v>
+      </c>
+      <c r="J6" s="6" t="inlineStr">
         <is>
           <t>8:25</t>
         </is>
       </c>
-      <c r="J6" s="6" t="n">
+      <c r="K6" s="6" t="n">
         <v>25.2</v>
       </c>
-      <c r="K6" s="6" t="inlineStr">
+      <c r="L6" s="6" t="inlineStr">
         <is>
           <t>6/20</t>
         </is>
       </c>
-      <c r="L6" s="17" t="n">
+      <c r="M6" s="17" t="n">
         <v>14</v>
       </c>
-      <c r="M6" s="17" t="inlineStr">
+      <c r="N6" s="17" t="inlineStr">
         <is>
           <t>Tuntas</t>
         </is>
       </c>
-      <c r="N6" s="22" t="inlineStr">
+      <c r="O6" s="17" t="inlineStr">
         <is>
           <t>A Sangat Baik</t>
         </is>
@@ -14290,30 +14296,33 @@
       <c r="H7" s="6" t="n">
         <v>90</v>
       </c>
-      <c r="I7" s="6" t="inlineStr">
+      <c r="I7" s="16" t="n">
+        <v>10800</v>
+      </c>
+      <c r="J7" s="6" t="inlineStr">
         <is>
           <t>14:18</t>
         </is>
       </c>
-      <c r="J7" s="6" t="n">
+      <c r="K7" s="6" t="n">
         <v>42.9</v>
       </c>
-      <c r="K7" s="6" t="inlineStr">
+      <c r="L7" s="6" t="inlineStr">
         <is>
           <t>tidak ikut</t>
         </is>
       </c>
-      <c r="L7" s="6" t="inlineStr">
+      <c r="M7" s="6" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="M7" s="17" t="inlineStr">
+      <c r="N7" s="17" t="inlineStr">
         <is>
           <t>Tuntas</t>
         </is>
       </c>
-      <c r="N7" s="22" t="inlineStr">
+      <c r="O7" s="17" t="inlineStr">
         <is>
           <t>A Sangat Baik</t>
         </is>
@@ -14346,28 +14355,31 @@
       <c r="H8" s="6" t="n">
         <v>75</v>
       </c>
-      <c r="I8" s="6" t="inlineStr">
+      <c r="I8" s="16" t="n">
+        <v>9000</v>
+      </c>
+      <c r="J8" s="6" t="inlineStr">
         <is>
           <t>4:28</t>
         </is>
       </c>
-      <c r="J8" s="6" t="n">
+      <c r="K8" s="6" t="n">
         <v>13.4</v>
       </c>
-      <c r="K8" s="6" t="inlineStr">
+      <c r="L8" s="6" t="inlineStr">
         <is>
           <t>12/20</t>
         </is>
       </c>
-      <c r="L8" s="17" t="n">
+      <c r="M8" s="17" t="n">
         <v>3</v>
       </c>
-      <c r="M8" s="17" t="inlineStr">
+      <c r="N8" s="17" t="inlineStr">
         <is>
           <t>Tuntas</t>
         </is>
       </c>
-      <c r="N8" s="22" t="inlineStr">
+      <c r="O8" s="17" t="inlineStr">
         <is>
           <t>B Baik</t>
         </is>
@@ -14400,28 +14412,31 @@
       <c r="H9" s="6" t="n">
         <v>75</v>
       </c>
-      <c r="I9" s="6" t="inlineStr">
+      <c r="I9" s="16" t="n">
+        <v>9000</v>
+      </c>
+      <c r="J9" s="6" t="inlineStr">
         <is>
           <t>18:41</t>
         </is>
       </c>
-      <c r="J9" s="6" t="n">
+      <c r="K9" s="6" t="n">
         <v>56</v>
       </c>
-      <c r="K9" s="6" t="inlineStr">
+      <c r="L9" s="6" t="inlineStr">
         <is>
           <t>12/20</t>
         </is>
       </c>
-      <c r="L9" s="17" t="n">
+      <c r="M9" s="17" t="n">
         <v>3</v>
       </c>
-      <c r="M9" s="17" t="inlineStr">
+      <c r="N9" s="17" t="inlineStr">
         <is>
           <t>Tuntas</t>
         </is>
       </c>
-      <c r="N9" s="22" t="inlineStr">
+      <c r="O9" s="17" t="inlineStr">
         <is>
           <t>B Baik</t>
         </is>
@@ -14454,28 +14469,31 @@
       <c r="H10" s="6" t="n">
         <v>70</v>
       </c>
-      <c r="I10" s="6" t="inlineStr">
+      <c r="I10" s="16" t="n">
+        <v>8400</v>
+      </c>
+      <c r="J10" s="6" t="inlineStr">
         <is>
           <t>7:02</t>
         </is>
       </c>
-      <c r="J10" s="6" t="n">
+      <c r="K10" s="6" t="n">
         <v>21.1</v>
       </c>
-      <c r="K10" s="6" t="inlineStr">
+      <c r="L10" s="6" t="inlineStr">
         <is>
           <t>9/20</t>
         </is>
       </c>
-      <c r="L10" s="17" t="n">
+      <c r="M10" s="17" t="n">
         <v>5</v>
       </c>
-      <c r="M10" s="17" t="inlineStr">
+      <c r="N10" s="17" t="inlineStr">
         <is>
           <t>Tuntas</t>
         </is>
       </c>
-      <c r="N10" s="22" t="inlineStr">
+      <c r="O10" s="17" t="inlineStr">
         <is>
           <t>B Baik</t>
         </is>
@@ -14508,28 +14526,31 @@
       <c r="H11" s="6" t="n">
         <v>70</v>
       </c>
-      <c r="I11" s="6" t="inlineStr">
+      <c r="I11" s="16" t="n">
+        <v>8400</v>
+      </c>
+      <c r="J11" s="6" t="inlineStr">
         <is>
           <t>8:09</t>
         </is>
       </c>
-      <c r="J11" s="6" t="n">
+      <c r="K11" s="6" t="n">
         <v>24.4</v>
       </c>
-      <c r="K11" s="6" t="inlineStr">
+      <c r="L11" s="6" t="inlineStr">
         <is>
           <t>8/20</t>
         </is>
       </c>
-      <c r="L11" s="17" t="n">
+      <c r="M11" s="17" t="n">
         <v>6</v>
       </c>
-      <c r="M11" s="17" t="inlineStr">
+      <c r="N11" s="17" t="inlineStr">
         <is>
           <t>Tuntas</t>
         </is>
       </c>
-      <c r="N11" s="22" t="inlineStr">
+      <c r="O11" s="17" t="inlineStr">
         <is>
           <t>B Baik</t>
         </is>
@@ -14562,28 +14583,31 @@
       <c r="H12" s="6" t="n">
         <v>65</v>
       </c>
-      <c r="I12" s="6" t="inlineStr">
+      <c r="I12" s="16" t="n">
+        <v>7800</v>
+      </c>
+      <c r="J12" s="6" t="inlineStr">
         <is>
           <t>14:50</t>
         </is>
       </c>
-      <c r="J12" s="6" t="n">
+      <c r="K12" s="6" t="n">
         <v>44.5</v>
       </c>
-      <c r="K12" s="6" t="inlineStr">
+      <c r="L12" s="6" t="inlineStr">
         <is>
           <t>10/20</t>
         </is>
       </c>
-      <c r="L12" s="17" t="n">
+      <c r="M12" s="17" t="n">
         <v>3</v>
       </c>
-      <c r="M12" s="17" t="inlineStr">
+      <c r="N12" s="17" t="inlineStr">
         <is>
           <t>Tuntas</t>
         </is>
       </c>
-      <c r="N12" s="36" t="inlineStr">
+      <c r="O12" s="26" t="inlineStr">
         <is>
           <t>C Cukup</t>
         </is>
@@ -14616,30 +14640,33 @@
       <c r="H13" s="6" t="n">
         <v>60</v>
       </c>
-      <c r="I13" s="6" t="inlineStr">
+      <c r="I13" s="16" t="n">
+        <v>7200</v>
+      </c>
+      <c r="J13" s="6" t="inlineStr">
         <is>
           <t>8:40</t>
         </is>
       </c>
-      <c r="J13" s="6" t="n">
+      <c r="K13" s="6" t="n">
         <v>26</v>
       </c>
-      <c r="K13" s="6" t="inlineStr">
+      <c r="L13" s="6" t="inlineStr">
         <is>
           <t>tidak ikut</t>
         </is>
       </c>
-      <c r="L13" s="6" t="inlineStr">
+      <c r="M13" s="6" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="M13" s="17" t="inlineStr">
+      <c r="N13" s="17" t="inlineStr">
         <is>
           <t>Tuntas</t>
         </is>
       </c>
-      <c r="N13" s="36" t="inlineStr">
+      <c r="O13" s="26" t="inlineStr">
         <is>
           <t>C Cukup</t>
         </is>
@@ -14672,28 +14699,31 @@
       <c r="H14" s="6" t="n">
         <v>50</v>
       </c>
-      <c r="I14" s="6" t="inlineStr">
+      <c r="I14" s="16" t="n">
+        <v>6000</v>
+      </c>
+      <c r="J14" s="6" t="inlineStr">
         <is>
           <t>9:03</t>
         </is>
       </c>
-      <c r="J14" s="6" t="n">
+      <c r="K14" s="6" t="n">
         <v>27.1</v>
       </c>
-      <c r="K14" s="6" t="inlineStr">
+      <c r="L14" s="6" t="inlineStr">
         <is>
           <t>6/20</t>
         </is>
       </c>
-      <c r="L14" s="17" t="n">
+      <c r="M14" s="17" t="n">
         <v>4</v>
       </c>
-      <c r="M14" s="17" t="inlineStr">
+      <c r="N14" s="17" t="inlineStr">
         <is>
           <t>Tuntas</t>
         </is>
       </c>
-      <c r="N14" s="36" t="inlineStr">
+      <c r="O14" s="26" t="inlineStr">
         <is>
           <t>D Kurang</t>
         </is>
@@ -14726,28 +14756,31 @@
       <c r="H15" s="6" t="n">
         <v>40</v>
       </c>
-      <c r="I15" s="6" t="inlineStr">
+      <c r="I15" s="16" t="n">
+        <v>4800</v>
+      </c>
+      <c r="J15" s="6" t="inlineStr">
         <is>
           <t>9:32</t>
         </is>
       </c>
-      <c r="J15" s="6" t="n">
+      <c r="K15" s="6" t="n">
         <v>28.6</v>
       </c>
-      <c r="K15" s="6" t="inlineStr">
+      <c r="L15" s="6" t="inlineStr">
         <is>
           <t>6/20</t>
         </is>
       </c>
-      <c r="L15" s="17" t="n">
+      <c r="M15" s="17" t="n">
         <v>2</v>
       </c>
-      <c r="M15" s="17" t="inlineStr">
+      <c r="N15" s="17" t="inlineStr">
         <is>
           <t>Tuntas</t>
         </is>
       </c>
-      <c r="N15" s="36" t="inlineStr">
+      <c r="O15" s="26" t="inlineStr">
         <is>
           <t>D Kurang</t>
         </is>
@@ -14778,32 +14811,35 @@
         <v>35</v>
       </c>
       <c r="H16" s="6" t="n">
-        <v>54</v>
-      </c>
-      <c r="I16" s="6" t="inlineStr">
+        <v>35</v>
+      </c>
+      <c r="I16" s="16" t="n">
+        <v>4300</v>
+      </c>
+      <c r="J16" s="6" t="inlineStr">
         <is>
           <t>10:30</t>
         </is>
       </c>
-      <c r="J16" s="6" t="n">
+      <c r="K16" s="6" t="n">
         <v>48.5</v>
       </c>
-      <c r="K16" s="6" t="inlineStr">
+      <c r="L16" s="6" t="inlineStr">
         <is>
           <t>tidak ikut</t>
         </is>
       </c>
-      <c r="L16" s="6" t="inlineStr">
+      <c r="M16" s="6" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="M16" s="28" t="inlineStr">
+      <c r="N16" s="28" t="inlineStr">
         <is>
           <t>Terputus (13/20)</t>
         </is>
       </c>
-      <c r="N16" s="23" t="inlineStr">
+      <c r="O16" s="28" t="inlineStr">
         <is>
           <t>E Sangat Kurang</t>
         </is>
@@ -14834,30 +14870,33 @@
         <v>10</v>
       </c>
       <c r="H17" s="6" t="n">
-        <v>67</v>
-      </c>
-      <c r="I17" s="6" t="inlineStr">
+        <v>10</v>
+      </c>
+      <c r="I17" s="16" t="n">
+        <v>1200</v>
+      </c>
+      <c r="J17" s="6" t="inlineStr">
         <is>
           <t>0:43</t>
         </is>
       </c>
-      <c r="J17" s="6" t="n">
+      <c r="K17" s="6" t="n">
         <v>14.3</v>
       </c>
-      <c r="K17" s="6" t="inlineStr">
+      <c r="L17" s="6" t="inlineStr">
         <is>
           <t>6/20</t>
         </is>
       </c>
-      <c r="L17" s="28" t="n">
+      <c r="M17" s="28" t="n">
         <v>-4</v>
       </c>
-      <c r="M17" s="28" t="inlineStr">
+      <c r="N17" s="28" t="inlineStr">
         <is>
           <t>Terputus (3/20)</t>
         </is>
       </c>
-      <c r="N17" s="23" t="inlineStr">
+      <c r="O17" s="28" t="inlineStr">
         <is>
           <t>E Sangat Kurang</t>
         </is>
@@ -14888,30 +14927,33 @@
         <v>5</v>
       </c>
       <c r="H18" s="6" t="n">
-        <v>50</v>
-      </c>
-      <c r="I18" s="6" t="inlineStr">
+        <v>5</v>
+      </c>
+      <c r="I18" s="16" t="n">
+        <v>600</v>
+      </c>
+      <c r="J18" s="6" t="inlineStr">
         <is>
           <t>0:41</t>
         </is>
       </c>
-      <c r="J18" s="6" t="n">
+      <c r="K18" s="6" t="n">
         <v>20.5</v>
       </c>
-      <c r="K18" s="6" t="inlineStr">
+      <c r="L18" s="6" t="inlineStr">
         <is>
           <t>2/20</t>
         </is>
       </c>
-      <c r="L18" s="28" t="n">
+      <c r="M18" s="28" t="n">
         <v>-1</v>
       </c>
-      <c r="M18" s="28" t="inlineStr">
+      <c r="N18" s="28" t="inlineStr">
         <is>
           <t>Terputus (2/20)</t>
         </is>
       </c>
-      <c r="N18" s="23" t="inlineStr">
+      <c r="O18" s="28" t="inlineStr">
         <is>
           <t>E Sangat Kurang</t>
         </is>
@@ -14944,28 +14986,31 @@
       <c r="H19" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="I19" s="6" t="inlineStr">
+      <c r="I19" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" s="6" t="inlineStr">
         <is>
           <t>0:00</t>
         </is>
       </c>
-      <c r="J19" s="6" t="n">
+      <c r="K19" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="K19" s="6" t="inlineStr">
+      <c r="L19" s="6" t="inlineStr">
         <is>
           <t>7/20</t>
         </is>
       </c>
-      <c r="L19" s="28" t="n">
+      <c r="M19" s="28" t="n">
         <v>-7</v>
       </c>
-      <c r="M19" s="28" t="inlineStr">
+      <c r="N19" s="28" t="inlineStr">
         <is>
           <t>Terputus (0/20)</t>
         </is>
       </c>
-      <c r="N19" s="23" t="inlineStr">
+      <c r="O19" s="28" t="inlineStr">
         <is>
           <t>E Sangat Kurang</t>
         </is>
@@ -14998,28 +15043,31 @@
       <c r="H20" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="I20" s="6" t="inlineStr">
+      <c r="I20" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" s="6" t="inlineStr">
         <is>
           <t>0:00</t>
         </is>
       </c>
-      <c r="J20" s="6" t="n">
+      <c r="K20" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="K20" s="6" t="inlineStr">
+      <c r="L20" s="6" t="inlineStr">
         <is>
           <t>10/20</t>
         </is>
       </c>
-      <c r="L20" s="28" t="n">
+      <c r="M20" s="28" t="n">
         <v>-10</v>
       </c>
-      <c r="M20" s="28" t="inlineStr">
+      <c r="N20" s="28" t="inlineStr">
         <is>
           <t>Terputus (0/20)</t>
         </is>
       </c>
-      <c r="N20" s="23" t="inlineStr">
+      <c r="O20" s="28" t="inlineStr">
         <is>
           <t>E Sangat Kurang</t>
         </is>
@@ -15145,1394 +15193,1394 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="37" t="inlineStr">
+      <c r="A24" s="36" t="inlineStr">
         <is>
           <t>Agnes Nurak</t>
         </is>
       </c>
-      <c r="B24" s="38" t="inlineStr">
+      <c r="B24" s="37" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="C24" s="38" t="inlineStr">
+      <c r="C24" s="37" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="D24" s="38" t="inlineStr">
+      <c r="D24" s="37" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="E24" s="38" t="inlineStr">
+      <c r="E24" s="37" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="F24" s="38" t="inlineStr">
+      <c r="F24" s="37" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="G24" s="38" t="inlineStr">
+      <c r="G24" s="37" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="H24" s="38" t="inlineStr">
+      <c r="H24" s="37" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="I24" s="38" t="inlineStr">
+      <c r="I24" s="37" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="J24" s="38" t="inlineStr">
+      <c r="J24" s="37" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="K24" s="38" t="inlineStr">
+      <c r="K24" s="37" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="L24" s="38" t="inlineStr">
+      <c r="L24" s="37" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="M24" s="38" t="inlineStr">
+      <c r="M24" s="37" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="N24" s="38" t="inlineStr">
+      <c r="N24" s="37" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="O24" s="38" t="inlineStr">
+      <c r="O24" s="37" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="P24" s="38" t="inlineStr">
+      <c r="P24" s="37" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="Q24" s="38" t="inlineStr">
+      <c r="Q24" s="37" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="R24" s="38" t="inlineStr">
+      <c r="R24" s="37" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="S24" s="38" t="inlineStr">
+      <c r="S24" s="37" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="T24" s="38" t="inlineStr">
+      <c r="T24" s="37" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="U24" s="38" t="inlineStr">
+      <c r="U24" s="37" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="V24" s="39" t="n">
+      <c r="V24" s="38" t="n">
         <v>20</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="37" t="inlineStr">
+      <c r="A25" s="36" t="inlineStr">
         <is>
           <t>Mien</t>
         </is>
       </c>
-      <c r="B25" s="38" t="inlineStr">
+      <c r="B25" s="37" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="C25" s="40" t="inlineStr">
+      <c r="C25" s="39" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="D25" s="38" t="inlineStr">
+      <c r="D25" s="37" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="E25" s="38" t="inlineStr">
+      <c r="E25" s="37" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="F25" s="38" t="inlineStr">
+      <c r="F25" s="37" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="G25" s="38" t="inlineStr">
+      <c r="G25" s="37" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="H25" s="38" t="inlineStr">
+      <c r="H25" s="37" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="I25" s="38" t="inlineStr">
+      <c r="I25" s="37" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="J25" s="38" t="inlineStr">
+      <c r="J25" s="37" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="K25" s="38" t="inlineStr">
+      <c r="K25" s="37" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="L25" s="38" t="inlineStr">
+      <c r="L25" s="37" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="M25" s="38" t="inlineStr">
+      <c r="M25" s="37" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="N25" s="38" t="inlineStr">
+      <c r="N25" s="37" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="O25" s="38" t="inlineStr">
+      <c r="O25" s="37" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="P25" s="40" t="inlineStr">
+      <c r="P25" s="39" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="Q25" s="38" t="inlineStr">
+      <c r="Q25" s="37" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="R25" s="38" t="inlineStr">
+      <c r="R25" s="37" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="S25" s="38" t="inlineStr">
+      <c r="S25" s="37" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="T25" s="38" t="inlineStr">
+      <c r="T25" s="37" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="U25" s="38" t="inlineStr">
+      <c r="U25" s="37" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="V25" s="39" t="n">
+      <c r="V25" s="38" t="n">
         <v>18</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="37" t="inlineStr">
+      <c r="A26" s="36" t="inlineStr">
         <is>
           <t>LESLY MARCHRITH NUSALY</t>
         </is>
       </c>
-      <c r="B26" s="38" t="inlineStr">
+      <c r="B26" s="37" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="C26" s="38" t="inlineStr">
+      <c r="C26" s="37" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="D26" s="40" t="inlineStr">
+      <c r="D26" s="39" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="E26" s="38" t="inlineStr">
+      <c r="E26" s="37" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="F26" s="38" t="inlineStr">
+      <c r="F26" s="37" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="G26" s="38" t="inlineStr">
+      <c r="G26" s="37" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="H26" s="38" t="inlineStr">
+      <c r="H26" s="37" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="I26" s="38" t="inlineStr">
+      <c r="I26" s="37" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="J26" s="38" t="inlineStr">
+      <c r="J26" s="37" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="K26" s="38" t="inlineStr">
+      <c r="K26" s="37" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="L26" s="40" t="inlineStr">
+      <c r="L26" s="39" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="M26" s="38" t="inlineStr">
+      <c r="M26" s="37" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="N26" s="38" t="inlineStr">
+      <c r="N26" s="37" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="O26" s="38" t="inlineStr">
+      <c r="O26" s="37" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="P26" s="40" t="inlineStr">
+      <c r="P26" s="39" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="Q26" s="40" t="inlineStr">
+      <c r="Q26" s="39" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="R26" s="40" t="inlineStr">
+      <c r="R26" s="39" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="S26" s="38" t="inlineStr">
+      <c r="S26" s="37" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="T26" s="38" t="inlineStr">
+      <c r="T26" s="37" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="U26" s="38" t="inlineStr">
+      <c r="U26" s="37" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="V26" s="39" t="n">
+      <c r="V26" s="38" t="n">
         <v>15</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="37" t="inlineStr">
+      <c r="A27" s="36" t="inlineStr">
         <is>
           <t>Gerarda Ina</t>
         </is>
       </c>
-      <c r="B27" s="38" t="inlineStr">
+      <c r="B27" s="37" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="C27" s="38" t="inlineStr">
+      <c r="C27" s="37" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="D27" s="38" t="inlineStr">
+      <c r="D27" s="37" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="E27" s="38" t="inlineStr">
+      <c r="E27" s="37" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="F27" s="38" t="inlineStr">
+      <c r="F27" s="37" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="G27" s="40" t="inlineStr">
+      <c r="G27" s="39" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="H27" s="38" t="inlineStr">
+      <c r="H27" s="37" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="I27" s="38" t="inlineStr">
+      <c r="I27" s="37" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="J27" s="38" t="inlineStr">
+      <c r="J27" s="37" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="K27" s="38" t="inlineStr">
+      <c r="K27" s="37" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="L27" s="40" t="inlineStr">
+      <c r="L27" s="39" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="M27" s="38" t="inlineStr">
+      <c r="M27" s="37" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="N27" s="40" t="inlineStr">
+      <c r="N27" s="39" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="O27" s="38" t="inlineStr">
+      <c r="O27" s="37" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="P27" s="38" t="inlineStr">
+      <c r="P27" s="37" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="Q27" s="38" t="inlineStr">
+      <c r="Q27" s="37" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="R27" s="40" t="inlineStr">
+      <c r="R27" s="39" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="S27" s="40" t="inlineStr">
+      <c r="S27" s="39" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="T27" s="38" t="inlineStr">
+      <c r="T27" s="37" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="U27" s="38" t="inlineStr">
+      <c r="U27" s="37" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="V27" s="39" t="n">
+      <c r="V27" s="38" t="n">
         <v>15</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="37" t="inlineStr">
+      <c r="A28" s="36" t="inlineStr">
         <is>
           <t>Mirza Caroline</t>
         </is>
       </c>
-      <c r="B28" s="38" t="inlineStr">
+      <c r="B28" s="37" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="C28" s="38" t="inlineStr">
+      <c r="C28" s="37" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="D28" s="40" t="inlineStr">
+      <c r="D28" s="39" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="E28" s="38" t="inlineStr">
+      <c r="E28" s="37" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="F28" s="38" t="inlineStr">
+      <c r="F28" s="37" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="G28" s="38" t="inlineStr">
+      <c r="G28" s="37" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="H28" s="40" t="inlineStr">
+      <c r="H28" s="39" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="I28" s="38" t="inlineStr">
+      <c r="I28" s="37" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="J28" s="38" t="inlineStr">
+      <c r="J28" s="37" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="K28" s="38" t="inlineStr">
+      <c r="K28" s="37" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="L28" s="40" t="inlineStr">
+      <c r="L28" s="39" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="M28" s="38" t="inlineStr">
+      <c r="M28" s="37" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="N28" s="38" t="inlineStr">
+      <c r="N28" s="37" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="O28" s="38" t="inlineStr">
+      <c r="O28" s="37" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="P28" s="38" t="inlineStr">
+      <c r="P28" s="37" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="Q28" s="40" t="inlineStr">
+      <c r="Q28" s="39" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="R28" s="40" t="inlineStr">
+      <c r="R28" s="39" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="S28" s="38" t="inlineStr">
+      <c r="S28" s="37" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="T28" s="40" t="inlineStr">
+      <c r="T28" s="39" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="U28" s="38" t="inlineStr">
+      <c r="U28" s="37" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="V28" s="39" t="n">
+      <c r="V28" s="38" t="n">
         <v>14</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="37" t="inlineStr">
+      <c r="A29" s="36" t="inlineStr">
         <is>
           <t>wisye pangalila</t>
         </is>
       </c>
-      <c r="B29" s="40" t="inlineStr">
+      <c r="B29" s="39" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="C29" s="40" t="inlineStr">
+      <c r="C29" s="39" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="D29" s="40" t="inlineStr">
+      <c r="D29" s="39" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="E29" s="38" t="inlineStr">
+      <c r="E29" s="37" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="F29" s="40" t="inlineStr">
+      <c r="F29" s="39" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="G29" s="38" t="inlineStr">
+      <c r="G29" s="37" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="H29" s="38" t="inlineStr">
+      <c r="H29" s="37" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="I29" s="38" t="inlineStr">
+      <c r="I29" s="37" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="J29" s="38" t="inlineStr">
+      <c r="J29" s="37" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="K29" s="40" t="inlineStr">
+      <c r="K29" s="39" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="L29" s="38" t="inlineStr">
+      <c r="L29" s="37" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="M29" s="38" t="inlineStr">
+      <c r="M29" s="37" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="N29" s="38" t="inlineStr">
+      <c r="N29" s="37" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="O29" s="38" t="inlineStr">
+      <c r="O29" s="37" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="P29" s="38" t="inlineStr">
+      <c r="P29" s="37" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="Q29" s="38" t="inlineStr">
+      <c r="Q29" s="37" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="R29" s="40" t="inlineStr">
+      <c r="R29" s="39" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="S29" s="38" t="inlineStr">
+      <c r="S29" s="37" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="T29" s="38" t="inlineStr">
+      <c r="T29" s="37" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="U29" s="38" t="inlineStr">
+      <c r="U29" s="37" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="V29" s="39" t="n">
+      <c r="V29" s="38" t="n">
         <v>14</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="37" t="inlineStr">
+      <c r="A30" s="36" t="inlineStr">
         <is>
           <t>Yovita</t>
         </is>
       </c>
-      <c r="B30" s="40" t="inlineStr">
+      <c r="B30" s="39" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="C30" s="40" t="inlineStr">
+      <c r="C30" s="39" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="D30" s="38" t="inlineStr">
+      <c r="D30" s="37" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="E30" s="38" t="inlineStr">
+      <c r="E30" s="37" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="F30" s="38" t="inlineStr">
+      <c r="F30" s="37" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="G30" s="40" t="inlineStr">
+      <c r="G30" s="39" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="H30" s="38" t="inlineStr">
+      <c r="H30" s="37" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="I30" s="38" t="inlineStr">
+      <c r="I30" s="37" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="J30" s="40" t="inlineStr">
+      <c r="J30" s="39" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="K30" s="38" t="inlineStr">
+      <c r="K30" s="37" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="L30" s="38" t="inlineStr">
+      <c r="L30" s="37" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="M30" s="40" t="inlineStr">
+      <c r="M30" s="39" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="N30" s="38" t="inlineStr">
+      <c r="N30" s="37" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="O30" s="38" t="inlineStr">
+      <c r="O30" s="37" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="P30" s="38" t="inlineStr">
+      <c r="P30" s="37" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="Q30" s="40" t="inlineStr">
+      <c r="Q30" s="39" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="R30" s="40" t="inlineStr">
+      <c r="R30" s="39" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="S30" s="38" t="inlineStr">
+      <c r="S30" s="37" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="T30" s="38" t="inlineStr">
+      <c r="T30" s="37" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="U30" s="38" t="inlineStr">
+      <c r="U30" s="37" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="V30" s="39" t="n">
+      <c r="V30" s="38" t="n">
         <v>13</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="37" t="inlineStr">
+      <c r="A31" s="36" t="inlineStr">
         <is>
           <t>Netty Nusaly</t>
         </is>
       </c>
-      <c r="B31" s="38" t="inlineStr">
+      <c r="B31" s="37" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="C31" s="38" t="inlineStr">
+      <c r="C31" s="37" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="D31" s="40" t="inlineStr">
+      <c r="D31" s="39" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="E31" s="38" t="inlineStr">
+      <c r="E31" s="37" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="F31" s="40" t="inlineStr">
+      <c r="F31" s="39" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="G31" s="38" t="inlineStr">
+      <c r="G31" s="37" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="H31" s="40" t="inlineStr">
+      <c r="H31" s="39" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="I31" s="38" t="inlineStr">
+      <c r="I31" s="37" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="J31" s="38" t="inlineStr">
+      <c r="J31" s="37" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="K31" s="38" t="inlineStr">
+      <c r="K31" s="37" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="L31" s="40" t="inlineStr">
+      <c r="L31" s="39" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="M31" s="38" t="inlineStr">
+      <c r="M31" s="37" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="N31" s="38" t="inlineStr">
+      <c r="N31" s="37" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="O31" s="38" t="inlineStr">
+      <c r="O31" s="37" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="P31" s="40" t="inlineStr">
+      <c r="P31" s="39" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="Q31" s="40" t="inlineStr">
+      <c r="Q31" s="39" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="R31" s="40" t="inlineStr">
+      <c r="R31" s="39" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="S31" s="38" t="inlineStr">
+      <c r="S31" s="37" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="T31" s="40" t="inlineStr">
+      <c r="T31" s="39" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="U31" s="38" t="inlineStr">
+      <c r="U31" s="37" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="V31" s="39" t="n">
+      <c r="V31" s="38" t="n">
         <v>12</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="37" t="inlineStr">
+      <c r="A32" s="36" t="inlineStr">
         <is>
           <t>Ivo Emelia</t>
         </is>
       </c>
-      <c r="B32" s="38" t="inlineStr">
+      <c r="B32" s="37" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="C32" s="40" t="inlineStr">
+      <c r="C32" s="39" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="D32" s="40" t="inlineStr">
+      <c r="D32" s="39" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="E32" s="38" t="inlineStr">
+      <c r="E32" s="37" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="F32" s="40" t="inlineStr">
+      <c r="F32" s="39" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="G32" s="40" t="inlineStr">
+      <c r="G32" s="39" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="H32" s="38" t="inlineStr">
+      <c r="H32" s="37" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="I32" s="38" t="inlineStr">
+      <c r="I32" s="37" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="J32" s="38" t="inlineStr">
+      <c r="J32" s="37" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="K32" s="38" t="inlineStr">
+      <c r="K32" s="37" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="L32" s="38" t="inlineStr">
+      <c r="L32" s="37" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="M32" s="40" t="inlineStr">
+      <c r="M32" s="39" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="N32" s="40" t="inlineStr">
+      <c r="N32" s="39" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="O32" s="40" t="inlineStr">
+      <c r="O32" s="39" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="P32" s="38" t="inlineStr">
+      <c r="P32" s="37" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="Q32" s="38" t="inlineStr">
+      <c r="Q32" s="37" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="R32" s="40" t="inlineStr">
+      <c r="R32" s="39" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="S32" s="40" t="inlineStr">
+      <c r="S32" s="39" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="T32" s="40" t="inlineStr">
+      <c r="T32" s="39" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="U32" s="38" t="inlineStr">
+      <c r="U32" s="37" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="V32" s="39" t="n">
+      <c r="V32" s="38" t="n">
         <v>10</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="37" t="inlineStr">
+      <c r="A33" s="36" t="inlineStr">
         <is>
           <t>Marsia Sairina</t>
         </is>
       </c>
-      <c r="B33" s="38" t="inlineStr">
+      <c r="B33" s="37" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="C33" s="40" t="inlineStr">
+      <c r="C33" s="39" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="D33" s="40" t="inlineStr">
+      <c r="D33" s="39" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="E33" s="40" t="inlineStr">
+      <c r="E33" s="39" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="F33" s="38" t="inlineStr">
+      <c r="F33" s="37" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="G33" s="38" t="inlineStr">
+      <c r="G33" s="37" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="H33" s="38" t="inlineStr">
+      <c r="H33" s="37" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="I33" s="38" t="inlineStr">
+      <c r="I33" s="37" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="J33" s="40" t="inlineStr">
+      <c r="J33" s="39" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="K33" s="40" t="inlineStr">
+      <c r="K33" s="39" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="L33" s="40" t="inlineStr">
+      <c r="L33" s="39" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="M33" s="40" t="inlineStr">
+      <c r="M33" s="39" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="N33" s="38" t="inlineStr">
+      <c r="N33" s="37" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="O33" s="40" t="inlineStr">
+      <c r="O33" s="39" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="P33" s="38" t="inlineStr">
+      <c r="P33" s="37" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="Q33" s="40" t="inlineStr">
+      <c r="Q33" s="39" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="R33" s="40" t="inlineStr">
+      <c r="R33" s="39" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="S33" s="40" t="inlineStr">
+      <c r="S33" s="39" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="T33" s="40" t="inlineStr">
+      <c r="T33" s="39" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="U33" s="38" t="inlineStr">
+      <c r="U33" s="37" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="V33" s="39" t="n">
+      <c r="V33" s="38" t="n">
         <v>8</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="37" t="inlineStr">
+      <c r="A34" s="36" t="inlineStr">
         <is>
           <t>Silvya Runturambi</t>
         </is>
       </c>
-      <c r="B34" s="38" t="inlineStr">
+      <c r="B34" s="37" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="C34" s="40" t="inlineStr">
+      <c r="C34" s="39" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="D34" s="40" t="inlineStr">
+      <c r="D34" s="39" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="E34" s="40" t="inlineStr">
+      <c r="E34" s="39" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="F34" s="40" t="inlineStr">
+      <c r="F34" s="39" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="G34" s="38" t="inlineStr">
+      <c r="G34" s="37" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="H34" s="38" t="inlineStr">
+      <c r="H34" s="37" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="I34" s="38" t="inlineStr">
+      <c r="I34" s="37" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="J34" s="38" t="inlineStr">
+      <c r="J34" s="37" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="K34" s="38" t="inlineStr">
+      <c r="K34" s="37" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="L34" s="40" t="inlineStr">
+      <c r="L34" s="39" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="M34" s="38" t="inlineStr">
+      <c r="M34" s="37" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="N34" s="40" t="inlineStr">
+      <c r="N34" s="39" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="O34" s="41" t="inlineStr"/>
-      <c r="P34" s="41" t="inlineStr"/>
-      <c r="Q34" s="41" t="inlineStr"/>
-      <c r="R34" s="41" t="inlineStr"/>
-      <c r="S34" s="41" t="inlineStr"/>
-      <c r="T34" s="41" t="inlineStr"/>
-      <c r="U34" s="41" t="inlineStr"/>
-      <c r="V34" s="39" t="n">
+      <c r="O34" s="40" t="inlineStr"/>
+      <c r="P34" s="40" t="inlineStr"/>
+      <c r="Q34" s="40" t="inlineStr"/>
+      <c r="R34" s="40" t="inlineStr"/>
+      <c r="S34" s="40" t="inlineStr"/>
+      <c r="T34" s="40" t="inlineStr"/>
+      <c r="U34" s="40" t="inlineStr"/>
+      <c r="V34" s="38" t="n">
         <v>7</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="37" t="inlineStr">
+      <c r="A35" s="36" t="inlineStr">
         <is>
           <t>Maria</t>
         </is>
       </c>
-      <c r="B35" s="38" t="inlineStr">
+      <c r="B35" s="37" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="C35" s="38" t="inlineStr">
+      <c r="C35" s="37" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="D35" s="40" t="inlineStr">
+      <c r="D35" s="39" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="E35" s="41" t="inlineStr"/>
-      <c r="F35" s="41" t="inlineStr"/>
-      <c r="G35" s="41" t="inlineStr"/>
-      <c r="H35" s="41" t="inlineStr"/>
-      <c r="I35" s="41" t="inlineStr"/>
-      <c r="J35" s="41" t="inlineStr"/>
-      <c r="K35" s="41" t="inlineStr"/>
-      <c r="L35" s="41" t="inlineStr"/>
-      <c r="M35" s="41" t="inlineStr"/>
-      <c r="N35" s="41" t="inlineStr"/>
-      <c r="O35" s="41" t="inlineStr"/>
-      <c r="P35" s="41" t="inlineStr"/>
-      <c r="Q35" s="41" t="inlineStr"/>
-      <c r="R35" s="41" t="inlineStr"/>
-      <c r="S35" s="41" t="inlineStr"/>
-      <c r="T35" s="41" t="inlineStr"/>
-      <c r="U35" s="41" t="inlineStr"/>
-      <c r="V35" s="39" t="n">
+      <c r="E35" s="40" t="inlineStr"/>
+      <c r="F35" s="40" t="inlineStr"/>
+      <c r="G35" s="40" t="inlineStr"/>
+      <c r="H35" s="40" t="inlineStr"/>
+      <c r="I35" s="40" t="inlineStr"/>
+      <c r="J35" s="40" t="inlineStr"/>
+      <c r="K35" s="40" t="inlineStr"/>
+      <c r="L35" s="40" t="inlineStr"/>
+      <c r="M35" s="40" t="inlineStr"/>
+      <c r="N35" s="40" t="inlineStr"/>
+      <c r="O35" s="40" t="inlineStr"/>
+      <c r="P35" s="40" t="inlineStr"/>
+      <c r="Q35" s="40" t="inlineStr"/>
+      <c r="R35" s="40" t="inlineStr"/>
+      <c r="S35" s="40" t="inlineStr"/>
+      <c r="T35" s="40" t="inlineStr"/>
+      <c r="U35" s="40" t="inlineStr"/>
+      <c r="V35" s="38" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="37" t="inlineStr">
+      <c r="A36" s="36" t="inlineStr">
         <is>
           <t>Ivonne runturambi</t>
         </is>
       </c>
-      <c r="B36" s="40" t="inlineStr">
+      <c r="B36" s="39" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="C36" s="38" t="inlineStr">
+      <c r="C36" s="37" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="D36" s="41" t="inlineStr"/>
-      <c r="E36" s="41" t="inlineStr"/>
-      <c r="F36" s="41" t="inlineStr"/>
-      <c r="G36" s="41" t="inlineStr"/>
-      <c r="H36" s="41" t="inlineStr"/>
-      <c r="I36" s="41" t="inlineStr"/>
-      <c r="J36" s="41" t="inlineStr"/>
-      <c r="K36" s="41" t="inlineStr"/>
-      <c r="L36" s="41" t="inlineStr"/>
-      <c r="M36" s="41" t="inlineStr"/>
-      <c r="N36" s="41" t="inlineStr"/>
-      <c r="O36" s="41" t="inlineStr"/>
-      <c r="P36" s="41" t="inlineStr"/>
-      <c r="Q36" s="41" t="inlineStr"/>
-      <c r="R36" s="41" t="inlineStr"/>
-      <c r="S36" s="41" t="inlineStr"/>
-      <c r="T36" s="41" t="inlineStr"/>
-      <c r="U36" s="41" t="inlineStr"/>
-      <c r="V36" s="39" t="n">
+      <c r="D36" s="40" t="inlineStr"/>
+      <c r="E36" s="40" t="inlineStr"/>
+      <c r="F36" s="40" t="inlineStr"/>
+      <c r="G36" s="40" t="inlineStr"/>
+      <c r="H36" s="40" t="inlineStr"/>
+      <c r="I36" s="40" t="inlineStr"/>
+      <c r="J36" s="40" t="inlineStr"/>
+      <c r="K36" s="40" t="inlineStr"/>
+      <c r="L36" s="40" t="inlineStr"/>
+      <c r="M36" s="40" t="inlineStr"/>
+      <c r="N36" s="40" t="inlineStr"/>
+      <c r="O36" s="40" t="inlineStr"/>
+      <c r="P36" s="40" t="inlineStr"/>
+      <c r="Q36" s="40" t="inlineStr"/>
+      <c r="R36" s="40" t="inlineStr"/>
+      <c r="S36" s="40" t="inlineStr"/>
+      <c r="T36" s="40" t="inlineStr"/>
+      <c r="U36" s="40" t="inlineStr"/>
+      <c r="V36" s="38" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="37" t="inlineStr">
+      <c r="A37" s="36" t="inlineStr">
         <is>
           <t>Tintin tityn</t>
         </is>
       </c>
-      <c r="B37" s="41" t="inlineStr"/>
-      <c r="C37" s="41" t="inlineStr"/>
-      <c r="D37" s="41" t="inlineStr"/>
-      <c r="E37" s="41" t="inlineStr"/>
-      <c r="F37" s="41" t="inlineStr"/>
-      <c r="G37" s="41" t="inlineStr"/>
-      <c r="H37" s="41" t="inlineStr"/>
-      <c r="I37" s="41" t="inlineStr"/>
-      <c r="J37" s="41" t="inlineStr"/>
-      <c r="K37" s="41" t="inlineStr"/>
-      <c r="L37" s="41" t="inlineStr"/>
-      <c r="M37" s="41" t="inlineStr"/>
-      <c r="N37" s="41" t="inlineStr"/>
-      <c r="O37" s="41" t="inlineStr"/>
-      <c r="P37" s="41" t="inlineStr"/>
-      <c r="Q37" s="41" t="inlineStr"/>
-      <c r="R37" s="41" t="inlineStr"/>
-      <c r="S37" s="41" t="inlineStr"/>
-      <c r="T37" s="41" t="inlineStr"/>
-      <c r="U37" s="41" t="inlineStr"/>
-      <c r="V37" s="39" t="n">
+      <c r="B37" s="40" t="inlineStr"/>
+      <c r="C37" s="40" t="inlineStr"/>
+      <c r="D37" s="40" t="inlineStr"/>
+      <c r="E37" s="40" t="inlineStr"/>
+      <c r="F37" s="40" t="inlineStr"/>
+      <c r="G37" s="40" t="inlineStr"/>
+      <c r="H37" s="40" t="inlineStr"/>
+      <c r="I37" s="40" t="inlineStr"/>
+      <c r="J37" s="40" t="inlineStr"/>
+      <c r="K37" s="40" t="inlineStr"/>
+      <c r="L37" s="40" t="inlineStr"/>
+      <c r="M37" s="40" t="inlineStr"/>
+      <c r="N37" s="40" t="inlineStr"/>
+      <c r="O37" s="40" t="inlineStr"/>
+      <c r="P37" s="40" t="inlineStr"/>
+      <c r="Q37" s="40" t="inlineStr"/>
+      <c r="R37" s="40" t="inlineStr"/>
+      <c r="S37" s="40" t="inlineStr"/>
+      <c r="T37" s="40" t="inlineStr"/>
+      <c r="U37" s="40" t="inlineStr"/>
+      <c r="V37" s="38" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="37" t="inlineStr">
+      <c r="A38" s="36" t="inlineStr">
         <is>
           <t>Yovita*</t>
         </is>
       </c>
-      <c r="B38" s="41" t="inlineStr"/>
-      <c r="C38" s="41" t="inlineStr"/>
-      <c r="D38" s="41" t="inlineStr"/>
-      <c r="E38" s="41" t="inlineStr"/>
-      <c r="F38" s="41" t="inlineStr"/>
-      <c r="G38" s="41" t="inlineStr"/>
-      <c r="H38" s="41" t="inlineStr"/>
-      <c r="I38" s="41" t="inlineStr"/>
-      <c r="J38" s="41" t="inlineStr"/>
-      <c r="K38" s="41" t="inlineStr"/>
-      <c r="L38" s="41" t="inlineStr"/>
-      <c r="M38" s="41" t="inlineStr"/>
-      <c r="N38" s="41" t="inlineStr"/>
-      <c r="O38" s="41" t="inlineStr"/>
-      <c r="P38" s="41" t="inlineStr"/>
-      <c r="Q38" s="41" t="inlineStr"/>
-      <c r="R38" s="41" t="inlineStr"/>
-      <c r="S38" s="41" t="inlineStr"/>
-      <c r="T38" s="41" t="inlineStr"/>
-      <c r="U38" s="41" t="inlineStr"/>
-      <c r="V38" s="39" t="n">
+      <c r="B38" s="40" t="inlineStr"/>
+      <c r="C38" s="40" t="inlineStr"/>
+      <c r="D38" s="40" t="inlineStr"/>
+      <c r="E38" s="40" t="inlineStr"/>
+      <c r="F38" s="40" t="inlineStr"/>
+      <c r="G38" s="40" t="inlineStr"/>
+      <c r="H38" s="40" t="inlineStr"/>
+      <c r="I38" s="40" t="inlineStr"/>
+      <c r="J38" s="40" t="inlineStr"/>
+      <c r="K38" s="40" t="inlineStr"/>
+      <c r="L38" s="40" t="inlineStr"/>
+      <c r="M38" s="40" t="inlineStr"/>
+      <c r="N38" s="40" t="inlineStr"/>
+      <c r="O38" s="40" t="inlineStr"/>
+      <c r="P38" s="40" t="inlineStr"/>
+      <c r="Q38" s="40" t="inlineStr"/>
+      <c r="R38" s="40" t="inlineStr"/>
+      <c r="S38" s="40" t="inlineStr"/>
+      <c r="T38" s="40" t="inlineStr"/>
+      <c r="U38" s="40" t="inlineStr"/>
+      <c r="V38" s="38" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="37" t="inlineStr">
+      <c r="A39" s="36" t="inlineStr">
         <is>
           <t>Benar per butir</t>
         </is>
       </c>
-      <c r="B39" s="42" t="n">
+      <c r="B39" s="41" t="n">
         <v>10</v>
       </c>
-      <c r="C39" s="42" t="n">
+      <c r="C39" s="41" t="n">
         <v>7</v>
       </c>
-      <c r="D39" s="42" t="n">
+      <c r="D39" s="41" t="n">
         <v>4</v>
       </c>
-      <c r="E39" s="42" t="n">
+      <c r="E39" s="41" t="n">
         <v>9</v>
       </c>
-      <c r="F39" s="42" t="n">
+      <c r="F39" s="41" t="n">
         <v>7</v>
       </c>
-      <c r="G39" s="42" t="n">
+      <c r="G39" s="41" t="n">
         <v>8</v>
       </c>
-      <c r="H39" s="42" t="n">
+      <c r="H39" s="41" t="n">
         <v>9</v>
       </c>
-      <c r="I39" s="42" t="n">
+      <c r="I39" s="41" t="n">
         <v>11</v>
       </c>
-      <c r="J39" s="42" t="n">
+      <c r="J39" s="41" t="n">
         <v>9</v>
       </c>
-      <c r="K39" s="42" t="n">
+      <c r="K39" s="41" t="n">
         <v>9</v>
       </c>
-      <c r="L39" s="42" t="n">
+      <c r="L39" s="41" t="n">
         <v>5</v>
       </c>
-      <c r="M39" s="42" t="n">
+      <c r="M39" s="41" t="n">
         <v>8</v>
       </c>
-      <c r="N39" s="42" t="n">
+      <c r="N39" s="41" t="n">
         <v>8</v>
       </c>
-      <c r="O39" s="42" t="n">
+      <c r="O39" s="41" t="n">
         <v>8</v>
       </c>
-      <c r="P39" s="42" t="n">
+      <c r="P39" s="41" t="n">
         <v>7</v>
       </c>
-      <c r="Q39" s="42" t="n">
+      <c r="Q39" s="41" t="n">
         <v>5</v>
       </c>
-      <c r="R39" s="42" t="n">
+      <c r="R39" s="41" t="n">
         <v>2</v>
       </c>
-      <c r="S39" s="42" t="n">
+      <c r="S39" s="41" t="n">
         <v>7</v>
       </c>
-      <c r="T39" s="42" t="n">
+      <c r="T39" s="41" t="n">
         <v>6</v>
       </c>
-      <c r="U39" s="42" t="n">
+      <c r="U39" s="41" t="n">
         <v>10</v>
       </c>
-      <c r="V39" s="39" t="n">
+      <c r="V39" s="38" t="n">
         <v>149</v>
       </c>
     </row>
@@ -16832,22 +16880,30 @@
     <row r="81" ht="44" customHeight="1">
       <c r="A81" s="15" t="inlineStr">
         <is>
-          <t>Korelasi waktu pengerjaan dengan jumlah benar pada sesi tuntas hanya r = 0,115 — praktis nol. Mengerjakan lebih lama tidak menghasilkan skor lebih tinggi. Dalam mode take-home tiga hari, waktu tercatat tidak lagi menjadi ukuran usaha yang bermakna.</t>
+          <t>Kolom Akurasi dan Poin Wayground disalin apa adanya dari sheet Participant Data ekspor resmi, disertakan agar setiap angka pada laporan ini dapat dicocokkan langsung ke berkas sumber. Poin Wayground memuat bonus kecepatan, sehingga peringkat poin TIDAK sama dengan peringkat kemampuan. Seluruh analisis akademik pada workbook ini memakai jumlah jawaban benar, bukan poin.</t>
         </is>
       </c>
     </row>
     <row r="82" ht="44" customHeight="1">
       <c r="A82" s="15" t="inlineStr">
         <is>
+          <t>Korelasi waktu pengerjaan dengan jumlah benar pada sesi tuntas hanya r = 0,115 — praktis nol. Mengerjakan lebih lama tidak menghasilkan skor lebih tinggi. Dalam mode take-home tiga hari, waktu tercatat tidak lagi menjadi ukuran usaha yang bermakna.</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" ht="44" customHeight="1">
+      <c r="A83" s="15" t="inlineStr">
+        <is>
           <t>Empat peserta post-test tidak mengikuti pre-test: Mien (18 benar), Netty Nusaly (12), Silvya Runturambi (7, sesi terputus). Nilai mereka tidak dapat dipakai untuk mengukur dampak pelatihan karena tidak ada titik awal pembanding.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="9">
+  <mergeCells count="10">
     <mergeCell ref="A80:N80"/>
     <mergeCell ref="A79:N79"/>
     <mergeCell ref="A22:N22"/>
+    <mergeCell ref="A83:N83"/>
     <mergeCell ref="A4:N4"/>
     <mergeCell ref="A2:N2"/>
     <mergeCell ref="A82:N82"/>
@@ -16953,16 +17009,16 @@
 d) [MATI]  Brand Kit tim  — 0 pemilih</t>
         </is>
       </c>
-      <c r="D5" s="43" t="n">
+      <c r="D5" s="42" t="n">
         <v>0.67</v>
       </c>
-      <c r="E5" s="43" t="n">
+      <c r="E5" s="42" t="n">
         <v>0.75</v>
       </c>
-      <c r="F5" s="43" t="n">
+      <c r="F5" s="42" t="n">
         <v>0.48</v>
       </c>
-      <c r="G5" s="44" t="inlineStr">
+      <c r="G5" s="43" t="inlineStr">
         <is>
           <t>1 dari 3</t>
         </is>
@@ -16990,16 +17046,16 @@
 d) Layanan cetak undangan digital  — 1 pemilih</t>
         </is>
       </c>
-      <c r="D6" s="43" t="n">
+      <c r="D6" s="42" t="n">
         <v>0.47</v>
       </c>
-      <c r="E6" s="43" t="n">
+      <c r="E6" s="42" t="n">
         <v>0.25</v>
       </c>
-      <c r="F6" s="43" t="n">
+      <c r="F6" s="42" t="n">
         <v>0.2</v>
       </c>
-      <c r="G6" s="45" t="inlineStr">
+      <c r="G6" s="44" t="inlineStr">
         <is>
           <t>3 dari 3</t>
         </is>
@@ -17023,16 +17079,16 @@
 d) [KUNCI] Brand Kit  — 4 pemilih</t>
         </is>
       </c>
-      <c r="D7" s="43" t="n">
+      <c r="D7" s="42" t="n">
         <v>0.27</v>
       </c>
-      <c r="E7" s="43" t="n">
+      <c r="E7" s="42" t="n">
         <v>0.75</v>
       </c>
-      <c r="F7" s="43" t="n">
+      <c r="F7" s="42" t="n">
         <v>0.62</v>
       </c>
-      <c r="G7" s="45" t="inlineStr">
+      <c r="G7" s="44" t="inlineStr">
         <is>
           <t>3 dari 3</t>
         </is>
@@ -17060,16 +17116,16 @@
 d) [MATI]  Gunakan posisi strategis untuk membedakan informasi primer dan sekunder 1/5  — 0 pemilih</t>
         </is>
       </c>
-      <c r="D8" s="43" t="n">
+      <c r="D8" s="42" t="n">
         <v>0.6</v>
       </c>
-      <c r="E8" s="43" t="n">
+      <c r="E8" s="42" t="n">
         <v>1</v>
       </c>
-      <c r="F8" s="43" t="n">
+      <c r="F8" s="42" t="n">
         <v>0.88</v>
       </c>
-      <c r="G8" s="44" t="inlineStr">
+      <c r="G8" s="43" t="inlineStr">
         <is>
           <t>1 dari 3</t>
         </is>
@@ -17097,16 +17153,16 @@
 d) [MATI]  Rp 130.000  — 0 pemilih</t>
         </is>
       </c>
-      <c r="D9" s="43" t="n">
+      <c r="D9" s="42" t="n">
         <v>0.47</v>
       </c>
-      <c r="E9" s="43" t="n">
+      <c r="E9" s="42" t="n">
         <v>1</v>
       </c>
-      <c r="F9" s="43" t="n">
+      <c r="F9" s="42" t="n">
         <v>0.7</v>
       </c>
-      <c r="G9" s="44" t="inlineStr">
+      <c r="G9" s="43" t="inlineStr">
         <is>
           <t>0 dari 3</t>
         </is>
@@ -17134,16 +17190,16 @@
 d) [MATI]  PPTX (agar mudah diedit kembali)  — 0 pemilih</t>
         </is>
       </c>
-      <c r="D10" s="43" t="n">
+      <c r="D10" s="42" t="n">
         <v>0.53</v>
       </c>
-      <c r="E10" s="43" t="n">
+      <c r="E10" s="42" t="n">
         <v>0.75</v>
       </c>
-      <c r="F10" s="43" t="n">
+      <c r="F10" s="42" t="n">
         <v>0.59</v>
       </c>
-      <c r="G10" s="44" t="inlineStr">
+      <c r="G10" s="43" t="inlineStr">
         <is>
           <t>1 dari 3</t>
         </is>
@@ -17176,16 +17232,16 @@
 d) [KUNCI] (1), (2), (3), dan (4)  — 1 pemilih</t>
         </is>
       </c>
-      <c r="D11" s="43" t="n">
+      <c r="D11" s="42" t="n">
         <v>0.6</v>
       </c>
-      <c r="E11" s="43" t="n">
+      <c r="E11" s="42" t="n">
         <v>1</v>
       </c>
-      <c r="F11" s="43" t="n">
+      <c r="F11" s="42" t="n">
         <v>0.65</v>
       </c>
-      <c r="G11" s="44" t="inlineStr">
+      <c r="G11" s="43" t="inlineStr">
         <is>
           <t>1 dari 3</t>
         </is>
@@ -17213,16 +17269,16 @@
 d) [KUNCI] Pertobatan, penyesalan, kerendahan hati, dan persiapan batin  — 11 pemilih</t>
         </is>
       </c>
-      <c r="D12" s="43" t="n">
+      <c r="D12" s="42" t="n">
         <v>0.73</v>
       </c>
-      <c r="E12" s="43" t="n">
+      <c r="E12" s="42" t="n">
         <v>1</v>
       </c>
-      <c r="F12" s="43" t="n">
+      <c r="F12" s="42" t="n">
         <v>0.86</v>
       </c>
-      <c r="G12" s="44" t="inlineStr">
+      <c r="G12" s="43" t="inlineStr">
         <is>
           <t>0 dari 3</t>
         </is>
@@ -17250,16 +17306,16 @@
 d) PNG (kualitas gambar tertinggi) 2/5  — 1 pemilih</t>
         </is>
       </c>
-      <c r="D13" s="43" t="n">
+      <c r="D13" s="42" t="n">
         <v>0.6</v>
       </c>
-      <c r="E13" s="43" t="n">
+      <c r="E13" s="42" t="n">
         <v>1</v>
       </c>
-      <c r="F13" s="43" t="n">
+      <c r="F13" s="42" t="n">
         <v>0.76</v>
       </c>
-      <c r="G13" s="46" t="inlineStr">
+      <c r="G13" s="45" t="inlineStr">
         <is>
           <t>2 dari 3</t>
         </is>
@@ -17283,16 +17339,16 @@
 d) Desain perlu diperbaiki hanya pada pemilihan warna, jumlah font sudah ideal  — 2 pemilih</t>
         </is>
       </c>
-      <c r="D14" s="43" t="n">
+      <c r="D14" s="42" t="n">
         <v>0.6</v>
       </c>
-      <c r="E14" s="43" t="n">
+      <c r="E14" s="42" t="n">
         <v>1</v>
       </c>
-      <c r="F14" s="43" t="n">
+      <c r="F14" s="42" t="n">
         <v>0.73</v>
       </c>
-      <c r="G14" s="44" t="inlineStr">
+      <c r="G14" s="43" t="inlineStr">
         <is>
           <t>1 dari 3</t>
         </is>
@@ -17320,16 +17376,16 @@
 d) [KUNCI] Pengaturan resolusi layar monitor  — 5 pemilih</t>
         </is>
       </c>
-      <c r="D15" s="43" t="n">
+      <c r="D15" s="42" t="n">
         <v>0.33</v>
       </c>
-      <c r="E15" s="43" t="n">
+      <c r="E15" s="42" t="n">
         <v>0.5</v>
       </c>
-      <c r="F15" s="43" t="n">
+      <c r="F15" s="42" t="n">
         <v>0.5600000000000001</v>
       </c>
-      <c r="G15" s="46" t="inlineStr">
+      <c r="G15" s="45" t="inlineStr">
         <is>
           <t>2 dari 3</t>
         </is>
@@ -17353,16 +17409,16 @@
 d) [MATI]  Cliff Obrecht, Cameron Adams, dan Larry Page  — 0 pemilih</t>
         </is>
       </c>
-      <c r="D16" s="43" t="n">
+      <c r="D16" s="42" t="n">
         <v>0.53</v>
       </c>
-      <c r="E16" s="43" t="n">
+      <c r="E16" s="42" t="n">
         <v>1</v>
       </c>
-      <c r="F16" s="43" t="n">
+      <c r="F16" s="42" t="n">
         <v>0.74</v>
       </c>
-      <c r="G16" s="46" t="inlineStr">
+      <c r="G16" s="45" t="inlineStr">
         <is>
           <t>2 dari 3</t>
         </is>
@@ -17386,16 +17442,16 @@
 d) Filter — sesuaikan tone warna gambar  — 2 pemilih</t>
         </is>
       </c>
-      <c r="D17" s="43" t="n">
+      <c r="D17" s="42" t="n">
         <v>0.53</v>
       </c>
-      <c r="E17" s="43" t="n">
+      <c r="E17" s="42" t="n">
         <v>0.75</v>
       </c>
-      <c r="F17" s="43" t="n">
+      <c r="F17" s="42" t="n">
         <v>0.72</v>
       </c>
-      <c r="G17" s="46" t="inlineStr">
+      <c r="G17" s="45" t="inlineStr">
         <is>
           <t>2 dari 3</t>
         </is>
@@ -17419,16 +17475,16 @@
 d) [KUNCI] 1080 x 1080 px (Instagram Feed) 3/5  — 8 pemilih</t>
         </is>
       </c>
-      <c r="D18" s="43" t="n">
+      <c r="D18" s="42" t="n">
         <v>0.53</v>
       </c>
-      <c r="E18" s="43" t="n">
+      <c r="E18" s="42" t="n">
         <v>1</v>
       </c>
-      <c r="F18" s="43" t="n">
+      <c r="F18" s="42" t="n">
         <v>0.87</v>
       </c>
-      <c r="G18" s="46" t="inlineStr">
+      <c r="G18" s="45" t="inlineStr">
         <is>
           <t>2 dari 3</t>
         </is>
@@ -17452,16 +17508,16 @@
 d) Semangat melayani untuk menginspirasi sesama  — 1 pemilih</t>
         </is>
       </c>
-      <c r="D19" s="43" t="n">
+      <c r="D19" s="42" t="n">
         <v>0.47</v>
       </c>
-      <c r="E19" s="43" t="n">
+      <c r="E19" s="42" t="n">
         <v>0.5</v>
       </c>
-      <c r="F19" s="43" t="n">
+      <c r="F19" s="42" t="n">
         <v>0.51</v>
       </c>
-      <c r="G19" s="45" t="inlineStr">
+      <c r="G19" s="44" t="inlineStr">
         <is>
           <t>3 dari 3</t>
         </is>
@@ -17485,16 +17541,16 @@
 d) Login → Pilih menu Unggahan → Import Template → Gunakan  — 1 pemilih</t>
         </is>
       </c>
-      <c r="D20" s="43" t="n">
+      <c r="D20" s="42" t="n">
         <v>0.33</v>
       </c>
-      <c r="E20" s="43" t="n">
+      <c r="E20" s="42" t="n">
         <v>0.75</v>
       </c>
-      <c r="F20" s="43" t="n">
+      <c r="F20" s="42" t="n">
         <v>0.6</v>
       </c>
-      <c r="G20" s="45" t="inlineStr">
+      <c r="G20" s="44" t="inlineStr">
         <is>
           <t>3 dari 3</t>
         </is>
@@ -17518,16 +17574,16 @@
 d) Share tautan desain tanpa akses edit  — 1 pemilih</t>
         </is>
       </c>
-      <c r="D21" s="43" t="n">
+      <c r="D21" s="42" t="n">
         <v>0.13</v>
       </c>
-      <c r="E21" s="43" t="n">
+      <c r="E21" s="42" t="n">
         <v>0.5</v>
       </c>
-      <c r="F21" s="43" t="n">
+      <c r="F21" s="42" t="n">
         <v>0.55</v>
       </c>
-      <c r="G21" s="45" t="inlineStr">
+      <c r="G21" s="44" t="inlineStr">
         <is>
           <t>3 dari 3</t>
         </is>
@@ -17555,16 +17611,16 @@
 d) Menggunakan template AI Canva untuk mendukung kegiatan pelayanan gereja 4/5  — 1 pemilih</t>
         </is>
       </c>
-      <c r="D22" s="43" t="n">
+      <c r="D22" s="42" t="n">
         <v>0.47</v>
       </c>
-      <c r="E22" s="43" t="n">
+      <c r="E22" s="42" t="n">
         <v>0.75</v>
       </c>
-      <c r="F22" s="43" t="n">
+      <c r="F22" s="42" t="n">
         <v>0.76</v>
       </c>
-      <c r="G22" s="46" t="inlineStr">
+      <c r="G22" s="45" t="inlineStr">
         <is>
           <t>2 dari 3</t>
         </is>
@@ -17588,16 +17644,16 @@
 d) Kombinasi tiga warna yang membentuk segitiga pada roda warna  — 4 pemilih</t>
         </is>
       </c>
-      <c r="D23" s="43" t="n">
+      <c r="D23" s="42" t="n">
         <v>0.4</v>
       </c>
-      <c r="E23" s="43" t="n">
+      <c r="E23" s="42" t="n">
         <v>1</v>
       </c>
-      <c r="F23" s="43" t="n">
+      <c r="F23" s="42" t="n">
         <v>0.75</v>
       </c>
-      <c r="G23" s="44" t="inlineStr">
+      <c r="G23" s="43" t="inlineStr">
         <is>
           <t>1 dari 3</t>
         </is>
@@ -17625,16 +17681,16 @@
 d) [MATI]  Canva hanya berguna untuk keperluan media sosial dan tidak relevan untuk pelayanan gereja 5/5  — 0 pemilih</t>
         </is>
       </c>
-      <c r="D24" s="43" t="n">
+      <c r="D24" s="42" t="n">
         <v>0.67</v>
       </c>
-      <c r="E24" s="43" t="n">
+      <c r="E24" s="42" t="n">
         <v>1</v>
       </c>
-      <c r="F24" s="43" t="n">
+      <c r="F24" s="42" t="n">
         <v>0.87</v>
       </c>
-      <c r="G24" s="44" t="inlineStr">
+      <c r="G24" s="43" t="inlineStr">
         <is>
           <t>0 dari 3</t>
         </is>
@@ -17682,12 +17738,12 @@
       <c r="H29" s="4" t="inlineStr"/>
     </row>
     <row r="30" ht="18" customHeight="1">
-      <c r="A30" s="47" t="inlineStr">
+      <c r="A30" s="46" t="inlineStr">
         <is>
           <t>Q1</t>
         </is>
       </c>
-      <c r="B30" s="44" t="inlineStr">
+      <c r="B30" s="43" t="inlineStr">
         <is>
           <t>a)</t>
         </is>
@@ -17704,12 +17760,12 @@
       <c r="H30" s="10" t="n"/>
     </row>
     <row r="31" ht="18" customHeight="1">
-      <c r="A31" s="47" t="inlineStr">
+      <c r="A31" s="46" t="inlineStr">
         <is>
           <t>Q1</t>
         </is>
       </c>
-      <c r="B31" s="44" t="inlineStr">
+      <c r="B31" s="43" t="inlineStr">
         <is>
           <t>d)</t>
         </is>
@@ -17726,12 +17782,12 @@
       <c r="H31" s="10" t="n"/>
     </row>
     <row r="32" ht="18" customHeight="1">
-      <c r="A32" s="47" t="inlineStr">
+      <c r="A32" s="46" t="inlineStr">
         <is>
           <t>Q4</t>
         </is>
       </c>
-      <c r="B32" s="44" t="inlineStr">
+      <c r="B32" s="43" t="inlineStr">
         <is>
           <t>a)</t>
         </is>
@@ -17748,12 +17804,12 @@
       <c r="H32" s="10" t="n"/>
     </row>
     <row r="33" ht="18" customHeight="1">
-      <c r="A33" s="47" t="inlineStr">
+      <c r="A33" s="46" t="inlineStr">
         <is>
           <t>Q4</t>
         </is>
       </c>
-      <c r="B33" s="44" t="inlineStr">
+      <c r="B33" s="43" t="inlineStr">
         <is>
           <t>d)</t>
         </is>
@@ -17770,12 +17826,12 @@
       <c r="H33" s="10" t="n"/>
     </row>
     <row r="34" ht="18" customHeight="1">
-      <c r="A34" s="47" t="inlineStr">
+      <c r="A34" s="46" t="inlineStr">
         <is>
           <t>Q5</t>
         </is>
       </c>
-      <c r="B34" s="44" t="inlineStr">
+      <c r="B34" s="43" t="inlineStr">
         <is>
           <t>c)</t>
         </is>
@@ -17792,12 +17848,12 @@
       <c r="H34" s="10" t="n"/>
     </row>
     <row r="35" ht="18" customHeight="1">
-      <c r="A35" s="47" t="inlineStr">
+      <c r="A35" s="46" t="inlineStr">
         <is>
           <t>Q5</t>
         </is>
       </c>
-      <c r="B35" s="44" t="inlineStr">
+      <c r="B35" s="43" t="inlineStr">
         <is>
           <t>d)</t>
         </is>
@@ -17814,12 +17870,12 @@
       <c r="H35" s="10" t="n"/>
     </row>
     <row r="36" ht="18" customHeight="1">
-      <c r="A36" s="47" t="inlineStr">
+      <c r="A36" s="46" t="inlineStr">
         <is>
           <t>Q6</t>
         </is>
       </c>
-      <c r="B36" s="44" t="inlineStr">
+      <c r="B36" s="43" t="inlineStr">
         <is>
           <t>b)</t>
         </is>
@@ -17836,12 +17892,12 @@
       <c r="H36" s="10" t="n"/>
     </row>
     <row r="37" ht="18" customHeight="1">
-      <c r="A37" s="47" t="inlineStr">
+      <c r="A37" s="46" t="inlineStr">
         <is>
           <t>Q6</t>
         </is>
       </c>
-      <c r="B37" s="44" t="inlineStr">
+      <c r="B37" s="43" t="inlineStr">
         <is>
           <t>d)</t>
         </is>
@@ -17858,12 +17914,12 @@
       <c r="H37" s="10" t="n"/>
     </row>
     <row r="38" ht="18" customHeight="1">
-      <c r="A38" s="47" t="inlineStr">
+      <c r="A38" s="46" t="inlineStr">
         <is>
           <t>Q8</t>
         </is>
       </c>
-      <c r="B38" s="44" t="inlineStr">
+      <c r="B38" s="43" t="inlineStr">
         <is>
           <t>a)</t>
         </is>
@@ -17880,12 +17936,12 @@
       <c r="H38" s="10" t="n"/>
     </row>
     <row r="39" ht="18" customHeight="1">
-      <c r="A39" s="47" t="inlineStr">
+      <c r="A39" s="46" t="inlineStr">
         <is>
           <t>Q8</t>
         </is>
       </c>
-      <c r="B39" s="44" t="inlineStr">
+      <c r="B39" s="43" t="inlineStr">
         <is>
           <t>b)</t>
         </is>
@@ -17902,12 +17958,12 @@
       <c r="H39" s="10" t="n"/>
     </row>
     <row r="40" ht="18" customHeight="1">
-      <c r="A40" s="47" t="inlineStr">
+      <c r="A40" s="46" t="inlineStr">
         <is>
           <t>Q8</t>
         </is>
       </c>
-      <c r="B40" s="44" t="inlineStr">
+      <c r="B40" s="43" t="inlineStr">
         <is>
           <t>c)</t>
         </is>
@@ -17924,12 +17980,12 @@
       <c r="H40" s="10" t="n"/>
     </row>
     <row r="41" ht="18" customHeight="1">
-      <c r="A41" s="47" t="inlineStr">
+      <c r="A41" s="46" t="inlineStr">
         <is>
           <t>Q9</t>
         </is>
       </c>
-      <c r="B41" s="44" t="inlineStr">
+      <c r="B41" s="43" t="inlineStr">
         <is>
           <t>b)</t>
         </is>
@@ -17946,12 +18002,12 @@
       <c r="H41" s="10" t="n"/>
     </row>
     <row r="42" ht="18" customHeight="1">
-      <c r="A42" s="47" t="inlineStr">
+      <c r="A42" s="46" t="inlineStr">
         <is>
           <t>Q10</t>
         </is>
       </c>
-      <c r="B42" s="44" t="inlineStr">
+      <c r="B42" s="43" t="inlineStr">
         <is>
           <t>a)</t>
         </is>
@@ -17968,12 +18024,12 @@
       <c r="H42" s="10" t="n"/>
     </row>
     <row r="43" ht="18" customHeight="1">
-      <c r="A43" s="47" t="inlineStr">
+      <c r="A43" s="46" t="inlineStr">
         <is>
           <t>Q10</t>
         </is>
       </c>
-      <c r="B43" s="44" t="inlineStr">
+      <c r="B43" s="43" t="inlineStr">
         <is>
           <t>c)</t>
         </is>
@@ -17990,12 +18046,12 @@
       <c r="H43" s="10" t="n"/>
     </row>
     <row r="44" ht="18" customHeight="1">
-      <c r="A44" s="47" t="inlineStr">
+      <c r="A44" s="46" t="inlineStr">
         <is>
           <t>Q11</t>
         </is>
       </c>
-      <c r="B44" s="44" t="inlineStr">
+      <c r="B44" s="43" t="inlineStr">
         <is>
           <t>a)</t>
         </is>
@@ -18012,12 +18068,12 @@
       <c r="H44" s="10" t="n"/>
     </row>
     <row r="45" ht="18" customHeight="1">
-      <c r="A45" s="47" t="inlineStr">
+      <c r="A45" s="46" t="inlineStr">
         <is>
           <t>Q12</t>
         </is>
       </c>
-      <c r="B45" s="44" t="inlineStr">
+      <c r="B45" s="43" t="inlineStr">
         <is>
           <t>a)</t>
         </is>
@@ -18034,12 +18090,12 @@
       <c r="H45" s="10" t="n"/>
     </row>
     <row r="46" ht="18" customHeight="1">
-      <c r="A46" s="47" t="inlineStr">
+      <c r="A46" s="46" t="inlineStr">
         <is>
           <t>Q12</t>
         </is>
       </c>
-      <c r="B46" s="44" t="inlineStr">
+      <c r="B46" s="43" t="inlineStr">
         <is>
           <t>d)</t>
         </is>
@@ -18056,12 +18112,12 @@
       <c r="H46" s="10" t="n"/>
     </row>
     <row r="47" ht="18" customHeight="1">
-      <c r="A47" s="47" t="inlineStr">
+      <c r="A47" s="46" t="inlineStr">
         <is>
           <t>Q13</t>
         </is>
       </c>
-      <c r="B47" s="44" t="inlineStr">
+      <c r="B47" s="43" t="inlineStr">
         <is>
           <t>c)</t>
         </is>
@@ -18078,12 +18134,12 @@
       <c r="H47" s="10" t="n"/>
     </row>
     <row r="48" ht="18" customHeight="1">
-      <c r="A48" s="47" t="inlineStr">
+      <c r="A48" s="46" t="inlineStr">
         <is>
           <t>Q14</t>
         </is>
       </c>
-      <c r="B48" s="44" t="inlineStr">
+      <c r="B48" s="43" t="inlineStr">
         <is>
           <t>c)</t>
         </is>
@@ -18100,12 +18156,12 @@
       <c r="H48" s="10" t="n"/>
     </row>
     <row r="49" ht="18" customHeight="1">
-      <c r="A49" s="47" t="inlineStr">
+      <c r="A49" s="46" t="inlineStr">
         <is>
           <t>Q18</t>
         </is>
       </c>
-      <c r="B49" s="44" t="inlineStr">
+      <c r="B49" s="43" t="inlineStr">
         <is>
           <t>a)</t>
         </is>
@@ -18122,12 +18178,12 @@
       <c r="H49" s="10" t="n"/>
     </row>
     <row r="50" ht="18" customHeight="1">
-      <c r="A50" s="47" t="inlineStr">
+      <c r="A50" s="46" t="inlineStr">
         <is>
           <t>Q19</t>
         </is>
       </c>
-      <c r="B50" s="44" t="inlineStr">
+      <c r="B50" s="43" t="inlineStr">
         <is>
           <t>a)</t>
         </is>
@@ -18144,12 +18200,12 @@
       <c r="H50" s="10" t="n"/>
     </row>
     <row r="51" ht="18" customHeight="1">
-      <c r="A51" s="47" t="inlineStr">
+      <c r="A51" s="46" t="inlineStr">
         <is>
           <t>Q19</t>
         </is>
       </c>
-      <c r="B51" s="44" t="inlineStr">
+      <c r="B51" s="43" t="inlineStr">
         <is>
           <t>b)</t>
         </is>
@@ -18166,12 +18222,12 @@
       <c r="H51" s="10" t="n"/>
     </row>
     <row r="52" ht="18" customHeight="1">
-      <c r="A52" s="47" t="inlineStr">
+      <c r="A52" s="46" t="inlineStr">
         <is>
           <t>Q20</t>
         </is>
       </c>
-      <c r="B52" s="44" t="inlineStr">
+      <c r="B52" s="43" t="inlineStr">
         <is>
           <t>a)</t>
         </is>
@@ -18188,12 +18244,12 @@
       <c r="H52" s="10" t="n"/>
     </row>
     <row r="53" ht="18" customHeight="1">
-      <c r="A53" s="47" t="inlineStr">
+      <c r="A53" s="46" t="inlineStr">
         <is>
           <t>Q20</t>
         </is>
       </c>
-      <c r="B53" s="44" t="inlineStr">
+      <c r="B53" s="43" t="inlineStr">
         <is>
           <t>b)</t>
         </is>
@@ -18210,12 +18266,12 @@
       <c r="H53" s="10" t="n"/>
     </row>
     <row r="54" ht="18" customHeight="1">
-      <c r="A54" s="47" t="inlineStr">
+      <c r="A54" s="46" t="inlineStr">
         <is>
           <t>Q20</t>
         </is>
       </c>
-      <c r="B54" s="44" t="inlineStr">
+      <c r="B54" s="43" t="inlineStr">
         <is>
           <t>d)</t>
         </is>
@@ -18346,7 +18402,7 @@
       <c r="H5" s="4" t="inlineStr"/>
     </row>
     <row r="6" ht="64" customHeight="1">
-      <c r="A6" s="48" t="n">
+      <c r="A6" s="47" t="n">
         <v>1</v>
       </c>
       <c r="B6" s="5" t="inlineStr">
@@ -18370,7 +18426,7 @@
       <c r="H6" s="10" t="n"/>
     </row>
     <row r="7" ht="64" customHeight="1">
-      <c r="A7" s="48" t="n">
+      <c r="A7" s="47" t="n">
         <v>2</v>
       </c>
       <c r="B7" s="5" t="inlineStr">
@@ -18394,7 +18450,7 @@
       <c r="H7" s="10" t="n"/>
     </row>
     <row r="8" ht="64" customHeight="1">
-      <c r="A8" s="48" t="n">
+      <c r="A8" s="47" t="n">
         <v>3</v>
       </c>
       <c r="B8" s="5" t="inlineStr">
@@ -18418,7 +18474,7 @@
       <c r="H8" s="10" t="n"/>
     </row>
     <row r="9" ht="64" customHeight="1">
-      <c r="A9" s="48" t="n">
+      <c r="A9" s="47" t="n">
         <v>4</v>
       </c>
       <c r="B9" s="5" t="inlineStr">
@@ -18442,7 +18498,7 @@
       <c r="H9" s="10" t="n"/>
     </row>
     <row r="10" ht="64" customHeight="1">
-      <c r="A10" s="48" t="n">
+      <c r="A10" s="47" t="n">
         <v>5</v>
       </c>
       <c r="B10" s="5" t="inlineStr">
@@ -18466,7 +18522,7 @@
       <c r="H10" s="10" t="n"/>
     </row>
     <row r="11" ht="64" customHeight="1">
-      <c r="A11" s="48" t="n">
+      <c r="A11" s="47" t="n">
         <v>6</v>
       </c>
       <c r="B11" s="5" t="inlineStr">
@@ -18984,7 +19040,7 @@
       <c r="F5" s="4" t="inlineStr"/>
     </row>
     <row r="6" ht="48" customHeight="1">
-      <c r="A6" s="49" t="inlineStr">
+      <c r="A6" s="48" t="inlineStr">
         <is>
           <t>post-testpelatihancanva25agustus2026-...-68e3ea.xlsx</t>
         </is>
@@ -19004,7 +19060,7 @@
       <c r="F6" s="10" t="n"/>
     </row>
     <row r="7" ht="48" customHeight="1">
-      <c r="A7" s="49" t="inlineStr">
+      <c r="A7" s="48" t="inlineStr">
         <is>
           <t>Free Printable post-test pelatihan canva 25 agustus 2026.pdf</t>
         </is>
@@ -19024,7 +19080,7 @@
       <c r="F7" s="10" t="n"/>
     </row>
     <row r="8" ht="48" customHeight="1">
-      <c r="A8" s="49" t="inlineStr">
+      <c r="A8" s="48" t="inlineStr">
         <is>
           <t>core.json / stats.json (dari laporan pre-test)</t>
         </is>
@@ -19242,7 +19298,7 @@
           <t>Tingkat kesukaran (p)</t>
         </is>
       </c>
-      <c r="B30" s="50" t="inlineStr">
+      <c r="B30" s="49" t="inlineStr">
         <is>
           <t>p = B / N</t>
         </is>
@@ -19262,7 +19318,7 @@
           <t>Daya beda (D)</t>
         </is>
       </c>
-      <c r="B31" s="50" t="inlineStr">
+      <c r="B31" s="49" t="inlineStr">
         <is>
           <t>D = (BA / nA) − (BB / nB)</t>
         </is>
@@ -19282,7 +19338,7 @@
           <t>Point-biserial</t>
         </is>
       </c>
-      <c r="B32" s="50" t="inlineStr">
+      <c r="B32" s="49" t="inlineStr">
         <is>
           <t>r = ((M1 − M0) / SDt) × akar(p × q)</t>
         </is>
@@ -19302,7 +19358,7 @@
           <t>Reliabilitas KR-20</t>
         </is>
       </c>
-      <c r="B33" s="50" t="inlineStr">
+      <c r="B33" s="49" t="inlineStr">
         <is>
           <t>KR20 = (k/(k−1)) × (1 − jumlah pq / varians)</t>
         </is>
@@ -19322,7 +19378,7 @@
           <t>Kesalahan baku ukur</t>
         </is>
       </c>
-      <c r="B34" s="50" t="inlineStr">
+      <c r="B34" s="49" t="inlineStr">
         <is>
           <t>SEM = SD × akar(1 − r)</t>
         </is>
@@ -19342,7 +19398,7 @@
           <t>Gain mentah</t>
         </is>
       </c>
-      <c r="B35" s="50" t="inlineStr">
+      <c r="B35" s="49" t="inlineStr">
         <is>
           <t>gain = post − pre</t>
         </is>
@@ -19362,7 +19418,7 @@
           <t>Gain ternormalisasi (Hake)</t>
         </is>
       </c>
-      <c r="B36" s="50" t="inlineStr">
+      <c r="B36" s="49" t="inlineStr">
         <is>
           <t>g = (post − pre) / (maks − pre)</t>
         </is>
@@ -19382,7 +19438,7 @@
           <t>Uji-t berpasangan</t>
         </is>
       </c>
-      <c r="B37" s="50" t="inlineStr">
+      <c r="B37" s="49" t="inlineStr">
         <is>
           <t>t = rata gain / (SD gain / akar n)</t>
         </is>
@@ -19402,7 +19458,7 @@
           <t>Ukuran efek Cohen dz</t>
         </is>
       </c>
-      <c r="B38" s="50" t="inlineStr">
+      <c r="B38" s="49" t="inlineStr">
         <is>
           <t>dz = rata gain / SD gain</t>
         </is>
@@ -19422,7 +19478,7 @@
           <t>Uji tanda</t>
         </is>
       </c>
-      <c r="B39" s="50" t="inlineStr">
+      <c r="B39" s="49" t="inlineStr">
         <is>
           <t>peluang binomial k naik dari n, p = 0,5</t>
         </is>
